--- a/Docs_StandardWork_Reference/แบบฟอร์มตารางจับเวลา 1.xlsx
+++ b/Docs_StandardWork_Reference/แบบฟอร์มตารางจับเวลา 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a16c04e9e107df29/33.INJ BU_One Drive/39.TPS Activity/Standardized Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_LocalFile_WebApp\ManMachineChart_StandardOperation\Docs_StandardWork_Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_D666A9E929A58410BE1D63A12D6BAFDB5E755147" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96612C38-6582-44F9-8397-47E0C198DFF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACA2753-DF9F-4870-850A-D97B6D9E19A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ตารางจับเวลา" sheetId="1" r:id="rId1"/>
@@ -412,9 +412,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="187" formatCode="0.0"/>
-    <numFmt numFmtId="188" formatCode="[$-101041E]d\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="189" formatCode="[$-101041E]d\ mmm\ yy;@"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="[$-101041E]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-101041E]d\ mmm\ yy;@"/>
   </numFmts>
   <fonts count="92" x14ac:knownFonts="1">
     <font>
@@ -2120,10 +2120,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2144,19 +2144,19 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2204,7 +2204,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="47" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="37" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="47" applyFont="1" applyBorder="1"/>
@@ -2275,7 +2275,7 @@
     <xf numFmtId="2" fontId="49" fillId="0" borderId="13" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2499,6 +2499,126 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="52" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="60" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="44" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="40" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="49" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="49" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="88" fillId="0" borderId="50" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="59" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="55" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2514,197 +2634,218 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="60" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="55" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="52" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="60" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="44" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="40" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="49" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="49" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="48" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="88" fillId="0" borderId="50" xfId="47" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="59" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="48" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="54" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="55" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="45" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="63" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="50" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="49" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="44" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="55" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="45" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="42" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="43" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="40" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="50" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="41" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="44" xfId="50" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="55" xfId="50" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="45" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="42" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="50" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="43" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="40" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="50" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="41" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="13" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="52" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="60" xfId="50" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="44" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="54" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="55" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="45" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="63" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="50" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="55" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="45" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="47" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="42" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="43" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="40" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="50" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="41" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="47" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="40" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="55" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="50" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="49" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2715,9 +2856,6 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="48" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="52" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="44" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2736,143 +2874,29 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="41" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="40" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="50" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="49" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="59" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="48" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="49" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="59" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="55" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="50" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="24" borderId="48" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="44" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="55" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="45" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="42" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="43" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="40" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="50" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="41" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="44" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="55" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="45" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="42" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="50" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="43" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="40" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="50" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="41" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="13" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="60" xfId="50" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="44" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="55" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="45" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="42" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="43" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="40" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="50" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="41" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="59" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="13" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="49" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2898,28 +2922,40 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="49" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="59" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="48" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="49" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="59" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="24" borderId="48" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2978,42 +3014,6 @@
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -7658,9 +7658,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7698,9 +7698,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7733,26 +7733,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7785,26 +7768,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7979,83 +7945,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S39"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="21.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.07421875" defaultRowHeight="21" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
-    <col min="2" max="2" width="79.6640625" style="2" customWidth="1"/>
-    <col min="3" max="17" width="13.33203125" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="2"/>
+    <col min="2" max="2" width="79.69140625" style="2" customWidth="1"/>
+    <col min="3" max="17" width="13.3046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9.07421875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A1" s="1"/>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="201" t="s">
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="N1" s="200" t="s">
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="241"/>
+      <c r="N1" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-    </row>
-    <row r="2" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="203" t="s">
+      <c r="O1" s="240"/>
+      <c r="P1" s="240"/>
+      <c r="Q1" s="240"/>
+    </row>
+    <row r="2" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="243" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-    </row>
-    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+    </row>
+    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="F3" s="146"/>
-      <c r="G3" s="201" t="s">
+      <c r="G3" s="241" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
-      <c r="L3" s="201"/>
-      <c r="N3" s="200" t="s">
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+      <c r="L3" s="241"/>
+      <c r="N3" s="240" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="200"/>
-      <c r="P3" s="200"/>
-      <c r="Q3" s="200"/>
-    </row>
-    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="O3" s="240"/>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="240"/>
+    </row>
+    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B4" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="201" t="s">
+      <c r="C4" s="241" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="201"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="201"/>
-    </row>
-    <row r="5" spans="1:19" ht="9.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+    </row>
+    <row r="5" spans="1:19" ht="9.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -8107,7 +8073,7 @@
       </c>
       <c r="R6" s="13"/>
     </row>
-    <row r="7" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A7" s="54">
         <v>1</v>
       </c>
@@ -8133,7 +8099,7 @@
       </c>
       <c r="S7" s="24"/>
     </row>
-    <row r="8" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="55">
         <v>2</v>
       </c>
@@ -8159,7 +8125,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A9" s="55">
         <v>3</v>
       </c>
@@ -8185,7 +8151,7 @@
       </c>
       <c r="S9" s="24"/>
     </row>
-    <row r="10" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A10" s="55">
         <v>4</v>
       </c>
@@ -8211,7 +8177,7 @@
       </c>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A11" s="55">
         <v>5</v>
       </c>
@@ -8237,7 +8203,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A12" s="55">
         <v>6</v>
       </c>
@@ -8263,7 +8229,7 @@
       </c>
       <c r="S12" s="24"/>
     </row>
-    <row r="13" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A13" s="55">
         <v>7</v>
       </c>
@@ -8289,7 +8255,7 @@
       </c>
       <c r="S13" s="24"/>
     </row>
-    <row r="14" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A14" s="55">
         <v>8</v>
       </c>
@@ -8315,7 +8281,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A15" s="55">
         <v>9</v>
       </c>
@@ -8341,7 +8307,7 @@
       </c>
       <c r="S15" s="24"/>
     </row>
-    <row r="16" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A16" s="55">
         <v>10</v>
       </c>
@@ -8367,7 +8333,7 @@
       </c>
       <c r="S16" s="24"/>
     </row>
-    <row r="17" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A17" s="55">
         <v>11</v>
       </c>
@@ -8393,7 +8359,7 @@
       </c>
       <c r="S17" s="24"/>
     </row>
-    <row r="18" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A18" s="55">
         <v>12</v>
       </c>
@@ -8419,7 +8385,7 @@
       </c>
       <c r="S18" s="24"/>
     </row>
-    <row r="19" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A19" s="55">
         <v>13</v>
       </c>
@@ -8445,7 +8411,7 @@
       </c>
       <c r="S19" s="24"/>
     </row>
-    <row r="20" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A20" s="55">
         <v>14</v>
       </c>
@@ -8471,7 +8437,7 @@
       </c>
       <c r="S20" s="24"/>
     </row>
-    <row r="21" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A21" s="55">
         <v>15</v>
       </c>
@@ -8497,7 +8463,7 @@
       </c>
       <c r="S21" s="24"/>
     </row>
-    <row r="22" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A22" s="55">
         <v>16</v>
       </c>
@@ -8523,7 +8489,7 @@
       </c>
       <c r="S22" s="24"/>
     </row>
-    <row r="23" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A23" s="55">
         <v>17</v>
       </c>
@@ -8549,7 +8515,7 @@
       </c>
       <c r="S23" s="24"/>
     </row>
-    <row r="24" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A24" s="55">
         <v>18</v>
       </c>
@@ -8575,7 +8541,7 @@
       </c>
       <c r="S24" s="24"/>
     </row>
-    <row r="25" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A25" s="55">
         <v>19</v>
       </c>
@@ -8601,7 +8567,7 @@
       </c>
       <c r="S25" s="24"/>
     </row>
-    <row r="26" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A26" s="55">
         <v>20</v>
       </c>
@@ -8627,7 +8593,7 @@
       </c>
       <c r="S26" s="24"/>
     </row>
-    <row r="27" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A27" s="55">
         <v>21</v>
       </c>
@@ -8653,7 +8619,7 @@
       </c>
       <c r="S27" s="24"/>
     </row>
-    <row r="28" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A28" s="55">
         <v>22</v>
       </c>
@@ -8679,7 +8645,7 @@
       </c>
       <c r="S28" s="24"/>
     </row>
-    <row r="29" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A29" s="55">
         <v>23</v>
       </c>
@@ -8705,7 +8671,7 @@
       </c>
       <c r="S29" s="35"/>
     </row>
-    <row r="30" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A30" s="55">
         <v>24</v>
       </c>
@@ -8731,7 +8697,7 @@
       </c>
       <c r="S30" s="24"/>
     </row>
-    <row r="31" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A31" s="55">
         <v>25</v>
       </c>
@@ -8757,7 +8723,7 @@
       </c>
       <c r="S31" s="24"/>
     </row>
-    <row r="32" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:19" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A32" s="55">
         <v>26</v>
       </c>
@@ -8782,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A33" s="55">
         <v>27</v>
       </c>
@@ -8807,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A34" s="55">
         <v>28</v>
       </c>
@@ -8832,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A35" s="55">
         <v>29</v>
       </c>
@@ -8857,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A36" s="55">
         <v>30</v>
       </c>
@@ -8882,7 +8848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:18" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="39"/>
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
@@ -8901,11 +8867,11 @@
       <c r="Q37" s="48"/>
       <c r="R37" s="39"/>
     </row>
-    <row r="38" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="198" t="s">
+    <row r="38" spans="1:18" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A38" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="199"/>
+      <c r="B38" s="239"/>
       <c r="C38" s="49"/>
       <c r="D38" s="49"/>
       <c r="E38" s="49"/>
@@ -8922,7 +8888,7 @@
       <c r="P38" s="52"/>
       <c r="Q38" s="52"/>
     </row>
-    <row r="39" spans="1:18" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:18" s="25" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.65">
       <c r="A39" s="53"/>
     </row>
   </sheetData>
@@ -8951,155 +8917,155 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W365"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="5" width="16.109375" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="18.109375" customWidth="1"/>
-    <col min="23" max="23" width="1.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.84375" customWidth="1"/>
+    <col min="3" max="3" width="13.3046875" customWidth="1"/>
+    <col min="4" max="5" width="16.07421875" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" customWidth="1"/>
+    <col min="7" max="12" width="17.69140625" customWidth="1"/>
+    <col min="13" max="13" width="18.07421875" customWidth="1"/>
+    <col min="23" max="23" width="1.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="46.5" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:23" ht="46.5" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A1" s="186"/>
       <c r="B1" s="189"/>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="237" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="204" t="s">
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
+      <c r="K1" s="237"/>
+      <c r="L1" s="237"/>
+      <c r="M1" s="237"/>
+      <c r="N1" s="228" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="204"/>
-      <c r="P1" s="204"/>
-      <c r="Q1" s="204" t="s">
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="204"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="204" t="s">
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228" t="s">
         <v>80</v>
       </c>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
-      <c r="W1" s="204"/>
-    </row>
-    <row r="2" spans="1:23" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+    </row>
+    <row r="2" spans="1:23" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="191"/>
       <c r="B2" s="190"/>
-      <c r="C2" s="240" t="s">
+      <c r="C2" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="M2" s="240"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="214"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="214"/>
-      <c r="S2" s="215"/>
-      <c r="T2" s="205"/>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
-      <c r="W2" s="205"/>
-    </row>
-    <row r="3" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="231" t="s">
+      <c r="D2" s="224"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="224"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
+      <c r="M2" s="224"/>
+      <c r="N2" s="206"/>
+      <c r="O2" s="207"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="206"/>
+      <c r="R2" s="207"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="229"/>
+      <c r="U2" s="229"/>
+      <c r="V2" s="229"/>
+      <c r="W2" s="229"/>
+    </row>
+    <row r="3" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="232"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="235" t="s">
+      <c r="B3" s="216"/>
+      <c r="C3" s="225"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="225"/>
+      <c r="F3" s="225"/>
+      <c r="G3" s="219" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="236"/>
-      <c r="I3" s="236"/>
-      <c r="J3" s="236"/>
-      <c r="K3" s="236"/>
-      <c r="L3" s="236"/>
-      <c r="M3" s="237"/>
-      <c r="N3" s="216"/>
-      <c r="O3" s="217"/>
-      <c r="P3" s="218"/>
-      <c r="Q3" s="216"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="218"/>
-      <c r="T3" s="205"/>
-      <c r="U3" s="205"/>
-      <c r="V3" s="205"/>
-      <c r="W3" s="205"/>
-    </row>
-    <row r="4" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="1.05">
-      <c r="A4" s="233" t="s">
+      <c r="H3" s="220"/>
+      <c r="I3" s="220"/>
+      <c r="J3" s="220"/>
+      <c r="K3" s="220"/>
+      <c r="L3" s="220"/>
+      <c r="M3" s="221"/>
+      <c r="N3" s="209"/>
+      <c r="O3" s="210"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="210"/>
+      <c r="S3" s="211"/>
+      <c r="T3" s="229"/>
+      <c r="U3" s="229"/>
+      <c r="V3" s="229"/>
+      <c r="W3" s="229"/>
+    </row>
+    <row r="4" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="1.4">
+      <c r="A4" s="217" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="234"/>
-      <c r="C4" s="241"/>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="238" t="s">
+      <c r="B4" s="218"/>
+      <c r="C4" s="225"/>
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="225"/>
+      <c r="G4" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="M4" s="239"/>
-      <c r="N4" s="219"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="221"/>
-      <c r="Q4" s="219"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="221"/>
-      <c r="T4" s="205"/>
-      <c r="U4" s="205"/>
-      <c r="V4" s="205"/>
-      <c r="W4" s="205"/>
-    </row>
-    <row r="5" spans="1:23" ht="36.6" x14ac:dyDescent="0.95">
-      <c r="A5" s="233" t="s">
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="229"/>
+      <c r="U4" s="229"/>
+      <c r="V4" s="229"/>
+      <c r="W4" s="229"/>
+    </row>
+    <row r="5" spans="1:23" ht="35.6" x14ac:dyDescent="1.25">
+      <c r="A5" s="217" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="234"/>
-      <c r="C5" s="241"/>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="225"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
       <c r="G5" s="184"/>
-      <c r="H5" s="242" t="s">
+      <c r="H5" s="226" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="243"/>
+      <c r="I5" s="227"/>
       <c r="J5" s="185"/>
-      <c r="K5" s="242" t="s">
+      <c r="K5" s="226" t="s">
         <v>83</v>
       </c>
-      <c r="L5" s="243"/>
+      <c r="L5" s="227"/>
       <c r="M5" s="169"/>
       <c r="N5" s="181"/>
       <c r="O5" s="169"/>
@@ -9114,30 +9080,30 @@
       <c r="V5" s="169"/>
       <c r="W5" s="189"/>
     </row>
-    <row r="6" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="226" t="s">
+    <row r="6" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="201" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="227" t="s">
+      <c r="C6" s="201"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="202" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="212" t="s">
+      <c r="G6" s="236" t="s">
         <v>97</v>
       </c>
-      <c r="H6" s="212"/>
-      <c r="I6" s="212"/>
-      <c r="J6" s="212" t="s">
+      <c r="H6" s="236"/>
+      <c r="I6" s="236"/>
+      <c r="J6" s="236" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="212"/>
-      <c r="L6" s="212"/>
-      <c r="M6" s="229" t="s">
+      <c r="K6" s="236"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="204" t="s">
         <v>106</v>
       </c>
       <c r="N6" s="182"/>
@@ -9153,13 +9119,13 @@
       <c r="V6" s="179"/>
       <c r="W6" s="188"/>
     </row>
-    <row r="7" spans="1:23" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="226"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="228"/>
+    <row r="7" spans="1:23" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="201"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="203"/>
       <c r="G7" s="194" t="s">
         <v>99</v>
       </c>
@@ -9178,7 +9144,7 @@
       <c r="L7" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="230"/>
+      <c r="M7" s="205"/>
       <c r="N7" s="183"/>
       <c r="O7" s="172"/>
       <c r="P7" s="172"/>
@@ -9190,12 +9156,12 @@
       <c r="V7" s="172"/>
       <c r="W7" s="190"/>
     </row>
-    <row r="8" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="180"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="224"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="225"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="199"/>
+      <c r="D8" s="199"/>
+      <c r="E8" s="200"/>
       <c r="F8" s="180"/>
       <c r="G8" s="180"/>
       <c r="H8" s="180"/>
@@ -9215,12 +9181,12 @@
       <c r="V8" s="180"/>
       <c r="W8" s="180"/>
     </row>
-    <row r="9" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="180"/>
-      <c r="B9" s="223"/>
-      <c r="C9" s="224"/>
-      <c r="D9" s="224"/>
-      <c r="E9" s="225"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="200"/>
       <c r="F9" s="180"/>
       <c r="G9" s="180"/>
       <c r="H9" s="180"/>
@@ -9240,12 +9206,12 @@
       <c r="V9" s="180"/>
       <c r="W9" s="180"/>
     </row>
-    <row r="10" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="180"/>
-      <c r="B10" s="223"/>
-      <c r="C10" s="224"/>
-      <c r="D10" s="224"/>
-      <c r="E10" s="225"/>
+      <c r="B10" s="198"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="200"/>
       <c r="F10" s="180"/>
       <c r="G10" s="180"/>
       <c r="H10" s="180"/>
@@ -9265,12 +9231,12 @@
       <c r="V10" s="180"/>
       <c r="W10" s="180"/>
     </row>
-    <row r="11" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="180"/>
-      <c r="B11" s="223"/>
-      <c r="C11" s="224"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="225"/>
+      <c r="B11" s="198"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="199"/>
+      <c r="E11" s="200"/>
       <c r="F11" s="180"/>
       <c r="G11" s="180"/>
       <c r="H11" s="180"/>
@@ -9290,12 +9256,12 @@
       <c r="V11" s="180"/>
       <c r="W11" s="180"/>
     </row>
-    <row r="12" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="180"/>
-      <c r="B12" s="223"/>
-      <c r="C12" s="224"/>
-      <c r="D12" s="224"/>
-      <c r="E12" s="225"/>
+      <c r="B12" s="198"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="200"/>
       <c r="F12" s="180"/>
       <c r="G12" s="180"/>
       <c r="H12" s="180"/>
@@ -9315,12 +9281,12 @@
       <c r="V12" s="180"/>
       <c r="W12" s="180"/>
     </row>
-    <row r="13" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="180"/>
-      <c r="B13" s="223"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="225"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
+      <c r="E13" s="200"/>
       <c r="F13" s="180"/>
       <c r="G13" s="180"/>
       <c r="H13" s="180"/>
@@ -9340,12 +9306,12 @@
       <c r="V13" s="180"/>
       <c r="W13" s="180"/>
     </row>
-    <row r="14" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="180"/>
-      <c r="B14" s="223"/>
-      <c r="C14" s="224"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="225"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
+      <c r="E14" s="200"/>
       <c r="F14" s="180"/>
       <c r="G14" s="180"/>
       <c r="H14" s="180"/>
@@ -9365,12 +9331,12 @@
       <c r="V14" s="180"/>
       <c r="W14" s="180"/>
     </row>
-    <row r="15" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="180"/>
-      <c r="B15" s="223"/>
-      <c r="C15" s="224"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="225"/>
+      <c r="B15" s="198"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
+      <c r="E15" s="200"/>
       <c r="F15" s="180"/>
       <c r="G15" s="180"/>
       <c r="H15" s="180"/>
@@ -9390,12 +9356,12 @@
       <c r="V15" s="180"/>
       <c r="W15" s="180"/>
     </row>
-    <row r="16" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="180"/>
-      <c r="B16" s="223"/>
-      <c r="C16" s="224"/>
-      <c r="D16" s="224"/>
-      <c r="E16" s="225"/>
+      <c r="B16" s="198"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
+      <c r="E16" s="200"/>
       <c r="F16" s="180"/>
       <c r="G16" s="180"/>
       <c r="H16" s="180"/>
@@ -9415,12 +9381,12 @@
       <c r="V16" s="180"/>
       <c r="W16" s="180"/>
     </row>
-    <row r="17" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="180"/>
-      <c r="B17" s="223"/>
-      <c r="C17" s="224"/>
-      <c r="D17" s="224"/>
-      <c r="E17" s="225"/>
+      <c r="B17" s="198"/>
+      <c r="C17" s="199"/>
+      <c r="D17" s="199"/>
+      <c r="E17" s="200"/>
       <c r="F17" s="180"/>
       <c r="G17" s="180"/>
       <c r="H17" s="180"/>
@@ -9440,12 +9406,12 @@
       <c r="V17" s="180"/>
       <c r="W17" s="180"/>
     </row>
-    <row r="18" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="180"/>
-      <c r="B18" s="223"/>
-      <c r="C18" s="224"/>
-      <c r="D18" s="224"/>
-      <c r="E18" s="225"/>
+      <c r="B18" s="198"/>
+      <c r="C18" s="199"/>
+      <c r="D18" s="199"/>
+      <c r="E18" s="200"/>
       <c r="F18" s="180"/>
       <c r="G18" s="180"/>
       <c r="H18" s="180"/>
@@ -9465,12 +9431,12 @@
       <c r="V18" s="180"/>
       <c r="W18" s="180"/>
     </row>
-    <row r="19" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="180"/>
-      <c r="B19" s="223"/>
-      <c r="C19" s="224"/>
-      <c r="D19" s="224"/>
-      <c r="E19" s="225"/>
+      <c r="B19" s="198"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="199"/>
+      <c r="E19" s="200"/>
       <c r="F19" s="180"/>
       <c r="G19" s="180"/>
       <c r="H19" s="180"/>
@@ -9490,12 +9456,12 @@
       <c r="V19" s="180"/>
       <c r="W19" s="180"/>
     </row>
-    <row r="20" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="180"/>
-      <c r="B20" s="223"/>
-      <c r="C20" s="224"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="225"/>
+      <c r="B20" s="198"/>
+      <c r="C20" s="199"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="200"/>
       <c r="F20" s="180"/>
       <c r="G20" s="180"/>
       <c r="H20" s="180"/>
@@ -9515,12 +9481,12 @@
       <c r="V20" s="180"/>
       <c r="W20" s="180"/>
     </row>
-    <row r="21" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="180"/>
-      <c r="B21" s="223"/>
-      <c r="C21" s="224"/>
-      <c r="D21" s="224"/>
-      <c r="E21" s="225"/>
+      <c r="B21" s="198"/>
+      <c r="C21" s="199"/>
+      <c r="D21" s="199"/>
+      <c r="E21" s="200"/>
       <c r="F21" s="180"/>
       <c r="G21" s="180"/>
       <c r="H21" s="180"/>
@@ -9540,12 +9506,12 @@
       <c r="V21" s="180"/>
       <c r="W21" s="180"/>
     </row>
-    <row r="22" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="180"/>
-      <c r="B22" s="223"/>
-      <c r="C22" s="224"/>
-      <c r="D22" s="224"/>
-      <c r="E22" s="225"/>
+      <c r="B22" s="198"/>
+      <c r="C22" s="199"/>
+      <c r="D22" s="199"/>
+      <c r="E22" s="200"/>
       <c r="F22" s="180"/>
       <c r="G22" s="180"/>
       <c r="H22" s="180"/>
@@ -9565,12 +9531,12 @@
       <c r="V22" s="180"/>
       <c r="W22" s="180"/>
     </row>
-    <row r="23" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="180"/>
-      <c r="B23" s="223"/>
-      <c r="C23" s="224"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="225"/>
+      <c r="B23" s="198"/>
+      <c r="C23" s="199"/>
+      <c r="D23" s="199"/>
+      <c r="E23" s="200"/>
       <c r="F23" s="180"/>
       <c r="G23" s="180"/>
       <c r="H23" s="180"/>
@@ -9590,12 +9556,12 @@
       <c r="V23" s="180"/>
       <c r="W23" s="180"/>
     </row>
-    <row r="24" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="180"/>
-      <c r="B24" s="223"/>
-      <c r="C24" s="224"/>
-      <c r="D24" s="224"/>
-      <c r="E24" s="225"/>
+      <c r="B24" s="198"/>
+      <c r="C24" s="199"/>
+      <c r="D24" s="199"/>
+      <c r="E24" s="200"/>
       <c r="F24" s="180"/>
       <c r="G24" s="180"/>
       <c r="H24" s="180"/>
@@ -9615,12 +9581,12 @@
       <c r="V24" s="180"/>
       <c r="W24" s="180"/>
     </row>
-    <row r="25" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="180"/>
-      <c r="B25" s="223"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="225"/>
+      <c r="B25" s="198"/>
+      <c r="C25" s="199"/>
+      <c r="D25" s="199"/>
+      <c r="E25" s="200"/>
       <c r="F25" s="180"/>
       <c r="G25" s="180"/>
       <c r="H25" s="180"/>
@@ -9640,16 +9606,16 @@
       <c r="V25" s="192"/>
       <c r="W25" s="192"/>
     </row>
-    <row r="26" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G26" s="206" t="s">
+    <row r="26" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="230" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="207"/>
-      <c r="I26" s="207"/>
-      <c r="J26" s="207"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="208"/>
-      <c r="M26" s="205"/>
+      <c r="H26" s="231"/>
+      <c r="I26" s="231"/>
+      <c r="J26" s="231"/>
+      <c r="K26" s="231"/>
+      <c r="L26" s="232"/>
+      <c r="M26" s="229"/>
       <c r="N26" s="193"/>
       <c r="O26" s="193"/>
       <c r="P26" s="193"/>
@@ -9661,367 +9627,371 @@
       <c r="V26" s="193"/>
       <c r="W26" s="193"/>
     </row>
-    <row r="27" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G27" s="209"/>
-      <c r="H27" s="210"/>
-      <c r="I27" s="210"/>
-      <c r="J27" s="210"/>
-      <c r="K27" s="210"/>
-      <c r="L27" s="211"/>
-      <c r="M27" s="205"/>
-    </row>
-    <row r="28" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:23" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G27" s="233"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="234"/>
+      <c r="J27" s="234"/>
+      <c r="K27" s="234"/>
+      <c r="L27" s="235"/>
+      <c r="M27" s="229"/>
+    </row>
+    <row r="28" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="T2:W4"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="G26:L27"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="Q2:S4"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="C1:M1"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:E7"/>
     <mergeCell ref="F6:F7"/>
@@ -10038,25 +10008,21 @@
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="T2:W4"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="G26:L27"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="Q2:S4"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="C1:M1"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="23" max="1048575" man="1"/>
   </colBreaks>
@@ -10067,136 +10033,136 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BD54"/>
-  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.84375" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="56" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" style="56" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" style="56" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="58" customWidth="1"/>
-    <col min="6" max="7" width="6.33203125" style="56" customWidth="1"/>
-    <col min="8" max="8" width="50.109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="57" customWidth="1"/>
-    <col min="10" max="10" width="24.44140625" style="57" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="57" customWidth="1"/>
-    <col min="12" max="13" width="15.5546875" style="57" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" style="57" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" style="57" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" style="57" customWidth="1"/>
+    <col min="1" max="1" width="5.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="17.07421875" style="56" customWidth="1"/>
+    <col min="3" max="3" width="53.69140625" style="56" customWidth="1"/>
+    <col min="4" max="4" width="10.07421875" style="57" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" style="58" customWidth="1"/>
+    <col min="6" max="7" width="6.3046875" style="56" customWidth="1"/>
+    <col min="8" max="8" width="50.07421875" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.69140625" style="57" customWidth="1"/>
+    <col min="10" max="10" width="24.4609375" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.69140625" style="57" customWidth="1"/>
+    <col min="12" max="13" width="15.53515625" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.07421875" style="57" customWidth="1"/>
+    <col min="15" max="15" width="12.84375" style="57" customWidth="1"/>
+    <col min="16" max="16" width="7.69140625" style="57" customWidth="1"/>
     <col min="17" max="17" width="6" style="57" customWidth="1"/>
-    <col min="18" max="18" width="6.109375" style="57" customWidth="1"/>
-    <col min="19" max="16384" width="3.88671875" style="57"/>
+    <col min="18" max="18" width="6.07421875" style="57" customWidth="1"/>
+    <col min="19" max="16384" width="3.84375" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="244"/>
       <c r="B1" s="244"/>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
-      <c r="G1" s="264"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="265" t="s">
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="265"/>
-      <c r="K1" s="265"/>
-      <c r="L1" s="265" t="s">
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="265"/>
-      <c r="N1" s="265"/>
-      <c r="O1" s="265" t="s">
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="265"/>
-      <c r="Q1" s="265"/>
-      <c r="R1" s="265"/>
-    </row>
-    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="246"/>
+      <c r="Q1" s="246"/>
+      <c r="R1" s="246"/>
+    </row>
+    <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="244"/>
       <c r="B2" s="244"/>
-      <c r="C2" s="264"/>
-      <c r="D2" s="264"/>
-      <c r="E2" s="264"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
-      <c r="H2" s="264"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="266"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="266"/>
-      <c r="N2" s="266"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="266"/>
-    </row>
-    <row r="3" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="245"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="M2" s="247"/>
+      <c r="N2" s="247"/>
+      <c r="O2" s="247"/>
+      <c r="P2" s="247"/>
+      <c r="Q2" s="247"/>
+      <c r="R2" s="247"/>
+    </row>
+    <row r="3" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="244"/>
       <c r="B3" s="244"/>
-      <c r="C3" s="264"/>
-      <c r="D3" s="264"/>
-      <c r="E3" s="264"/>
-      <c r="F3" s="264"/>
-      <c r="G3" s="264"/>
-      <c r="H3" s="264"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="266"/>
-      <c r="P3" s="266"/>
-      <c r="Q3" s="266"/>
-      <c r="R3" s="266"/>
-    </row>
-    <row r="4" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="249" t="s">
+      <c r="C3" s="245"/>
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="245"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="M3" s="247"/>
+      <c r="N3" s="247"/>
+      <c r="O3" s="247"/>
+      <c r="P3" s="247"/>
+      <c r="Q3" s="247"/>
+      <c r="R3" s="247"/>
+    </row>
+    <row r="4" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="250" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="249"/>
-      <c r="C4" s="249"/>
+      <c r="B4" s="250"/>
+      <c r="C4" s="250"/>
       <c r="D4" s="60"/>
-      <c r="F4" s="259" t="s">
+      <c r="F4" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="260"/>
-      <c r="H4" s="263" t="s">
+      <c r="G4" s="261"/>
+      <c r="H4" s="264" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="247" t="s">
+      <c r="I4" s="248" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="248"/>
-      <c r="K4" s="247" t="s">
+      <c r="J4" s="249"/>
+      <c r="K4" s="248" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="248"/>
-      <c r="M4" s="247" t="s">
+      <c r="L4" s="249"/>
+      <c r="M4" s="248" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="248"/>
+      <c r="N4" s="249"/>
       <c r="O4" s="57" t="s">
         <v>30</v>
       </c>
       <c r="R4" s="68"/>
     </row>
-    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="249" t="s">
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="250" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="249"/>
-      <c r="C5" s="249"/>
+      <c r="B5" s="250"/>
+      <c r="C5" s="250"/>
       <c r="D5" s="60"/>
-      <c r="F5" s="261"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="263"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="263"/>
+      <c r="H5" s="264"/>
       <c r="I5" s="61"/>
       <c r="J5" s="62"/>
       <c r="K5" s="63"/>
@@ -10208,17 +10174,17 @@
       <c r="P5" s="67"/>
       <c r="R5" s="68"/>
     </row>
-    <row r="6" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="249"/>
-      <c r="B6" s="249"/>
-      <c r="C6" s="249"/>
+    <row r="6" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="250"/>
+      <c r="B6" s="250"/>
+      <c r="C6" s="250"/>
       <c r="D6" s="196" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="70"/>
       <c r="F6" s="71"/>
       <c r="G6" s="72"/>
-      <c r="H6" s="250" t="s">
+      <c r="H6" s="251" t="s">
         <v>34</v>
       </c>
       <c r="I6" s="69" t="s">
@@ -10235,17 +10201,17 @@
       </c>
       <c r="R6" s="68"/>
     </row>
-    <row r="7" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="251" t="s">
+    <row r="7" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="252"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="257"/>
-      <c r="E7" s="258"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="258"/>
+      <c r="E7" s="259"/>
       <c r="F7" s="75"/>
       <c r="G7" s="76"/>
-      <c r="H7" s="250"/>
+      <c r="H7" s="251"/>
       <c r="I7" s="61"/>
       <c r="J7" s="77"/>
       <c r="K7" s="78"/>
@@ -10261,10 +10227,10 @@
       </c>
       <c r="R7" s="68"/>
     </row>
-    <row r="8" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="254"/>
-      <c r="B8" s="255"/>
-      <c r="C8" s="256"/>
+    <row r="8" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="255"/>
+      <c r="B8" s="256"/>
+      <c r="C8" s="257"/>
       <c r="D8" s="83"/>
       <c r="E8" s="84" t="s">
         <v>39</v>
@@ -10289,14 +10255,14 @@
       <c r="Q8" s="89"/>
       <c r="R8" s="90"/>
     </row>
-    <row r="9" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="245" t="s">
+      <c r="B9" s="265" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="246"/>
+      <c r="C9" s="266"/>
       <c r="D9" s="92" t="s">
         <v>45</v>
       </c>
@@ -10311,7 +10277,7 @@
       </c>
       <c r="R9" s="68"/>
     </row>
-    <row r="10" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="83">
         <v>1</v>
       </c>
@@ -10326,7 +10292,7 @@
       </c>
       <c r="R10" s="68"/>
     </row>
-    <row r="11" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="83">
         <v>2</v>
       </c>
@@ -10342,7 +10308,7 @@
       </c>
       <c r="R11" s="68"/>
     </row>
-    <row r="12" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="83">
         <v>3</v>
       </c>
@@ -10358,7 +10324,7 @@
       </c>
       <c r="R12" s="68"/>
     </row>
-    <row r="13" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="83">
         <v>4</v>
       </c>
@@ -10374,7 +10340,7 @@
       </c>
       <c r="R13" s="68"/>
     </row>
-    <row r="14" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="83">
         <v>5</v>
       </c>
@@ -10390,7 +10356,7 @@
       </c>
       <c r="R14" s="68"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="83">
         <v>6</v>
       </c>
@@ -10406,7 +10372,7 @@
       </c>
       <c r="R15" s="68"/>
     </row>
-    <row r="16" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="83">
         <v>7</v>
       </c>
@@ -10422,7 +10388,7 @@
       </c>
       <c r="R16" s="68"/>
     </row>
-    <row r="17" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="83">
         <v>8</v>
       </c>
@@ -10438,7 +10404,7 @@
       </c>
       <c r="R17" s="68"/>
     </row>
-    <row r="18" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="83">
         <v>9</v>
       </c>
@@ -10454,7 +10420,7 @@
       </c>
       <c r="R18" s="68"/>
     </row>
-    <row r="19" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="83">
         <v>10</v>
       </c>
@@ -10470,7 +10436,7 @@
       </c>
       <c r="R19" s="68"/>
     </row>
-    <row r="20" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="83">
         <v>11</v>
       </c>
@@ -10486,7 +10452,7 @@
       </c>
       <c r="R20" s="68"/>
     </row>
-    <row r="21" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="83">
         <v>12</v>
       </c>
@@ -10502,7 +10468,7 @@
       </c>
       <c r="R21" s="68"/>
     </row>
-    <row r="22" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="83">
         <v>13</v>
       </c>
@@ -10518,7 +10484,7 @@
       </c>
       <c r="R22" s="68"/>
     </row>
-    <row r="23" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="83">
         <v>14</v>
       </c>
@@ -10534,7 +10500,7 @@
       </c>
       <c r="R23" s="68"/>
     </row>
-    <row r="24" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="83">
         <v>15</v>
       </c>
@@ -10550,7 +10516,7 @@
       </c>
       <c r="R24" s="68"/>
     </row>
-    <row r="25" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="83">
         <v>16</v>
       </c>
@@ -10566,7 +10532,7 @@
       </c>
       <c r="R25" s="68"/>
     </row>
-    <row r="26" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="83">
         <v>17</v>
       </c>
@@ -10582,7 +10548,7 @@
       </c>
       <c r="R26" s="68"/>
     </row>
-    <row r="27" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="83">
         <v>18</v>
       </c>
@@ -10598,7 +10564,7 @@
       </c>
       <c r="R27" s="68"/>
     </row>
-    <row r="28" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="83">
         <v>19</v>
       </c>
@@ -10614,7 +10580,7 @@
       </c>
       <c r="R28" s="68"/>
     </row>
-    <row r="29" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="83">
         <v>20</v>
       </c>
@@ -10630,7 +10596,7 @@
       </c>
       <c r="R29" s="68"/>
     </row>
-    <row r="30" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="83">
         <v>21</v>
       </c>
@@ -10646,7 +10612,7 @@
       </c>
       <c r="R30" s="68"/>
     </row>
-    <row r="31" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="83">
         <v>22</v>
       </c>
@@ -10662,7 +10628,7 @@
       </c>
       <c r="R31" s="68"/>
     </row>
-    <row r="32" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="83">
         <v>23</v>
       </c>
@@ -10678,7 +10644,7 @@
       </c>
       <c r="R32" s="68"/>
     </row>
-    <row r="33" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="83">
         <v>24</v>
       </c>
@@ -10694,7 +10660,7 @@
       </c>
       <c r="R33" s="68"/>
     </row>
-    <row r="34" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="83">
         <v>25</v>
       </c>
@@ -10710,7 +10676,7 @@
       </c>
       <c r="R34" s="68"/>
     </row>
-    <row r="35" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="83">
         <v>26</v>
       </c>
@@ -10726,7 +10692,7 @@
       </c>
       <c r="R35" s="68"/>
     </row>
-    <row r="36" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="83">
         <v>27</v>
       </c>
@@ -10742,7 +10708,7 @@
       </c>
       <c r="R36" s="68"/>
     </row>
-    <row r="37" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="83">
         <v>28</v>
       </c>
@@ -10758,7 +10724,7 @@
       </c>
       <c r="R37" s="68"/>
     </row>
-    <row r="38" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="83">
         <v>29</v>
       </c>
@@ -10774,7 +10740,7 @@
       </c>
       <c r="R38" s="68"/>
     </row>
-    <row r="39" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="83">
         <v>30</v>
       </c>
@@ -10790,7 +10756,7 @@
       </c>
       <c r="R39" s="68"/>
     </row>
-    <row r="40" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="99"/>
       <c r="B40" s="197"/>
       <c r="C40" s="100"/>
@@ -10801,7 +10767,7 @@
       <c r="H40" s="101"/>
       <c r="R40" s="68"/>
     </row>
-    <row r="41" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="59"/>
       <c r="D41" s="97"/>
       <c r="E41" s="93">
@@ -10820,7 +10786,7 @@
       <c r="K41" s="103"/>
       <c r="R41" s="68"/>
     </row>
-    <row r="42" spans="1:18" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="104"/>
       <c r="B42" s="105"/>
       <c r="C42" s="105"/>
@@ -10847,13 +10813,13 @@
       <c r="Q42" s="110"/>
       <c r="R42" s="112"/>
     </row>
-    <row r="43" spans="1:18" ht="32.4" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:56" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="32.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:56" s="58" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="56"/>
       <c r="B50" s="56"/>
       <c r="C50" s="56"/>
@@ -10910,7 +10876,7 @@
       <c r="BC50" s="57"/>
       <c r="BD50" s="57"/>
     </row>
-    <row r="51" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="56"/>
       <c r="B51" s="56"/>
       <c r="C51" s="113"/>
@@ -10967,7 +10933,7 @@
       <c r="BC51" s="57"/>
       <c r="BD51" s="57"/>
     </row>
-    <row r="52" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="56"/>
       <c r="B52" s="56"/>
       <c r="C52" s="113"/>
@@ -11024,7 +10990,7 @@
       <c r="BC52" s="57"/>
       <c r="BD52" s="57"/>
     </row>
-    <row r="53" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:56" s="58" customFormat="1" ht="27.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="56"/>
       <c r="B53" s="56"/>
       <c r="C53" s="113"/>
@@ -11081,7 +11047,7 @@
       <c r="BC53" s="57"/>
       <c r="BD53" s="57"/>
     </row>
-    <row r="54" spans="1:56" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:56" s="58" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="56"/>
       <c r="B54" s="56"/>
       <c r="C54" s="113"/>
@@ -11140,24 +11106,25 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:H3"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="L2:N3"/>
-    <mergeCell ref="O2:R3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="F4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
@@ -11170,25 +11137,24 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="F4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:H3"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="L2:N3"/>
+    <mergeCell ref="O2:R3"/>
   </mergeCells>
   <conditionalFormatting sqref="F41">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
@@ -11208,346 +11174,346 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:AY47"/>
-  <sheetFormatPr defaultColWidth="5.44140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="5.4609375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.85"/>
   <cols>
-    <col min="1" max="37" width="5.6640625" style="166" customWidth="1"/>
-    <col min="38" max="38" width="5.6640625" style="165" customWidth="1"/>
-    <col min="39" max="40" width="5.44140625" style="165" customWidth="1"/>
-    <col min="41" max="257" width="5.44140625" style="166"/>
-    <col min="258" max="258" width="13.44140625" style="166" customWidth="1"/>
-    <col min="259" max="296" width="5.44140625" style="166" customWidth="1"/>
-    <col min="297" max="513" width="5.44140625" style="166"/>
-    <col min="514" max="514" width="13.44140625" style="166" customWidth="1"/>
-    <col min="515" max="552" width="5.44140625" style="166" customWidth="1"/>
-    <col min="553" max="769" width="5.44140625" style="166"/>
-    <col min="770" max="770" width="13.44140625" style="166" customWidth="1"/>
-    <col min="771" max="808" width="5.44140625" style="166" customWidth="1"/>
-    <col min="809" max="1025" width="5.44140625" style="166"/>
-    <col min="1026" max="1026" width="13.44140625" style="166" customWidth="1"/>
-    <col min="1027" max="1064" width="5.44140625" style="166" customWidth="1"/>
-    <col min="1065" max="1281" width="5.44140625" style="166"/>
-    <col min="1282" max="1282" width="13.44140625" style="166" customWidth="1"/>
-    <col min="1283" max="1320" width="5.44140625" style="166" customWidth="1"/>
-    <col min="1321" max="1537" width="5.44140625" style="166"/>
-    <col min="1538" max="1538" width="13.44140625" style="166" customWidth="1"/>
-    <col min="1539" max="1576" width="5.44140625" style="166" customWidth="1"/>
-    <col min="1577" max="1793" width="5.44140625" style="166"/>
-    <col min="1794" max="1794" width="13.44140625" style="166" customWidth="1"/>
-    <col min="1795" max="1832" width="5.44140625" style="166" customWidth="1"/>
-    <col min="1833" max="2049" width="5.44140625" style="166"/>
-    <col min="2050" max="2050" width="13.44140625" style="166" customWidth="1"/>
-    <col min="2051" max="2088" width="5.44140625" style="166" customWidth="1"/>
-    <col min="2089" max="2305" width="5.44140625" style="166"/>
-    <col min="2306" max="2306" width="13.44140625" style="166" customWidth="1"/>
-    <col min="2307" max="2344" width="5.44140625" style="166" customWidth="1"/>
-    <col min="2345" max="2561" width="5.44140625" style="166"/>
-    <col min="2562" max="2562" width="13.44140625" style="166" customWidth="1"/>
-    <col min="2563" max="2600" width="5.44140625" style="166" customWidth="1"/>
-    <col min="2601" max="2817" width="5.44140625" style="166"/>
-    <col min="2818" max="2818" width="13.44140625" style="166" customWidth="1"/>
-    <col min="2819" max="2856" width="5.44140625" style="166" customWidth="1"/>
-    <col min="2857" max="3073" width="5.44140625" style="166"/>
-    <col min="3074" max="3074" width="13.44140625" style="166" customWidth="1"/>
-    <col min="3075" max="3112" width="5.44140625" style="166" customWidth="1"/>
-    <col min="3113" max="3329" width="5.44140625" style="166"/>
-    <col min="3330" max="3330" width="13.44140625" style="166" customWidth="1"/>
-    <col min="3331" max="3368" width="5.44140625" style="166" customWidth="1"/>
-    <col min="3369" max="3585" width="5.44140625" style="166"/>
-    <col min="3586" max="3586" width="13.44140625" style="166" customWidth="1"/>
-    <col min="3587" max="3624" width="5.44140625" style="166" customWidth="1"/>
-    <col min="3625" max="3841" width="5.44140625" style="166"/>
-    <col min="3842" max="3842" width="13.44140625" style="166" customWidth="1"/>
-    <col min="3843" max="3880" width="5.44140625" style="166" customWidth="1"/>
-    <col min="3881" max="4097" width="5.44140625" style="166"/>
-    <col min="4098" max="4098" width="13.44140625" style="166" customWidth="1"/>
-    <col min="4099" max="4136" width="5.44140625" style="166" customWidth="1"/>
-    <col min="4137" max="4353" width="5.44140625" style="166"/>
-    <col min="4354" max="4354" width="13.44140625" style="166" customWidth="1"/>
-    <col min="4355" max="4392" width="5.44140625" style="166" customWidth="1"/>
-    <col min="4393" max="4609" width="5.44140625" style="166"/>
-    <col min="4610" max="4610" width="13.44140625" style="166" customWidth="1"/>
-    <col min="4611" max="4648" width="5.44140625" style="166" customWidth="1"/>
-    <col min="4649" max="4865" width="5.44140625" style="166"/>
-    <col min="4866" max="4866" width="13.44140625" style="166" customWidth="1"/>
-    <col min="4867" max="4904" width="5.44140625" style="166" customWidth="1"/>
-    <col min="4905" max="5121" width="5.44140625" style="166"/>
-    <col min="5122" max="5122" width="13.44140625" style="166" customWidth="1"/>
-    <col min="5123" max="5160" width="5.44140625" style="166" customWidth="1"/>
-    <col min="5161" max="5377" width="5.44140625" style="166"/>
-    <col min="5378" max="5378" width="13.44140625" style="166" customWidth="1"/>
-    <col min="5379" max="5416" width="5.44140625" style="166" customWidth="1"/>
-    <col min="5417" max="5633" width="5.44140625" style="166"/>
-    <col min="5634" max="5634" width="13.44140625" style="166" customWidth="1"/>
-    <col min="5635" max="5672" width="5.44140625" style="166" customWidth="1"/>
-    <col min="5673" max="5889" width="5.44140625" style="166"/>
-    <col min="5890" max="5890" width="13.44140625" style="166" customWidth="1"/>
-    <col min="5891" max="5928" width="5.44140625" style="166" customWidth="1"/>
-    <col min="5929" max="6145" width="5.44140625" style="166"/>
-    <col min="6146" max="6146" width="13.44140625" style="166" customWidth="1"/>
-    <col min="6147" max="6184" width="5.44140625" style="166" customWidth="1"/>
-    <col min="6185" max="6401" width="5.44140625" style="166"/>
-    <col min="6402" max="6402" width="13.44140625" style="166" customWidth="1"/>
-    <col min="6403" max="6440" width="5.44140625" style="166" customWidth="1"/>
-    <col min="6441" max="6657" width="5.44140625" style="166"/>
-    <col min="6658" max="6658" width="13.44140625" style="166" customWidth="1"/>
-    <col min="6659" max="6696" width="5.44140625" style="166" customWidth="1"/>
-    <col min="6697" max="6913" width="5.44140625" style="166"/>
-    <col min="6914" max="6914" width="13.44140625" style="166" customWidth="1"/>
-    <col min="6915" max="6952" width="5.44140625" style="166" customWidth="1"/>
-    <col min="6953" max="7169" width="5.44140625" style="166"/>
-    <col min="7170" max="7170" width="13.44140625" style="166" customWidth="1"/>
-    <col min="7171" max="7208" width="5.44140625" style="166" customWidth="1"/>
-    <col min="7209" max="7425" width="5.44140625" style="166"/>
-    <col min="7426" max="7426" width="13.44140625" style="166" customWidth="1"/>
-    <col min="7427" max="7464" width="5.44140625" style="166" customWidth="1"/>
-    <col min="7465" max="7681" width="5.44140625" style="166"/>
-    <col min="7682" max="7682" width="13.44140625" style="166" customWidth="1"/>
-    <col min="7683" max="7720" width="5.44140625" style="166" customWidth="1"/>
-    <col min="7721" max="7937" width="5.44140625" style="166"/>
-    <col min="7938" max="7938" width="13.44140625" style="166" customWidth="1"/>
-    <col min="7939" max="7976" width="5.44140625" style="166" customWidth="1"/>
-    <col min="7977" max="8193" width="5.44140625" style="166"/>
-    <col min="8194" max="8194" width="13.44140625" style="166" customWidth="1"/>
-    <col min="8195" max="8232" width="5.44140625" style="166" customWidth="1"/>
-    <col min="8233" max="8449" width="5.44140625" style="166"/>
-    <col min="8450" max="8450" width="13.44140625" style="166" customWidth="1"/>
-    <col min="8451" max="8488" width="5.44140625" style="166" customWidth="1"/>
-    <col min="8489" max="8705" width="5.44140625" style="166"/>
-    <col min="8706" max="8706" width="13.44140625" style="166" customWidth="1"/>
-    <col min="8707" max="8744" width="5.44140625" style="166" customWidth="1"/>
-    <col min="8745" max="8961" width="5.44140625" style="166"/>
-    <col min="8962" max="8962" width="13.44140625" style="166" customWidth="1"/>
-    <col min="8963" max="9000" width="5.44140625" style="166" customWidth="1"/>
-    <col min="9001" max="9217" width="5.44140625" style="166"/>
-    <col min="9218" max="9218" width="13.44140625" style="166" customWidth="1"/>
-    <col min="9219" max="9256" width="5.44140625" style="166" customWidth="1"/>
-    <col min="9257" max="9473" width="5.44140625" style="166"/>
-    <col min="9474" max="9474" width="13.44140625" style="166" customWidth="1"/>
-    <col min="9475" max="9512" width="5.44140625" style="166" customWidth="1"/>
-    <col min="9513" max="9729" width="5.44140625" style="166"/>
-    <col min="9730" max="9730" width="13.44140625" style="166" customWidth="1"/>
-    <col min="9731" max="9768" width="5.44140625" style="166" customWidth="1"/>
-    <col min="9769" max="9985" width="5.44140625" style="166"/>
-    <col min="9986" max="9986" width="13.44140625" style="166" customWidth="1"/>
-    <col min="9987" max="10024" width="5.44140625" style="166" customWidth="1"/>
-    <col min="10025" max="10241" width="5.44140625" style="166"/>
-    <col min="10242" max="10242" width="13.44140625" style="166" customWidth="1"/>
-    <col min="10243" max="10280" width="5.44140625" style="166" customWidth="1"/>
-    <col min="10281" max="10497" width="5.44140625" style="166"/>
-    <col min="10498" max="10498" width="13.44140625" style="166" customWidth="1"/>
-    <col min="10499" max="10536" width="5.44140625" style="166" customWidth="1"/>
-    <col min="10537" max="10753" width="5.44140625" style="166"/>
-    <col min="10754" max="10754" width="13.44140625" style="166" customWidth="1"/>
-    <col min="10755" max="10792" width="5.44140625" style="166" customWidth="1"/>
-    <col min="10793" max="11009" width="5.44140625" style="166"/>
-    <col min="11010" max="11010" width="13.44140625" style="166" customWidth="1"/>
-    <col min="11011" max="11048" width="5.44140625" style="166" customWidth="1"/>
-    <col min="11049" max="11265" width="5.44140625" style="166"/>
-    <col min="11266" max="11266" width="13.44140625" style="166" customWidth="1"/>
-    <col min="11267" max="11304" width="5.44140625" style="166" customWidth="1"/>
-    <col min="11305" max="11521" width="5.44140625" style="166"/>
-    <col min="11522" max="11522" width="13.44140625" style="166" customWidth="1"/>
-    <col min="11523" max="11560" width="5.44140625" style="166" customWidth="1"/>
-    <col min="11561" max="11777" width="5.44140625" style="166"/>
-    <col min="11778" max="11778" width="13.44140625" style="166" customWidth="1"/>
-    <col min="11779" max="11816" width="5.44140625" style="166" customWidth="1"/>
-    <col min="11817" max="12033" width="5.44140625" style="166"/>
-    <col min="12034" max="12034" width="13.44140625" style="166" customWidth="1"/>
-    <col min="12035" max="12072" width="5.44140625" style="166" customWidth="1"/>
-    <col min="12073" max="12289" width="5.44140625" style="166"/>
-    <col min="12290" max="12290" width="13.44140625" style="166" customWidth="1"/>
-    <col min="12291" max="12328" width="5.44140625" style="166" customWidth="1"/>
-    <col min="12329" max="12545" width="5.44140625" style="166"/>
-    <col min="12546" max="12546" width="13.44140625" style="166" customWidth="1"/>
-    <col min="12547" max="12584" width="5.44140625" style="166" customWidth="1"/>
-    <col min="12585" max="12801" width="5.44140625" style="166"/>
-    <col min="12802" max="12802" width="13.44140625" style="166" customWidth="1"/>
-    <col min="12803" max="12840" width="5.44140625" style="166" customWidth="1"/>
-    <col min="12841" max="13057" width="5.44140625" style="166"/>
-    <col min="13058" max="13058" width="13.44140625" style="166" customWidth="1"/>
-    <col min="13059" max="13096" width="5.44140625" style="166" customWidth="1"/>
-    <col min="13097" max="13313" width="5.44140625" style="166"/>
-    <col min="13314" max="13314" width="13.44140625" style="166" customWidth="1"/>
-    <col min="13315" max="13352" width="5.44140625" style="166" customWidth="1"/>
-    <col min="13353" max="13569" width="5.44140625" style="166"/>
-    <col min="13570" max="13570" width="13.44140625" style="166" customWidth="1"/>
-    <col min="13571" max="13608" width="5.44140625" style="166" customWidth="1"/>
-    <col min="13609" max="13825" width="5.44140625" style="166"/>
-    <col min="13826" max="13826" width="13.44140625" style="166" customWidth="1"/>
-    <col min="13827" max="13864" width="5.44140625" style="166" customWidth="1"/>
-    <col min="13865" max="14081" width="5.44140625" style="166"/>
-    <col min="14082" max="14082" width="13.44140625" style="166" customWidth="1"/>
-    <col min="14083" max="14120" width="5.44140625" style="166" customWidth="1"/>
-    <col min="14121" max="14337" width="5.44140625" style="166"/>
-    <col min="14338" max="14338" width="13.44140625" style="166" customWidth="1"/>
-    <col min="14339" max="14376" width="5.44140625" style="166" customWidth="1"/>
-    <col min="14377" max="14593" width="5.44140625" style="166"/>
-    <col min="14594" max="14594" width="13.44140625" style="166" customWidth="1"/>
-    <col min="14595" max="14632" width="5.44140625" style="166" customWidth="1"/>
-    <col min="14633" max="14849" width="5.44140625" style="166"/>
-    <col min="14850" max="14850" width="13.44140625" style="166" customWidth="1"/>
-    <col min="14851" max="14888" width="5.44140625" style="166" customWidth="1"/>
-    <col min="14889" max="15105" width="5.44140625" style="166"/>
-    <col min="15106" max="15106" width="13.44140625" style="166" customWidth="1"/>
-    <col min="15107" max="15144" width="5.44140625" style="166" customWidth="1"/>
-    <col min="15145" max="15361" width="5.44140625" style="166"/>
-    <col min="15362" max="15362" width="13.44140625" style="166" customWidth="1"/>
-    <col min="15363" max="15400" width="5.44140625" style="166" customWidth="1"/>
-    <col min="15401" max="15617" width="5.44140625" style="166"/>
-    <col min="15618" max="15618" width="13.44140625" style="166" customWidth="1"/>
-    <col min="15619" max="15656" width="5.44140625" style="166" customWidth="1"/>
-    <col min="15657" max="15873" width="5.44140625" style="166"/>
-    <col min="15874" max="15874" width="13.44140625" style="166" customWidth="1"/>
-    <col min="15875" max="15912" width="5.44140625" style="166" customWidth="1"/>
-    <col min="15913" max="16129" width="5.44140625" style="166"/>
-    <col min="16130" max="16130" width="13.44140625" style="166" customWidth="1"/>
-    <col min="16131" max="16168" width="5.44140625" style="166" customWidth="1"/>
-    <col min="16169" max="16384" width="5.44140625" style="166"/>
+    <col min="1" max="37" width="5.69140625" style="166" customWidth="1"/>
+    <col min="38" max="38" width="5.69140625" style="165" customWidth="1"/>
+    <col min="39" max="40" width="5.4609375" style="165" customWidth="1"/>
+    <col min="41" max="257" width="5.4609375" style="166"/>
+    <col min="258" max="258" width="13.4609375" style="166" customWidth="1"/>
+    <col min="259" max="296" width="5.4609375" style="166" customWidth="1"/>
+    <col min="297" max="513" width="5.4609375" style="166"/>
+    <col min="514" max="514" width="13.4609375" style="166" customWidth="1"/>
+    <col min="515" max="552" width="5.4609375" style="166" customWidth="1"/>
+    <col min="553" max="769" width="5.4609375" style="166"/>
+    <col min="770" max="770" width="13.4609375" style="166" customWidth="1"/>
+    <col min="771" max="808" width="5.4609375" style="166" customWidth="1"/>
+    <col min="809" max="1025" width="5.4609375" style="166"/>
+    <col min="1026" max="1026" width="13.4609375" style="166" customWidth="1"/>
+    <col min="1027" max="1064" width="5.4609375" style="166" customWidth="1"/>
+    <col min="1065" max="1281" width="5.4609375" style="166"/>
+    <col min="1282" max="1282" width="13.4609375" style="166" customWidth="1"/>
+    <col min="1283" max="1320" width="5.4609375" style="166" customWidth="1"/>
+    <col min="1321" max="1537" width="5.4609375" style="166"/>
+    <col min="1538" max="1538" width="13.4609375" style="166" customWidth="1"/>
+    <col min="1539" max="1576" width="5.4609375" style="166" customWidth="1"/>
+    <col min="1577" max="1793" width="5.4609375" style="166"/>
+    <col min="1794" max="1794" width="13.4609375" style="166" customWidth="1"/>
+    <col min="1795" max="1832" width="5.4609375" style="166" customWidth="1"/>
+    <col min="1833" max="2049" width="5.4609375" style="166"/>
+    <col min="2050" max="2050" width="13.4609375" style="166" customWidth="1"/>
+    <col min="2051" max="2088" width="5.4609375" style="166" customWidth="1"/>
+    <col min="2089" max="2305" width="5.4609375" style="166"/>
+    <col min="2306" max="2306" width="13.4609375" style="166" customWidth="1"/>
+    <col min="2307" max="2344" width="5.4609375" style="166" customWidth="1"/>
+    <col min="2345" max="2561" width="5.4609375" style="166"/>
+    <col min="2562" max="2562" width="13.4609375" style="166" customWidth="1"/>
+    <col min="2563" max="2600" width="5.4609375" style="166" customWidth="1"/>
+    <col min="2601" max="2817" width="5.4609375" style="166"/>
+    <col min="2818" max="2818" width="13.4609375" style="166" customWidth="1"/>
+    <col min="2819" max="2856" width="5.4609375" style="166" customWidth="1"/>
+    <col min="2857" max="3073" width="5.4609375" style="166"/>
+    <col min="3074" max="3074" width="13.4609375" style="166" customWidth="1"/>
+    <col min="3075" max="3112" width="5.4609375" style="166" customWidth="1"/>
+    <col min="3113" max="3329" width="5.4609375" style="166"/>
+    <col min="3330" max="3330" width="13.4609375" style="166" customWidth="1"/>
+    <col min="3331" max="3368" width="5.4609375" style="166" customWidth="1"/>
+    <col min="3369" max="3585" width="5.4609375" style="166"/>
+    <col min="3586" max="3586" width="13.4609375" style="166" customWidth="1"/>
+    <col min="3587" max="3624" width="5.4609375" style="166" customWidth="1"/>
+    <col min="3625" max="3841" width="5.4609375" style="166"/>
+    <col min="3842" max="3842" width="13.4609375" style="166" customWidth="1"/>
+    <col min="3843" max="3880" width="5.4609375" style="166" customWidth="1"/>
+    <col min="3881" max="4097" width="5.4609375" style="166"/>
+    <col min="4098" max="4098" width="13.4609375" style="166" customWidth="1"/>
+    <col min="4099" max="4136" width="5.4609375" style="166" customWidth="1"/>
+    <col min="4137" max="4353" width="5.4609375" style="166"/>
+    <col min="4354" max="4354" width="13.4609375" style="166" customWidth="1"/>
+    <col min="4355" max="4392" width="5.4609375" style="166" customWidth="1"/>
+    <col min="4393" max="4609" width="5.4609375" style="166"/>
+    <col min="4610" max="4610" width="13.4609375" style="166" customWidth="1"/>
+    <col min="4611" max="4648" width="5.4609375" style="166" customWidth="1"/>
+    <col min="4649" max="4865" width="5.4609375" style="166"/>
+    <col min="4866" max="4866" width="13.4609375" style="166" customWidth="1"/>
+    <col min="4867" max="4904" width="5.4609375" style="166" customWidth="1"/>
+    <col min="4905" max="5121" width="5.4609375" style="166"/>
+    <col min="5122" max="5122" width="13.4609375" style="166" customWidth="1"/>
+    <col min="5123" max="5160" width="5.4609375" style="166" customWidth="1"/>
+    <col min="5161" max="5377" width="5.4609375" style="166"/>
+    <col min="5378" max="5378" width="13.4609375" style="166" customWidth="1"/>
+    <col min="5379" max="5416" width="5.4609375" style="166" customWidth="1"/>
+    <col min="5417" max="5633" width="5.4609375" style="166"/>
+    <col min="5634" max="5634" width="13.4609375" style="166" customWidth="1"/>
+    <col min="5635" max="5672" width="5.4609375" style="166" customWidth="1"/>
+    <col min="5673" max="5889" width="5.4609375" style="166"/>
+    <col min="5890" max="5890" width="13.4609375" style="166" customWidth="1"/>
+    <col min="5891" max="5928" width="5.4609375" style="166" customWidth="1"/>
+    <col min="5929" max="6145" width="5.4609375" style="166"/>
+    <col min="6146" max="6146" width="13.4609375" style="166" customWidth="1"/>
+    <col min="6147" max="6184" width="5.4609375" style="166" customWidth="1"/>
+    <col min="6185" max="6401" width="5.4609375" style="166"/>
+    <col min="6402" max="6402" width="13.4609375" style="166" customWidth="1"/>
+    <col min="6403" max="6440" width="5.4609375" style="166" customWidth="1"/>
+    <col min="6441" max="6657" width="5.4609375" style="166"/>
+    <col min="6658" max="6658" width="13.4609375" style="166" customWidth="1"/>
+    <col min="6659" max="6696" width="5.4609375" style="166" customWidth="1"/>
+    <col min="6697" max="6913" width="5.4609375" style="166"/>
+    <col min="6914" max="6914" width="13.4609375" style="166" customWidth="1"/>
+    <col min="6915" max="6952" width="5.4609375" style="166" customWidth="1"/>
+    <col min="6953" max="7169" width="5.4609375" style="166"/>
+    <col min="7170" max="7170" width="13.4609375" style="166" customWidth="1"/>
+    <col min="7171" max="7208" width="5.4609375" style="166" customWidth="1"/>
+    <col min="7209" max="7425" width="5.4609375" style="166"/>
+    <col min="7426" max="7426" width="13.4609375" style="166" customWidth="1"/>
+    <col min="7427" max="7464" width="5.4609375" style="166" customWidth="1"/>
+    <col min="7465" max="7681" width="5.4609375" style="166"/>
+    <col min="7682" max="7682" width="13.4609375" style="166" customWidth="1"/>
+    <col min="7683" max="7720" width="5.4609375" style="166" customWidth="1"/>
+    <col min="7721" max="7937" width="5.4609375" style="166"/>
+    <col min="7938" max="7938" width="13.4609375" style="166" customWidth="1"/>
+    <col min="7939" max="7976" width="5.4609375" style="166" customWidth="1"/>
+    <col min="7977" max="8193" width="5.4609375" style="166"/>
+    <col min="8194" max="8194" width="13.4609375" style="166" customWidth="1"/>
+    <col min="8195" max="8232" width="5.4609375" style="166" customWidth="1"/>
+    <col min="8233" max="8449" width="5.4609375" style="166"/>
+    <col min="8450" max="8450" width="13.4609375" style="166" customWidth="1"/>
+    <col min="8451" max="8488" width="5.4609375" style="166" customWidth="1"/>
+    <col min="8489" max="8705" width="5.4609375" style="166"/>
+    <col min="8706" max="8706" width="13.4609375" style="166" customWidth="1"/>
+    <col min="8707" max="8744" width="5.4609375" style="166" customWidth="1"/>
+    <col min="8745" max="8961" width="5.4609375" style="166"/>
+    <col min="8962" max="8962" width="13.4609375" style="166" customWidth="1"/>
+    <col min="8963" max="9000" width="5.4609375" style="166" customWidth="1"/>
+    <col min="9001" max="9217" width="5.4609375" style="166"/>
+    <col min="9218" max="9218" width="13.4609375" style="166" customWidth="1"/>
+    <col min="9219" max="9256" width="5.4609375" style="166" customWidth="1"/>
+    <col min="9257" max="9473" width="5.4609375" style="166"/>
+    <col min="9474" max="9474" width="13.4609375" style="166" customWidth="1"/>
+    <col min="9475" max="9512" width="5.4609375" style="166" customWidth="1"/>
+    <col min="9513" max="9729" width="5.4609375" style="166"/>
+    <col min="9730" max="9730" width="13.4609375" style="166" customWidth="1"/>
+    <col min="9731" max="9768" width="5.4609375" style="166" customWidth="1"/>
+    <col min="9769" max="9985" width="5.4609375" style="166"/>
+    <col min="9986" max="9986" width="13.4609375" style="166" customWidth="1"/>
+    <col min="9987" max="10024" width="5.4609375" style="166" customWidth="1"/>
+    <col min="10025" max="10241" width="5.4609375" style="166"/>
+    <col min="10242" max="10242" width="13.4609375" style="166" customWidth="1"/>
+    <col min="10243" max="10280" width="5.4609375" style="166" customWidth="1"/>
+    <col min="10281" max="10497" width="5.4609375" style="166"/>
+    <col min="10498" max="10498" width="13.4609375" style="166" customWidth="1"/>
+    <col min="10499" max="10536" width="5.4609375" style="166" customWidth="1"/>
+    <col min="10537" max="10753" width="5.4609375" style="166"/>
+    <col min="10754" max="10754" width="13.4609375" style="166" customWidth="1"/>
+    <col min="10755" max="10792" width="5.4609375" style="166" customWidth="1"/>
+    <col min="10793" max="11009" width="5.4609375" style="166"/>
+    <col min="11010" max="11010" width="13.4609375" style="166" customWidth="1"/>
+    <col min="11011" max="11048" width="5.4609375" style="166" customWidth="1"/>
+    <col min="11049" max="11265" width="5.4609375" style="166"/>
+    <col min="11266" max="11266" width="13.4609375" style="166" customWidth="1"/>
+    <col min="11267" max="11304" width="5.4609375" style="166" customWidth="1"/>
+    <col min="11305" max="11521" width="5.4609375" style="166"/>
+    <col min="11522" max="11522" width="13.4609375" style="166" customWidth="1"/>
+    <col min="11523" max="11560" width="5.4609375" style="166" customWidth="1"/>
+    <col min="11561" max="11777" width="5.4609375" style="166"/>
+    <col min="11778" max="11778" width="13.4609375" style="166" customWidth="1"/>
+    <col min="11779" max="11816" width="5.4609375" style="166" customWidth="1"/>
+    <col min="11817" max="12033" width="5.4609375" style="166"/>
+    <col min="12034" max="12034" width="13.4609375" style="166" customWidth="1"/>
+    <col min="12035" max="12072" width="5.4609375" style="166" customWidth="1"/>
+    <col min="12073" max="12289" width="5.4609375" style="166"/>
+    <col min="12290" max="12290" width="13.4609375" style="166" customWidth="1"/>
+    <col min="12291" max="12328" width="5.4609375" style="166" customWidth="1"/>
+    <col min="12329" max="12545" width="5.4609375" style="166"/>
+    <col min="12546" max="12546" width="13.4609375" style="166" customWidth="1"/>
+    <col min="12547" max="12584" width="5.4609375" style="166" customWidth="1"/>
+    <col min="12585" max="12801" width="5.4609375" style="166"/>
+    <col min="12802" max="12802" width="13.4609375" style="166" customWidth="1"/>
+    <col min="12803" max="12840" width="5.4609375" style="166" customWidth="1"/>
+    <col min="12841" max="13057" width="5.4609375" style="166"/>
+    <col min="13058" max="13058" width="13.4609375" style="166" customWidth="1"/>
+    <col min="13059" max="13096" width="5.4609375" style="166" customWidth="1"/>
+    <col min="13097" max="13313" width="5.4609375" style="166"/>
+    <col min="13314" max="13314" width="13.4609375" style="166" customWidth="1"/>
+    <col min="13315" max="13352" width="5.4609375" style="166" customWidth="1"/>
+    <col min="13353" max="13569" width="5.4609375" style="166"/>
+    <col min="13570" max="13570" width="13.4609375" style="166" customWidth="1"/>
+    <col min="13571" max="13608" width="5.4609375" style="166" customWidth="1"/>
+    <col min="13609" max="13825" width="5.4609375" style="166"/>
+    <col min="13826" max="13826" width="13.4609375" style="166" customWidth="1"/>
+    <col min="13827" max="13864" width="5.4609375" style="166" customWidth="1"/>
+    <col min="13865" max="14081" width="5.4609375" style="166"/>
+    <col min="14082" max="14082" width="13.4609375" style="166" customWidth="1"/>
+    <col min="14083" max="14120" width="5.4609375" style="166" customWidth="1"/>
+    <col min="14121" max="14337" width="5.4609375" style="166"/>
+    <col min="14338" max="14338" width="13.4609375" style="166" customWidth="1"/>
+    <col min="14339" max="14376" width="5.4609375" style="166" customWidth="1"/>
+    <col min="14377" max="14593" width="5.4609375" style="166"/>
+    <col min="14594" max="14594" width="13.4609375" style="166" customWidth="1"/>
+    <col min="14595" max="14632" width="5.4609375" style="166" customWidth="1"/>
+    <col min="14633" max="14849" width="5.4609375" style="166"/>
+    <col min="14850" max="14850" width="13.4609375" style="166" customWidth="1"/>
+    <col min="14851" max="14888" width="5.4609375" style="166" customWidth="1"/>
+    <col min="14889" max="15105" width="5.4609375" style="166"/>
+    <col min="15106" max="15106" width="13.4609375" style="166" customWidth="1"/>
+    <col min="15107" max="15144" width="5.4609375" style="166" customWidth="1"/>
+    <col min="15145" max="15361" width="5.4609375" style="166"/>
+    <col min="15362" max="15362" width="13.4609375" style="166" customWidth="1"/>
+    <col min="15363" max="15400" width="5.4609375" style="166" customWidth="1"/>
+    <col min="15401" max="15617" width="5.4609375" style="166"/>
+    <col min="15618" max="15618" width="13.4609375" style="166" customWidth="1"/>
+    <col min="15619" max="15656" width="5.4609375" style="166" customWidth="1"/>
+    <col min="15657" max="15873" width="5.4609375" style="166"/>
+    <col min="15874" max="15874" width="13.4609375" style="166" customWidth="1"/>
+    <col min="15875" max="15912" width="5.4609375" style="166" customWidth="1"/>
+    <col min="15913" max="16129" width="5.4609375" style="166"/>
+    <col min="16130" max="16130" width="13.4609375" style="166" customWidth="1"/>
+    <col min="16131" max="16168" width="5.4609375" style="166" customWidth="1"/>
+    <col min="16169" max="16384" width="5.4609375" style="166"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B1" s="202" t="s">
+    <row r="1" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B1" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="202"/>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-    </row>
-    <row r="2" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="317" t="s">
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
+      <c r="K1" s="242"/>
+      <c r="L1" s="242"/>
+      <c r="M1" s="242"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="242"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
+      <c r="V1" s="242"/>
+    </row>
+    <row r="2" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B2" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="317"/>
-      <c r="D2" s="317"/>
-      <c r="E2" s="317"/>
-      <c r="F2" s="317"/>
-      <c r="G2" s="317"/>
-      <c r="H2" s="317"/>
-      <c r="I2" s="317"/>
-      <c r="J2" s="317"/>
-      <c r="K2" s="317"/>
-      <c r="L2" s="317"/>
-      <c r="M2" s="317"/>
-      <c r="N2" s="317"/>
-      <c r="O2" s="317"/>
-      <c r="P2" s="317"/>
-      <c r="Q2" s="317"/>
-      <c r="R2" s="317"/>
-      <c r="S2" s="317"/>
-      <c r="T2" s="317"/>
-      <c r="U2" s="317"/>
-      <c r="V2" s="317"/>
-    </row>
-    <row r="3" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B3" s="318" t="s">
+      <c r="C2" s="267"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="267"/>
+      <c r="J2" s="267"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="267"/>
+      <c r="N2" s="267"/>
+      <c r="O2" s="267"/>
+      <c r="P2" s="267"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="267"/>
+      <c r="S2" s="267"/>
+      <c r="T2" s="267"/>
+      <c r="U2" s="267"/>
+      <c r="V2" s="267"/>
+    </row>
+    <row r="3" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="1.25">
+      <c r="B3" s="268" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="318"/>
-      <c r="D3" s="318"/>
-      <c r="E3" s="320"/>
-      <c r="F3" s="320"/>
-      <c r="G3" s="320"/>
-      <c r="H3" s="320"/>
-      <c r="I3" s="320"/>
-      <c r="J3" s="320"/>
-      <c r="K3" s="271" t="s">
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="270"/>
+      <c r="K3" s="317" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="272"/>
-      <c r="M3" s="272"/>
-      <c r="N3" s="272"/>
-      <c r="O3" s="272"/>
-      <c r="P3" s="272"/>
-      <c r="Q3" s="272"/>
-      <c r="R3" s="272"/>
-      <c r="S3" s="272"/>
-      <c r="T3" s="272"/>
-      <c r="U3" s="272"/>
-      <c r="V3" s="272"/>
-      <c r="W3" s="272"/>
-      <c r="X3" s="272"/>
-      <c r="Y3" s="272"/>
-      <c r="Z3" s="272"/>
-      <c r="AA3" s="272"/>
-      <c r="AB3" s="272"/>
-      <c r="AC3" s="273"/>
-      <c r="AD3" s="267" t="s">
+      <c r="L3" s="318"/>
+      <c r="M3" s="318"/>
+      <c r="N3" s="318"/>
+      <c r="O3" s="318"/>
+      <c r="P3" s="318"/>
+      <c r="Q3" s="318"/>
+      <c r="R3" s="318"/>
+      <c r="S3" s="318"/>
+      <c r="T3" s="318"/>
+      <c r="U3" s="318"/>
+      <c r="V3" s="318"/>
+      <c r="W3" s="318"/>
+      <c r="X3" s="318"/>
+      <c r="Y3" s="318"/>
+      <c r="Z3" s="318"/>
+      <c r="AA3" s="318"/>
+      <c r="AB3" s="318"/>
+      <c r="AC3" s="319"/>
+      <c r="AD3" s="314" t="s">
         <v>75</v>
       </c>
-      <c r="AE3" s="268"/>
-      <c r="AF3" s="268"/>
-      <c r="AG3" s="268"/>
-      <c r="AH3" s="268"/>
-      <c r="AI3" s="268"/>
-      <c r="AJ3" s="268"/>
-      <c r="AK3" s="268"/>
-      <c r="AL3" s="269"/>
-    </row>
-    <row r="4" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.95">
-      <c r="B4" s="319" t="s">
+      <c r="AE3" s="315"/>
+      <c r="AF3" s="315"/>
+      <c r="AG3" s="315"/>
+      <c r="AH3" s="315"/>
+      <c r="AI3" s="315"/>
+      <c r="AJ3" s="315"/>
+      <c r="AK3" s="315"/>
+      <c r="AL3" s="316"/>
+    </row>
+    <row r="4" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="1.25">
+      <c r="B4" s="269" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="321"/>
-      <c r="F4" s="321"/>
-      <c r="G4" s="321"/>
-      <c r="H4" s="321"/>
-      <c r="I4" s="321"/>
-      <c r="J4" s="321"/>
-      <c r="K4" s="274" t="s">
+      <c r="C4" s="269"/>
+      <c r="D4" s="269"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="320" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="275"/>
-      <c r="M4" s="275"/>
-      <c r="N4" s="275"/>
-      <c r="O4" s="275"/>
-      <c r="P4" s="275"/>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="276"/>
-      <c r="AD4" s="270" t="s">
+      <c r="L4" s="321"/>
+      <c r="M4" s="321"/>
+      <c r="N4" s="321"/>
+      <c r="O4" s="321"/>
+      <c r="P4" s="321"/>
+      <c r="Q4" s="321"/>
+      <c r="R4" s="321"/>
+      <c r="S4" s="321"/>
+      <c r="T4" s="321"/>
+      <c r="U4" s="321"/>
+      <c r="V4" s="321"/>
+      <c r="W4" s="321"/>
+      <c r="X4" s="321"/>
+      <c r="Y4" s="321"/>
+      <c r="Z4" s="321"/>
+      <c r="AA4" s="321"/>
+      <c r="AB4" s="321"/>
+      <c r="AC4" s="322"/>
+      <c r="AD4" s="294" t="s">
         <v>78</v>
       </c>
-      <c r="AE4" s="270"/>
-      <c r="AF4" s="270"/>
-      <c r="AG4" s="270" t="s">
+      <c r="AE4" s="294"/>
+      <c r="AF4" s="294"/>
+      <c r="AG4" s="294" t="s">
         <v>79</v>
       </c>
-      <c r="AH4" s="270"/>
-      <c r="AI4" s="270"/>
-      <c r="AJ4" s="270" t="s">
+      <c r="AH4" s="294"/>
+      <c r="AI4" s="294"/>
+      <c r="AJ4" s="294" t="s">
         <v>80</v>
       </c>
-      <c r="AK4" s="270"/>
-      <c r="AL4" s="270"/>
+      <c r="AK4" s="294"/>
+      <c r="AL4" s="294"/>
       <c r="AQ4" s="167"/>
       <c r="AR4" s="167"/>
       <c r="AS4" s="167"/>
@@ -11558,52 +11524,52 @@
       <c r="AX4" s="167"/>
       <c r="AY4" s="167"/>
     </row>
-    <row r="5" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.95">
-      <c r="B5" s="319" t="s">
+    <row r="5" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="1.25">
+      <c r="B5" s="269" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="319"/>
-      <c r="D5" s="319"/>
-      <c r="E5" s="321"/>
-      <c r="F5" s="321"/>
-      <c r="G5" s="321"/>
-      <c r="H5" s="321"/>
-      <c r="I5" s="321"/>
-      <c r="J5" s="322"/>
-      <c r="K5" s="279" t="s">
+      <c r="C5" s="269"/>
+      <c r="D5" s="269"/>
+      <c r="E5" s="271"/>
+      <c r="F5" s="271"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="272"/>
+      <c r="K5" s="310" t="s">
         <v>81</v>
       </c>
-      <c r="L5" s="279"/>
-      <c r="M5" s="280"/>
-      <c r="N5" s="280"/>
-      <c r="O5" s="280"/>
-      <c r="P5" s="280"/>
-      <c r="Q5" s="280"/>
-      <c r="R5" s="280"/>
+      <c r="L5" s="310"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
+      <c r="O5" s="311"/>
+      <c r="P5" s="311"/>
+      <c r="Q5" s="311"/>
+      <c r="R5" s="311"/>
       <c r="S5" s="168"/>
       <c r="T5" s="169"/>
       <c r="U5" s="169"/>
-      <c r="V5" s="281" t="s">
+      <c r="V5" s="312" t="s">
         <v>82</v>
       </c>
-      <c r="W5" s="281"/>
+      <c r="W5" s="312"/>
       <c r="X5" s="169"/>
       <c r="Y5" s="169"/>
       <c r="Z5" s="169"/>
-      <c r="AA5" s="281" t="s">
+      <c r="AA5" s="312" t="s">
         <v>83</v>
       </c>
-      <c r="AB5" s="281"/>
+      <c r="AB5" s="312"/>
       <c r="AC5" s="170"/>
-      <c r="AD5" s="283"/>
-      <c r="AE5" s="283"/>
-      <c r="AF5" s="283"/>
-      <c r="AG5" s="283"/>
-      <c r="AH5" s="283"/>
-      <c r="AI5" s="283"/>
-      <c r="AJ5" s="283"/>
-      <c r="AK5" s="283"/>
-      <c r="AL5" s="283"/>
+      <c r="AD5" s="305"/>
+      <c r="AE5" s="305"/>
+      <c r="AF5" s="305"/>
+      <c r="AG5" s="305"/>
+      <c r="AH5" s="305"/>
+      <c r="AI5" s="305"/>
+      <c r="AJ5" s="305"/>
+      <c r="AK5" s="305"/>
+      <c r="AL5" s="305"/>
       <c r="AQ5" s="167"/>
       <c r="AR5" s="167"/>
       <c r="AS5" s="167"/>
@@ -11614,1240 +11580,1240 @@
       <c r="AX5" s="167"/>
       <c r="AY5" s="167"/>
     </row>
-    <row r="6" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="277"/>
-      <c r="C6" s="278"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="278"/>
-      <c r="J6" s="278"/>
-      <c r="K6" s="284" t="s">
+    <row r="6" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B6" s="308"/>
+      <c r="C6" s="309"/>
+      <c r="D6" s="309"/>
+      <c r="E6" s="309"/>
+      <c r="F6" s="309"/>
+      <c r="G6" s="309"/>
+      <c r="H6" s="309"/>
+      <c r="I6" s="309"/>
+      <c r="J6" s="309"/>
+      <c r="K6" s="306" t="s">
         <v>84</v>
       </c>
-      <c r="L6" s="284"/>
-      <c r="M6" s="285"/>
-      <c r="N6" s="285"/>
-      <c r="O6" s="285"/>
-      <c r="P6" s="285"/>
-      <c r="Q6" s="285"/>
-      <c r="R6" s="285"/>
+      <c r="L6" s="306"/>
+      <c r="M6" s="307"/>
+      <c r="N6" s="307"/>
+      <c r="O6" s="307"/>
+      <c r="P6" s="307"/>
+      <c r="Q6" s="307"/>
+      <c r="R6" s="307"/>
       <c r="S6" s="171"/>
       <c r="T6" s="172"/>
       <c r="U6" s="172"/>
-      <c r="V6" s="282"/>
-      <c r="W6" s="282"/>
+      <c r="V6" s="313"/>
+      <c r="W6" s="313"/>
       <c r="X6" s="172"/>
       <c r="Y6" s="172"/>
       <c r="Z6" s="172"/>
-      <c r="AA6" s="282"/>
-      <c r="AB6" s="282"/>
+      <c r="AA6" s="313"/>
+      <c r="AB6" s="313"/>
       <c r="AC6" s="173"/>
-      <c r="AD6" s="283"/>
-      <c r="AE6" s="283"/>
-      <c r="AF6" s="283"/>
-      <c r="AG6" s="283"/>
-      <c r="AH6" s="283"/>
-      <c r="AI6" s="283"/>
-      <c r="AJ6" s="283"/>
-      <c r="AK6" s="283"/>
-      <c r="AL6" s="283"/>
-    </row>
-    <row r="7" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B7" s="295"/>
-      <c r="C7" s="296"/>
-      <c r="D7" s="296"/>
-      <c r="E7" s="296"/>
-      <c r="F7" s="296"/>
-      <c r="G7" s="296"/>
-      <c r="H7" s="296"/>
-      <c r="I7" s="296"/>
-      <c r="J7" s="296"/>
-      <c r="K7" s="296"/>
-      <c r="L7" s="296"/>
-      <c r="M7" s="296"/>
-      <c r="N7" s="296"/>
-      <c r="O7" s="296"/>
-      <c r="P7" s="296"/>
-      <c r="Q7" s="296"/>
-      <c r="R7" s="296"/>
-      <c r="S7" s="296"/>
-      <c r="T7" s="296"/>
-      <c r="U7" s="296"/>
-      <c r="V7" s="296"/>
-      <c r="W7" s="296"/>
-      <c r="X7" s="296"/>
-      <c r="Y7" s="296"/>
-      <c r="Z7" s="296"/>
-      <c r="AA7" s="296"/>
-      <c r="AB7" s="296"/>
-      <c r="AC7" s="296"/>
-      <c r="AD7" s="296"/>
-      <c r="AE7" s="296"/>
-      <c r="AF7" s="296"/>
-      <c r="AG7" s="296"/>
-      <c r="AH7" s="297"/>
-      <c r="AI7" s="304" t="s">
+      <c r="AD6" s="305"/>
+      <c r="AE6" s="305"/>
+      <c r="AF6" s="305"/>
+      <c r="AG6" s="305"/>
+      <c r="AH6" s="305"/>
+      <c r="AI6" s="305"/>
+      <c r="AJ6" s="305"/>
+      <c r="AK6" s="305"/>
+      <c r="AL6" s="305"/>
+    </row>
+    <row r="7" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.95">
+      <c r="B7" s="282"/>
+      <c r="C7" s="283"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="283"/>
+      <c r="M7" s="283"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="283"/>
+      <c r="P7" s="283"/>
+      <c r="Q7" s="283"/>
+      <c r="R7" s="283"/>
+      <c r="S7" s="283"/>
+      <c r="T7" s="283"/>
+      <c r="U7" s="283"/>
+      <c r="V7" s="283"/>
+      <c r="W7" s="283"/>
+      <c r="X7" s="283"/>
+      <c r="Y7" s="283"/>
+      <c r="Z7" s="283"/>
+      <c r="AA7" s="283"/>
+      <c r="AB7" s="283"/>
+      <c r="AC7" s="283"/>
+      <c r="AD7" s="283"/>
+      <c r="AE7" s="283"/>
+      <c r="AF7" s="283"/>
+      <c r="AG7" s="283"/>
+      <c r="AH7" s="284"/>
+      <c r="AI7" s="291" t="s">
         <v>85</v>
       </c>
-      <c r="AJ7" s="304"/>
-      <c r="AK7" s="304"/>
-      <c r="AL7" s="304"/>
-    </row>
-    <row r="8" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="298"/>
-      <c r="C8" s="299"/>
-      <c r="D8" s="299"/>
-      <c r="E8" s="299"/>
-      <c r="F8" s="299"/>
-      <c r="G8" s="299"/>
-      <c r="H8" s="299"/>
-      <c r="I8" s="299"/>
-      <c r="J8" s="299"/>
-      <c r="K8" s="299"/>
-      <c r="L8" s="299"/>
-      <c r="M8" s="299"/>
-      <c r="N8" s="299"/>
-      <c r="O8" s="299"/>
-      <c r="P8" s="299"/>
-      <c r="Q8" s="299"/>
-      <c r="R8" s="299"/>
-      <c r="S8" s="299"/>
-      <c r="T8" s="299"/>
-      <c r="U8" s="299"/>
-      <c r="V8" s="299"/>
-      <c r="W8" s="299"/>
-      <c r="X8" s="299"/>
-      <c r="Y8" s="299"/>
-      <c r="Z8" s="299"/>
-      <c r="AA8" s="299"/>
-      <c r="AB8" s="299"/>
-      <c r="AC8" s="299"/>
-      <c r="AD8" s="299"/>
-      <c r="AE8" s="299"/>
-      <c r="AF8" s="299"/>
-      <c r="AG8" s="299"/>
-      <c r="AH8" s="300"/>
-      <c r="AI8" s="305"/>
-      <c r="AJ8" s="305"/>
-      <c r="AK8" s="305"/>
-      <c r="AL8" s="305"/>
+      <c r="AJ7" s="291"/>
+      <c r="AK7" s="291"/>
+      <c r="AL7" s="291"/>
+    </row>
+    <row r="8" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B8" s="285"/>
+      <c r="C8" s="286"/>
+      <c r="D8" s="286"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="286"/>
+      <c r="J8" s="286"/>
+      <c r="K8" s="286"/>
+      <c r="L8" s="286"/>
+      <c r="M8" s="286"/>
+      <c r="N8" s="286"/>
+      <c r="O8" s="286"/>
+      <c r="P8" s="286"/>
+      <c r="Q8" s="286"/>
+      <c r="R8" s="286"/>
+      <c r="S8" s="286"/>
+      <c r="T8" s="286"/>
+      <c r="U8" s="286"/>
+      <c r="V8" s="286"/>
+      <c r="W8" s="286"/>
+      <c r="X8" s="286"/>
+      <c r="Y8" s="286"/>
+      <c r="Z8" s="286"/>
+      <c r="AA8" s="286"/>
+      <c r="AB8" s="286"/>
+      <c r="AC8" s="286"/>
+      <c r="AD8" s="286"/>
+      <c r="AE8" s="286"/>
+      <c r="AF8" s="286"/>
+      <c r="AG8" s="286"/>
+      <c r="AH8" s="287"/>
+      <c r="AI8" s="292"/>
+      <c r="AJ8" s="292"/>
+      <c r="AK8" s="292"/>
+      <c r="AL8" s="292"/>
       <c r="AM8" s="174"/>
       <c r="AN8" s="174"/>
     </row>
-    <row r="9" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="298"/>
-      <c r="C9" s="299"/>
-      <c r="D9" s="299"/>
-      <c r="E9" s="299"/>
-      <c r="F9" s="299"/>
-      <c r="G9" s="299"/>
-      <c r="H9" s="299"/>
-      <c r="I9" s="299"/>
-      <c r="J9" s="299"/>
-      <c r="K9" s="299"/>
-      <c r="L9" s="299"/>
-      <c r="M9" s="299"/>
-      <c r="N9" s="299"/>
-      <c r="O9" s="299"/>
-      <c r="P9" s="299"/>
-      <c r="Q9" s="299"/>
-      <c r="R9" s="299"/>
-      <c r="S9" s="299"/>
-      <c r="T9" s="299"/>
-      <c r="U9" s="299"/>
-      <c r="V9" s="299"/>
-      <c r="W9" s="299"/>
-      <c r="X9" s="299"/>
-      <c r="Y9" s="299"/>
-      <c r="Z9" s="299"/>
-      <c r="AA9" s="299"/>
-      <c r="AB9" s="299"/>
-      <c r="AC9" s="299"/>
-      <c r="AD9" s="299"/>
-      <c r="AE9" s="299"/>
-      <c r="AF9" s="299"/>
-      <c r="AG9" s="299"/>
-      <c r="AH9" s="300"/>
-      <c r="AI9" s="305"/>
-      <c r="AJ9" s="305"/>
-      <c r="AK9" s="305"/>
-      <c r="AL9" s="305"/>
+    <row r="9" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B9" s="285"/>
+      <c r="C9" s="286"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="286"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="286"/>
+      <c r="M9" s="286"/>
+      <c r="N9" s="286"/>
+      <c r="O9" s="286"/>
+      <c r="P9" s="286"/>
+      <c r="Q9" s="286"/>
+      <c r="R9" s="286"/>
+      <c r="S9" s="286"/>
+      <c r="T9" s="286"/>
+      <c r="U9" s="286"/>
+      <c r="V9" s="286"/>
+      <c r="W9" s="286"/>
+      <c r="X9" s="286"/>
+      <c r="Y9" s="286"/>
+      <c r="Z9" s="286"/>
+      <c r="AA9" s="286"/>
+      <c r="AB9" s="286"/>
+      <c r="AC9" s="286"/>
+      <c r="AD9" s="286"/>
+      <c r="AE9" s="286"/>
+      <c r="AF9" s="286"/>
+      <c r="AG9" s="286"/>
+      <c r="AH9" s="287"/>
+      <c r="AI9" s="292"/>
+      <c r="AJ9" s="292"/>
+      <c r="AK9" s="292"/>
+      <c r="AL9" s="292"/>
       <c r="AM9" s="176"/>
       <c r="AN9" s="176"/>
     </row>
-    <row r="10" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="298"/>
-      <c r="C10" s="299"/>
-      <c r="D10" s="299"/>
-      <c r="E10" s="299"/>
-      <c r="F10" s="299"/>
-      <c r="G10" s="299"/>
-      <c r="H10" s="299"/>
-      <c r="I10" s="299"/>
-      <c r="J10" s="299"/>
-      <c r="K10" s="299"/>
-      <c r="L10" s="299"/>
-      <c r="M10" s="299"/>
-      <c r="N10" s="299"/>
-      <c r="O10" s="299"/>
-      <c r="P10" s="299"/>
-      <c r="Q10" s="299"/>
-      <c r="R10" s="299"/>
-      <c r="S10" s="299"/>
-      <c r="T10" s="299"/>
-      <c r="U10" s="299"/>
-      <c r="V10" s="299"/>
-      <c r="W10" s="299"/>
-      <c r="X10" s="299"/>
-      <c r="Y10" s="299"/>
-      <c r="Z10" s="299"/>
-      <c r="AA10" s="299"/>
-      <c r="AB10" s="299"/>
-      <c r="AC10" s="299"/>
-      <c r="AD10" s="299"/>
-      <c r="AE10" s="299"/>
-      <c r="AF10" s="299"/>
-      <c r="AG10" s="299"/>
-      <c r="AH10" s="300"/>
-      <c r="AI10" s="305"/>
-      <c r="AJ10" s="305"/>
-      <c r="AK10" s="305"/>
-      <c r="AL10" s="305"/>
+    <row r="10" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B10" s="285"/>
+      <c r="C10" s="286"/>
+      <c r="D10" s="286"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="286"/>
+      <c r="H10" s="286"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="286"/>
+      <c r="K10" s="286"/>
+      <c r="L10" s="286"/>
+      <c r="M10" s="286"/>
+      <c r="N10" s="286"/>
+      <c r="O10" s="286"/>
+      <c r="P10" s="286"/>
+      <c r="Q10" s="286"/>
+      <c r="R10" s="286"/>
+      <c r="S10" s="286"/>
+      <c r="T10" s="286"/>
+      <c r="U10" s="286"/>
+      <c r="V10" s="286"/>
+      <c r="W10" s="286"/>
+      <c r="X10" s="286"/>
+      <c r="Y10" s="286"/>
+      <c r="Z10" s="286"/>
+      <c r="AA10" s="286"/>
+      <c r="AB10" s="286"/>
+      <c r="AC10" s="286"/>
+      <c r="AD10" s="286"/>
+      <c r="AE10" s="286"/>
+      <c r="AF10" s="286"/>
+      <c r="AG10" s="286"/>
+      <c r="AH10" s="287"/>
+      <c r="AI10" s="292"/>
+      <c r="AJ10" s="292"/>
+      <c r="AK10" s="292"/>
+      <c r="AL10" s="292"/>
       <c r="AM10" s="176"/>
       <c r="AN10" s="176"/>
     </row>
-    <row r="11" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="298"/>
-      <c r="C11" s="299"/>
-      <c r="D11" s="299"/>
-      <c r="E11" s="299"/>
-      <c r="F11" s="299"/>
-      <c r="G11" s="299"/>
-      <c r="H11" s="299"/>
-      <c r="I11" s="299"/>
-      <c r="J11" s="299"/>
-      <c r="K11" s="299"/>
-      <c r="L11" s="299"/>
-      <c r="M11" s="299"/>
-      <c r="N11" s="299"/>
-      <c r="O11" s="299"/>
-      <c r="P11" s="299"/>
-      <c r="Q11" s="299"/>
-      <c r="R11" s="299"/>
-      <c r="S11" s="299"/>
-      <c r="T11" s="299"/>
-      <c r="U11" s="299"/>
-      <c r="V11" s="299"/>
-      <c r="W11" s="299"/>
-      <c r="X11" s="299"/>
-      <c r="Y11" s="299"/>
-      <c r="Z11" s="299"/>
-      <c r="AA11" s="299"/>
-      <c r="AB11" s="299"/>
-      <c r="AC11" s="299"/>
-      <c r="AD11" s="299"/>
-      <c r="AE11" s="299"/>
-      <c r="AF11" s="299"/>
-      <c r="AG11" s="299"/>
-      <c r="AH11" s="300"/>
-      <c r="AI11" s="305" t="s">
+    <row r="11" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B11" s="285"/>
+      <c r="C11" s="286"/>
+      <c r="D11" s="286"/>
+      <c r="E11" s="286"/>
+      <c r="F11" s="286"/>
+      <c r="G11" s="286"/>
+      <c r="H11" s="286"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="286"/>
+      <c r="K11" s="286"/>
+      <c r="L11" s="286"/>
+      <c r="M11" s="286"/>
+      <c r="N11" s="286"/>
+      <c r="O11" s="286"/>
+      <c r="P11" s="286"/>
+      <c r="Q11" s="286"/>
+      <c r="R11" s="286"/>
+      <c r="S11" s="286"/>
+      <c r="T11" s="286"/>
+      <c r="U11" s="286"/>
+      <c r="V11" s="286"/>
+      <c r="W11" s="286"/>
+      <c r="X11" s="286"/>
+      <c r="Y11" s="286"/>
+      <c r="Z11" s="286"/>
+      <c r="AA11" s="286"/>
+      <c r="AB11" s="286"/>
+      <c r="AC11" s="286"/>
+      <c r="AD11" s="286"/>
+      <c r="AE11" s="286"/>
+      <c r="AF11" s="286"/>
+      <c r="AG11" s="286"/>
+      <c r="AH11" s="287"/>
+      <c r="AI11" s="292" t="s">
         <v>86</v>
       </c>
-      <c r="AJ11" s="305"/>
-      <c r="AK11" s="305"/>
-      <c r="AL11" s="305"/>
+      <c r="AJ11" s="292"/>
+      <c r="AK11" s="292"/>
+      <c r="AL11" s="292"/>
       <c r="AM11" s="176"/>
       <c r="AN11" s="176"/>
     </row>
-    <row r="12" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="298"/>
-      <c r="C12" s="299"/>
-      <c r="D12" s="299"/>
-      <c r="E12" s="299"/>
-      <c r="F12" s="299"/>
-      <c r="G12" s="299"/>
-      <c r="H12" s="299"/>
-      <c r="I12" s="299"/>
-      <c r="J12" s="299"/>
-      <c r="K12" s="299"/>
-      <c r="L12" s="299"/>
-      <c r="M12" s="299"/>
-      <c r="N12" s="299"/>
-      <c r="O12" s="299"/>
-      <c r="P12" s="299"/>
-      <c r="Q12" s="299"/>
-      <c r="R12" s="299"/>
-      <c r="S12" s="299"/>
-      <c r="T12" s="299"/>
-      <c r="U12" s="299"/>
-      <c r="V12" s="299"/>
-      <c r="W12" s="299"/>
-      <c r="X12" s="299"/>
-      <c r="Y12" s="299"/>
-      <c r="Z12" s="299"/>
-      <c r="AA12" s="299"/>
-      <c r="AB12" s="299"/>
-      <c r="AC12" s="299"/>
-      <c r="AD12" s="299"/>
-      <c r="AE12" s="299"/>
-      <c r="AF12" s="299"/>
-      <c r="AG12" s="299"/>
-      <c r="AH12" s="300"/>
-      <c r="AI12" s="305"/>
-      <c r="AJ12" s="305"/>
-      <c r="AK12" s="305"/>
-      <c r="AL12" s="305"/>
+    <row r="12" spans="2:51" s="175" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="B12" s="285"/>
+      <c r="C12" s="286"/>
+      <c r="D12" s="286"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="286"/>
+      <c r="G12" s="286"/>
+      <c r="H12" s="286"/>
+      <c r="I12" s="286"/>
+      <c r="J12" s="286"/>
+      <c r="K12" s="286"/>
+      <c r="L12" s="286"/>
+      <c r="M12" s="286"/>
+      <c r="N12" s="286"/>
+      <c r="O12" s="286"/>
+      <c r="P12" s="286"/>
+      <c r="Q12" s="286"/>
+      <c r="R12" s="286"/>
+      <c r="S12" s="286"/>
+      <c r="T12" s="286"/>
+      <c r="U12" s="286"/>
+      <c r="V12" s="286"/>
+      <c r="W12" s="286"/>
+      <c r="X12" s="286"/>
+      <c r="Y12" s="286"/>
+      <c r="Z12" s="286"/>
+      <c r="AA12" s="286"/>
+      <c r="AB12" s="286"/>
+      <c r="AC12" s="286"/>
+      <c r="AD12" s="286"/>
+      <c r="AE12" s="286"/>
+      <c r="AF12" s="286"/>
+      <c r="AG12" s="286"/>
+      <c r="AH12" s="287"/>
+      <c r="AI12" s="292"/>
+      <c r="AJ12" s="292"/>
+      <c r="AK12" s="292"/>
+      <c r="AL12" s="292"/>
       <c r="AM12" s="176"/>
       <c r="AN12" s="176"/>
     </row>
-    <row r="13" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="298"/>
-      <c r="C13" s="299"/>
-      <c r="D13" s="299"/>
-      <c r="E13" s="299"/>
-      <c r="F13" s="299"/>
-      <c r="G13" s="299"/>
-      <c r="H13" s="299"/>
-      <c r="I13" s="299"/>
-      <c r="J13" s="299"/>
-      <c r="K13" s="299"/>
-      <c r="L13" s="299"/>
-      <c r="M13" s="299"/>
-      <c r="N13" s="299"/>
-      <c r="O13" s="299"/>
-      <c r="P13" s="299"/>
-      <c r="Q13" s="299"/>
-      <c r="R13" s="299"/>
-      <c r="S13" s="299"/>
-      <c r="T13" s="299"/>
-      <c r="U13" s="299"/>
-      <c r="V13" s="299"/>
-      <c r="W13" s="299"/>
-      <c r="X13" s="299"/>
-      <c r="Y13" s="299"/>
-      <c r="Z13" s="299"/>
-      <c r="AA13" s="299"/>
-      <c r="AB13" s="299"/>
-      <c r="AC13" s="299"/>
-      <c r="AD13" s="299"/>
-      <c r="AE13" s="299"/>
-      <c r="AF13" s="299"/>
-      <c r="AG13" s="299"/>
-      <c r="AH13" s="300"/>
-      <c r="AI13" s="305"/>
-      <c r="AJ13" s="305"/>
-      <c r="AK13" s="305"/>
-      <c r="AL13" s="305"/>
-    </row>
-    <row r="14" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="298"/>
-      <c r="C14" s="299"/>
-      <c r="D14" s="299"/>
-      <c r="E14" s="299"/>
-      <c r="F14" s="299"/>
-      <c r="G14" s="299"/>
-      <c r="H14" s="299"/>
-      <c r="I14" s="299"/>
-      <c r="J14" s="299"/>
-      <c r="K14" s="299"/>
-      <c r="L14" s="299"/>
-      <c r="M14" s="299"/>
-      <c r="N14" s="299"/>
-      <c r="O14" s="299"/>
-      <c r="P14" s="299"/>
-      <c r="Q14" s="299"/>
-      <c r="R14" s="299"/>
-      <c r="S14" s="299"/>
-      <c r="T14" s="299"/>
-      <c r="U14" s="299"/>
-      <c r="V14" s="299"/>
-      <c r="W14" s="299"/>
-      <c r="X14" s="299"/>
-      <c r="Y14" s="299"/>
-      <c r="Z14" s="299"/>
-      <c r="AA14" s="299"/>
-      <c r="AB14" s="299"/>
-      <c r="AC14" s="299"/>
-      <c r="AD14" s="299"/>
-      <c r="AE14" s="299"/>
-      <c r="AF14" s="299"/>
-      <c r="AG14" s="299"/>
-      <c r="AH14" s="300"/>
-      <c r="AI14" s="305"/>
-      <c r="AJ14" s="305"/>
-      <c r="AK14" s="305"/>
-      <c r="AL14" s="305"/>
-    </row>
-    <row r="15" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B15" s="298"/>
-      <c r="C15" s="299"/>
-      <c r="D15" s="299"/>
-      <c r="E15" s="299"/>
-      <c r="F15" s="299"/>
-      <c r="G15" s="299"/>
-      <c r="H15" s="299"/>
-      <c r="I15" s="299"/>
-      <c r="J15" s="299"/>
-      <c r="K15" s="299"/>
-      <c r="L15" s="299"/>
-      <c r="M15" s="299"/>
-      <c r="N15" s="299"/>
-      <c r="O15" s="299"/>
-      <c r="P15" s="299"/>
-      <c r="Q15" s="299"/>
-      <c r="R15" s="299"/>
-      <c r="S15" s="299"/>
-      <c r="T15" s="299"/>
-      <c r="U15" s="299"/>
-      <c r="V15" s="299"/>
-      <c r="W15" s="299"/>
-      <c r="X15" s="299"/>
-      <c r="Y15" s="299"/>
-      <c r="Z15" s="299"/>
-      <c r="AA15" s="299"/>
-      <c r="AB15" s="299"/>
-      <c r="AC15" s="299"/>
-      <c r="AD15" s="299"/>
-      <c r="AE15" s="299"/>
-      <c r="AF15" s="299"/>
-      <c r="AG15" s="299"/>
-      <c r="AH15" s="300"/>
-      <c r="AI15" s="306" t="s">
+    <row r="13" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B13" s="285"/>
+      <c r="C13" s="286"/>
+      <c r="D13" s="286"/>
+      <c r="E13" s="286"/>
+      <c r="F13" s="286"/>
+      <c r="G13" s="286"/>
+      <c r="H13" s="286"/>
+      <c r="I13" s="286"/>
+      <c r="J13" s="286"/>
+      <c r="K13" s="286"/>
+      <c r="L13" s="286"/>
+      <c r="M13" s="286"/>
+      <c r="N13" s="286"/>
+      <c r="O13" s="286"/>
+      <c r="P13" s="286"/>
+      <c r="Q13" s="286"/>
+      <c r="R13" s="286"/>
+      <c r="S13" s="286"/>
+      <c r="T13" s="286"/>
+      <c r="U13" s="286"/>
+      <c r="V13" s="286"/>
+      <c r="W13" s="286"/>
+      <c r="X13" s="286"/>
+      <c r="Y13" s="286"/>
+      <c r="Z13" s="286"/>
+      <c r="AA13" s="286"/>
+      <c r="AB13" s="286"/>
+      <c r="AC13" s="286"/>
+      <c r="AD13" s="286"/>
+      <c r="AE13" s="286"/>
+      <c r="AF13" s="286"/>
+      <c r="AG13" s="286"/>
+      <c r="AH13" s="287"/>
+      <c r="AI13" s="292"/>
+      <c r="AJ13" s="292"/>
+      <c r="AK13" s="292"/>
+      <c r="AL13" s="292"/>
+    </row>
+    <row r="14" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B14" s="285"/>
+      <c r="C14" s="286"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="286"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="286"/>
+      <c r="K14" s="286"/>
+      <c r="L14" s="286"/>
+      <c r="M14" s="286"/>
+      <c r="N14" s="286"/>
+      <c r="O14" s="286"/>
+      <c r="P14" s="286"/>
+      <c r="Q14" s="286"/>
+      <c r="R14" s="286"/>
+      <c r="S14" s="286"/>
+      <c r="T14" s="286"/>
+      <c r="U14" s="286"/>
+      <c r="V14" s="286"/>
+      <c r="W14" s="286"/>
+      <c r="X14" s="286"/>
+      <c r="Y14" s="286"/>
+      <c r="Z14" s="286"/>
+      <c r="AA14" s="286"/>
+      <c r="AB14" s="286"/>
+      <c r="AC14" s="286"/>
+      <c r="AD14" s="286"/>
+      <c r="AE14" s="286"/>
+      <c r="AF14" s="286"/>
+      <c r="AG14" s="286"/>
+      <c r="AH14" s="287"/>
+      <c r="AI14" s="292"/>
+      <c r="AJ14" s="292"/>
+      <c r="AK14" s="292"/>
+      <c r="AL14" s="292"/>
+    </row>
+    <row r="15" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B15" s="285"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
+      <c r="H15" s="286"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="286"/>
+      <c r="K15" s="286"/>
+      <c r="L15" s="286"/>
+      <c r="M15" s="286"/>
+      <c r="N15" s="286"/>
+      <c r="O15" s="286"/>
+      <c r="P15" s="286"/>
+      <c r="Q15" s="286"/>
+      <c r="R15" s="286"/>
+      <c r="S15" s="286"/>
+      <c r="T15" s="286"/>
+      <c r="U15" s="286"/>
+      <c r="V15" s="286"/>
+      <c r="W15" s="286"/>
+      <c r="X15" s="286"/>
+      <c r="Y15" s="286"/>
+      <c r="Z15" s="286"/>
+      <c r="AA15" s="286"/>
+      <c r="AB15" s="286"/>
+      <c r="AC15" s="286"/>
+      <c r="AD15" s="286"/>
+      <c r="AE15" s="286"/>
+      <c r="AF15" s="286"/>
+      <c r="AG15" s="286"/>
+      <c r="AH15" s="287"/>
+      <c r="AI15" s="293" t="s">
         <v>87</v>
       </c>
-      <c r="AJ15" s="306"/>
-      <c r="AK15" s="306"/>
-      <c r="AL15" s="306"/>
-    </row>
-    <row r="16" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B16" s="298"/>
-      <c r="C16" s="299"/>
-      <c r="D16" s="299"/>
-      <c r="E16" s="299"/>
-      <c r="F16" s="299"/>
-      <c r="G16" s="299"/>
-      <c r="H16" s="299"/>
-      <c r="I16" s="299"/>
-      <c r="J16" s="299"/>
-      <c r="K16" s="299"/>
-      <c r="L16" s="299"/>
-      <c r="M16" s="299"/>
-      <c r="N16" s="299"/>
-      <c r="O16" s="299"/>
-      <c r="P16" s="299"/>
-      <c r="Q16" s="299"/>
-      <c r="R16" s="299"/>
-      <c r="S16" s="299"/>
-      <c r="T16" s="299"/>
-      <c r="U16" s="299"/>
-      <c r="V16" s="299"/>
-      <c r="W16" s="299"/>
-      <c r="X16" s="299"/>
-      <c r="Y16" s="299"/>
-      <c r="Z16" s="299"/>
-      <c r="AA16" s="299"/>
-      <c r="AB16" s="299"/>
-      <c r="AC16" s="299"/>
-      <c r="AD16" s="299"/>
-      <c r="AE16" s="299"/>
-      <c r="AF16" s="299"/>
-      <c r="AG16" s="299"/>
-      <c r="AH16" s="300"/>
-      <c r="AI16" s="306"/>
-      <c r="AJ16" s="306"/>
-      <c r="AK16" s="306"/>
-      <c r="AL16" s="306"/>
-    </row>
-    <row r="17" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B17" s="298"/>
-      <c r="C17" s="299"/>
-      <c r="D17" s="299"/>
-      <c r="E17" s="299"/>
-      <c r="F17" s="299"/>
-      <c r="G17" s="299"/>
-      <c r="H17" s="299"/>
-      <c r="I17" s="299"/>
-      <c r="J17" s="299"/>
-      <c r="K17" s="299"/>
-      <c r="L17" s="299"/>
-      <c r="M17" s="299"/>
-      <c r="N17" s="299"/>
-      <c r="O17" s="299"/>
-      <c r="P17" s="299"/>
-      <c r="Q17" s="299"/>
-      <c r="R17" s="299"/>
-      <c r="S17" s="299"/>
-      <c r="T17" s="299"/>
-      <c r="U17" s="299"/>
-      <c r="V17" s="299"/>
-      <c r="W17" s="299"/>
-      <c r="X17" s="299"/>
-      <c r="Y17" s="299"/>
-      <c r="Z17" s="299"/>
-      <c r="AA17" s="299"/>
-      <c r="AB17" s="299"/>
-      <c r="AC17" s="299"/>
-      <c r="AD17" s="299"/>
-      <c r="AE17" s="299"/>
-      <c r="AF17" s="299"/>
-      <c r="AG17" s="299"/>
-      <c r="AH17" s="300"/>
-      <c r="AI17" s="306"/>
-      <c r="AJ17" s="306"/>
-      <c r="AK17" s="306"/>
-      <c r="AL17" s="306"/>
-    </row>
-    <row r="18" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B18" s="298"/>
-      <c r="C18" s="299"/>
-      <c r="D18" s="299"/>
-      <c r="E18" s="299"/>
-      <c r="F18" s="299"/>
-      <c r="G18" s="299"/>
-      <c r="H18" s="299"/>
-      <c r="I18" s="299"/>
-      <c r="J18" s="299"/>
-      <c r="K18" s="299"/>
-      <c r="L18" s="299"/>
-      <c r="M18" s="299"/>
-      <c r="N18" s="299"/>
-      <c r="O18" s="299"/>
-      <c r="P18" s="299"/>
-      <c r="Q18" s="299"/>
-      <c r="R18" s="299"/>
-      <c r="S18" s="299"/>
-      <c r="T18" s="299"/>
-      <c r="U18" s="299"/>
-      <c r="V18" s="299"/>
-      <c r="W18" s="299"/>
-      <c r="X18" s="299"/>
-      <c r="Y18" s="299"/>
-      <c r="Z18" s="299"/>
-      <c r="AA18" s="299"/>
-      <c r="AB18" s="299"/>
-      <c r="AC18" s="299"/>
-      <c r="AD18" s="299"/>
-      <c r="AE18" s="299"/>
-      <c r="AF18" s="299"/>
-      <c r="AG18" s="299"/>
-      <c r="AH18" s="300"/>
-      <c r="AI18" s="306"/>
-      <c r="AJ18" s="306"/>
-      <c r="AK18" s="306"/>
-      <c r="AL18" s="306"/>
-    </row>
-    <row r="19" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B19" s="298"/>
-      <c r="C19" s="299"/>
-      <c r="D19" s="299"/>
-      <c r="E19" s="299"/>
-      <c r="F19" s="299"/>
-      <c r="G19" s="299"/>
-      <c r="H19" s="299"/>
-      <c r="I19" s="299"/>
-      <c r="J19" s="299"/>
-      <c r="K19" s="299"/>
-      <c r="L19" s="299"/>
-      <c r="M19" s="299"/>
-      <c r="N19" s="299"/>
-      <c r="O19" s="299"/>
-      <c r="P19" s="299"/>
-      <c r="Q19" s="299"/>
-      <c r="R19" s="299"/>
-      <c r="S19" s="299"/>
-      <c r="T19" s="299"/>
-      <c r="U19" s="299"/>
-      <c r="V19" s="299"/>
-      <c r="W19" s="299"/>
-      <c r="X19" s="299"/>
-      <c r="Y19" s="299"/>
-      <c r="Z19" s="299"/>
-      <c r="AA19" s="299"/>
-      <c r="AB19" s="299"/>
-      <c r="AC19" s="299"/>
-      <c r="AD19" s="299"/>
-      <c r="AE19" s="299"/>
-      <c r="AF19" s="299"/>
-      <c r="AG19" s="299"/>
-      <c r="AH19" s="300"/>
-      <c r="AI19" s="270" t="s">
+      <c r="AJ15" s="293"/>
+      <c r="AK15" s="293"/>
+      <c r="AL15" s="293"/>
+    </row>
+    <row r="16" spans="2:51" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B16" s="285"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="286"/>
+      <c r="K16" s="286"/>
+      <c r="L16" s="286"/>
+      <c r="M16" s="286"/>
+      <c r="N16" s="286"/>
+      <c r="O16" s="286"/>
+      <c r="P16" s="286"/>
+      <c r="Q16" s="286"/>
+      <c r="R16" s="286"/>
+      <c r="S16" s="286"/>
+      <c r="T16" s="286"/>
+      <c r="U16" s="286"/>
+      <c r="V16" s="286"/>
+      <c r="W16" s="286"/>
+      <c r="X16" s="286"/>
+      <c r="Y16" s="286"/>
+      <c r="Z16" s="286"/>
+      <c r="AA16" s="286"/>
+      <c r="AB16" s="286"/>
+      <c r="AC16" s="286"/>
+      <c r="AD16" s="286"/>
+      <c r="AE16" s="286"/>
+      <c r="AF16" s="286"/>
+      <c r="AG16" s="286"/>
+      <c r="AH16" s="287"/>
+      <c r="AI16" s="293"/>
+      <c r="AJ16" s="293"/>
+      <c r="AK16" s="293"/>
+      <c r="AL16" s="293"/>
+    </row>
+    <row r="17" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B17" s="285"/>
+      <c r="C17" s="286"/>
+      <c r="D17" s="286"/>
+      <c r="E17" s="286"/>
+      <c r="F17" s="286"/>
+      <c r="G17" s="286"/>
+      <c r="H17" s="286"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="286"/>
+      <c r="K17" s="286"/>
+      <c r="L17" s="286"/>
+      <c r="M17" s="286"/>
+      <c r="N17" s="286"/>
+      <c r="O17" s="286"/>
+      <c r="P17" s="286"/>
+      <c r="Q17" s="286"/>
+      <c r="R17" s="286"/>
+      <c r="S17" s="286"/>
+      <c r="T17" s="286"/>
+      <c r="U17" s="286"/>
+      <c r="V17" s="286"/>
+      <c r="W17" s="286"/>
+      <c r="X17" s="286"/>
+      <c r="Y17" s="286"/>
+      <c r="Z17" s="286"/>
+      <c r="AA17" s="286"/>
+      <c r="AB17" s="286"/>
+      <c r="AC17" s="286"/>
+      <c r="AD17" s="286"/>
+      <c r="AE17" s="286"/>
+      <c r="AF17" s="286"/>
+      <c r="AG17" s="286"/>
+      <c r="AH17" s="287"/>
+      <c r="AI17" s="293"/>
+      <c r="AJ17" s="293"/>
+      <c r="AK17" s="293"/>
+      <c r="AL17" s="293"/>
+    </row>
+    <row r="18" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B18" s="285"/>
+      <c r="C18" s="286"/>
+      <c r="D18" s="286"/>
+      <c r="E18" s="286"/>
+      <c r="F18" s="286"/>
+      <c r="G18" s="286"/>
+      <c r="H18" s="286"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="286"/>
+      <c r="K18" s="286"/>
+      <c r="L18" s="286"/>
+      <c r="M18" s="286"/>
+      <c r="N18" s="286"/>
+      <c r="O18" s="286"/>
+      <c r="P18" s="286"/>
+      <c r="Q18" s="286"/>
+      <c r="R18" s="286"/>
+      <c r="S18" s="286"/>
+      <c r="T18" s="286"/>
+      <c r="U18" s="286"/>
+      <c r="V18" s="286"/>
+      <c r="W18" s="286"/>
+      <c r="X18" s="286"/>
+      <c r="Y18" s="286"/>
+      <c r="Z18" s="286"/>
+      <c r="AA18" s="286"/>
+      <c r="AB18" s="286"/>
+      <c r="AC18" s="286"/>
+      <c r="AD18" s="286"/>
+      <c r="AE18" s="286"/>
+      <c r="AF18" s="286"/>
+      <c r="AG18" s="286"/>
+      <c r="AH18" s="287"/>
+      <c r="AI18" s="293"/>
+      <c r="AJ18" s="293"/>
+      <c r="AK18" s="293"/>
+      <c r="AL18" s="293"/>
+    </row>
+    <row r="19" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B19" s="285"/>
+      <c r="C19" s="286"/>
+      <c r="D19" s="286"/>
+      <c r="E19" s="286"/>
+      <c r="F19" s="286"/>
+      <c r="G19" s="286"/>
+      <c r="H19" s="286"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="286"/>
+      <c r="K19" s="286"/>
+      <c r="L19" s="286"/>
+      <c r="M19" s="286"/>
+      <c r="N19" s="286"/>
+      <c r="O19" s="286"/>
+      <c r="P19" s="286"/>
+      <c r="Q19" s="286"/>
+      <c r="R19" s="286"/>
+      <c r="S19" s="286"/>
+      <c r="T19" s="286"/>
+      <c r="U19" s="286"/>
+      <c r="V19" s="286"/>
+      <c r="W19" s="286"/>
+      <c r="X19" s="286"/>
+      <c r="Y19" s="286"/>
+      <c r="Z19" s="286"/>
+      <c r="AA19" s="286"/>
+      <c r="AB19" s="286"/>
+      <c r="AC19" s="286"/>
+      <c r="AD19" s="286"/>
+      <c r="AE19" s="286"/>
+      <c r="AF19" s="286"/>
+      <c r="AG19" s="286"/>
+      <c r="AH19" s="287"/>
+      <c r="AI19" s="294" t="s">
         <v>88</v>
       </c>
-      <c r="AJ19" s="270"/>
-      <c r="AK19" s="270"/>
-      <c r="AL19" s="270"/>
-    </row>
-    <row r="20" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B20" s="298"/>
-      <c r="C20" s="299"/>
-      <c r="D20" s="299"/>
-      <c r="E20" s="299"/>
-      <c r="F20" s="299"/>
-      <c r="G20" s="299"/>
-      <c r="H20" s="299"/>
-      <c r="I20" s="299"/>
-      <c r="J20" s="299"/>
-      <c r="K20" s="299"/>
-      <c r="L20" s="299"/>
-      <c r="M20" s="299"/>
-      <c r="N20" s="299"/>
-      <c r="O20" s="299"/>
-      <c r="P20" s="299"/>
-      <c r="Q20" s="299"/>
-      <c r="R20" s="299"/>
-      <c r="S20" s="299"/>
-      <c r="T20" s="299"/>
-      <c r="U20" s="299"/>
-      <c r="V20" s="299"/>
-      <c r="W20" s="299"/>
-      <c r="X20" s="299"/>
-      <c r="Y20" s="299"/>
-      <c r="Z20" s="299"/>
-      <c r="AA20" s="299"/>
-      <c r="AB20" s="299"/>
-      <c r="AC20" s="299"/>
-      <c r="AD20" s="299"/>
-      <c r="AE20" s="299"/>
-      <c r="AF20" s="299"/>
-      <c r="AG20" s="299"/>
-      <c r="AH20" s="300"/>
-      <c r="AI20" s="307" t="s">
+      <c r="AJ19" s="294"/>
+      <c r="AK19" s="294"/>
+      <c r="AL19" s="294"/>
+    </row>
+    <row r="20" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B20" s="285"/>
+      <c r="C20" s="286"/>
+      <c r="D20" s="286"/>
+      <c r="E20" s="286"/>
+      <c r="F20" s="286"/>
+      <c r="G20" s="286"/>
+      <c r="H20" s="286"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="286"/>
+      <c r="K20" s="286"/>
+      <c r="L20" s="286"/>
+      <c r="M20" s="286"/>
+      <c r="N20" s="286"/>
+      <c r="O20" s="286"/>
+      <c r="P20" s="286"/>
+      <c r="Q20" s="286"/>
+      <c r="R20" s="286"/>
+      <c r="S20" s="286"/>
+      <c r="T20" s="286"/>
+      <c r="U20" s="286"/>
+      <c r="V20" s="286"/>
+      <c r="W20" s="286"/>
+      <c r="X20" s="286"/>
+      <c r="Y20" s="286"/>
+      <c r="Z20" s="286"/>
+      <c r="AA20" s="286"/>
+      <c r="AB20" s="286"/>
+      <c r="AC20" s="286"/>
+      <c r="AD20" s="286"/>
+      <c r="AE20" s="286"/>
+      <c r="AF20" s="286"/>
+      <c r="AG20" s="286"/>
+      <c r="AH20" s="287"/>
+      <c r="AI20" s="295" t="s">
         <v>89</v>
       </c>
-      <c r="AJ20" s="307"/>
-      <c r="AK20" s="307"/>
-      <c r="AL20" s="307"/>
-    </row>
-    <row r="21" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="298"/>
-      <c r="C21" s="299"/>
-      <c r="D21" s="299"/>
-      <c r="E21" s="299"/>
-      <c r="F21" s="299"/>
-      <c r="G21" s="299"/>
-      <c r="H21" s="299"/>
-      <c r="I21" s="299"/>
-      <c r="J21" s="299"/>
-      <c r="K21" s="299"/>
-      <c r="L21" s="299"/>
-      <c r="M21" s="299"/>
-      <c r="N21" s="299"/>
-      <c r="O21" s="299"/>
-      <c r="P21" s="299"/>
-      <c r="Q21" s="299"/>
-      <c r="R21" s="299"/>
-      <c r="S21" s="299"/>
-      <c r="T21" s="299"/>
-      <c r="U21" s="299"/>
-      <c r="V21" s="299"/>
-      <c r="W21" s="299"/>
-      <c r="X21" s="299"/>
-      <c r="Y21" s="299"/>
-      <c r="Z21" s="299"/>
-      <c r="AA21" s="299"/>
-      <c r="AB21" s="299"/>
-      <c r="AC21" s="299"/>
-      <c r="AD21" s="299"/>
-      <c r="AE21" s="299"/>
-      <c r="AF21" s="299"/>
-      <c r="AG21" s="299"/>
-      <c r="AH21" s="300"/>
-      <c r="AI21" s="308"/>
-      <c r="AJ21" s="309"/>
-      <c r="AK21" s="309"/>
-      <c r="AL21" s="310"/>
-    </row>
-    <row r="22" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B22" s="298"/>
-      <c r="C22" s="299"/>
-      <c r="D22" s="299"/>
-      <c r="E22" s="299"/>
-      <c r="F22" s="299"/>
-      <c r="G22" s="299"/>
-      <c r="H22" s="299"/>
-      <c r="I22" s="299"/>
-      <c r="J22" s="299"/>
-      <c r="K22" s="299"/>
-      <c r="L22" s="299"/>
-      <c r="M22" s="299"/>
-      <c r="N22" s="299"/>
-      <c r="O22" s="299"/>
-      <c r="P22" s="299"/>
-      <c r="Q22" s="299"/>
-      <c r="R22" s="299"/>
-      <c r="S22" s="299"/>
-      <c r="T22" s="299"/>
-      <c r="U22" s="299"/>
-      <c r="V22" s="299"/>
-      <c r="W22" s="299"/>
-      <c r="X22" s="299"/>
-      <c r="Y22" s="299"/>
-      <c r="Z22" s="299"/>
-      <c r="AA22" s="299"/>
-      <c r="AB22" s="299"/>
-      <c r="AC22" s="299"/>
-      <c r="AD22" s="299"/>
-      <c r="AE22" s="299"/>
-      <c r="AF22" s="299"/>
-      <c r="AG22" s="299"/>
-      <c r="AH22" s="300"/>
-      <c r="AI22" s="311"/>
-      <c r="AJ22" s="312"/>
-      <c r="AK22" s="312"/>
-      <c r="AL22" s="313"/>
-    </row>
-    <row r="23" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B23" s="298"/>
-      <c r="C23" s="299"/>
-      <c r="D23" s="299"/>
-      <c r="E23" s="299"/>
-      <c r="F23" s="299"/>
-      <c r="G23" s="299"/>
-      <c r="H23" s="299"/>
-      <c r="I23" s="299"/>
-      <c r="J23" s="299"/>
-      <c r="K23" s="299"/>
-      <c r="L23" s="299"/>
-      <c r="M23" s="299"/>
-      <c r="N23" s="299"/>
-      <c r="O23" s="299"/>
-      <c r="P23" s="299"/>
-      <c r="Q23" s="299"/>
-      <c r="R23" s="299"/>
-      <c r="S23" s="299"/>
-      <c r="T23" s="299"/>
-      <c r="U23" s="299"/>
-      <c r="V23" s="299"/>
-      <c r="W23" s="299"/>
-      <c r="X23" s="299"/>
-      <c r="Y23" s="299"/>
-      <c r="Z23" s="299"/>
-      <c r="AA23" s="299"/>
-      <c r="AB23" s="299"/>
-      <c r="AC23" s="299"/>
-      <c r="AD23" s="299"/>
-      <c r="AE23" s="299"/>
-      <c r="AF23" s="299"/>
-      <c r="AG23" s="299"/>
-      <c r="AH23" s="300"/>
-      <c r="AI23" s="314"/>
-      <c r="AJ23" s="315"/>
-      <c r="AK23" s="315"/>
-      <c r="AL23" s="316"/>
-    </row>
-    <row r="24" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B24" s="298"/>
-      <c r="C24" s="299"/>
-      <c r="D24" s="299"/>
-      <c r="E24" s="299"/>
-      <c r="F24" s="299"/>
-      <c r="G24" s="299"/>
-      <c r="H24" s="299"/>
-      <c r="I24" s="299"/>
-      <c r="J24" s="299"/>
-      <c r="K24" s="299"/>
-      <c r="L24" s="299"/>
-      <c r="M24" s="299"/>
-      <c r="N24" s="299"/>
-      <c r="O24" s="299"/>
-      <c r="P24" s="299"/>
-      <c r="Q24" s="299"/>
-      <c r="R24" s="299"/>
-      <c r="S24" s="299"/>
-      <c r="T24" s="299"/>
-      <c r="U24" s="299"/>
-      <c r="V24" s="299"/>
-      <c r="W24" s="299"/>
-      <c r="X24" s="299"/>
-      <c r="Y24" s="299"/>
-      <c r="Z24" s="299"/>
-      <c r="AA24" s="299"/>
-      <c r="AB24" s="299"/>
-      <c r="AC24" s="299"/>
-      <c r="AD24" s="299"/>
-      <c r="AE24" s="299"/>
-      <c r="AF24" s="299"/>
-      <c r="AG24" s="299"/>
-      <c r="AH24" s="300"/>
-      <c r="AI24" s="304" t="s">
+      <c r="AJ20" s="295"/>
+      <c r="AK20" s="295"/>
+      <c r="AL20" s="295"/>
+    </row>
+    <row r="21" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B21" s="285"/>
+      <c r="C21" s="286"/>
+      <c r="D21" s="286"/>
+      <c r="E21" s="286"/>
+      <c r="F21" s="286"/>
+      <c r="G21" s="286"/>
+      <c r="H21" s="286"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="286"/>
+      <c r="K21" s="286"/>
+      <c r="L21" s="286"/>
+      <c r="M21" s="286"/>
+      <c r="N21" s="286"/>
+      <c r="O21" s="286"/>
+      <c r="P21" s="286"/>
+      <c r="Q21" s="286"/>
+      <c r="R21" s="286"/>
+      <c r="S21" s="286"/>
+      <c r="T21" s="286"/>
+      <c r="U21" s="286"/>
+      <c r="V21" s="286"/>
+      <c r="W21" s="286"/>
+      <c r="X21" s="286"/>
+      <c r="Y21" s="286"/>
+      <c r="Z21" s="286"/>
+      <c r="AA21" s="286"/>
+      <c r="AB21" s="286"/>
+      <c r="AC21" s="286"/>
+      <c r="AD21" s="286"/>
+      <c r="AE21" s="286"/>
+      <c r="AF21" s="286"/>
+      <c r="AG21" s="286"/>
+      <c r="AH21" s="287"/>
+      <c r="AI21" s="296"/>
+      <c r="AJ21" s="297"/>
+      <c r="AK21" s="297"/>
+      <c r="AL21" s="298"/>
+    </row>
+    <row r="22" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B22" s="285"/>
+      <c r="C22" s="286"/>
+      <c r="D22" s="286"/>
+      <c r="E22" s="286"/>
+      <c r="F22" s="286"/>
+      <c r="G22" s="286"/>
+      <c r="H22" s="286"/>
+      <c r="I22" s="286"/>
+      <c r="J22" s="286"/>
+      <c r="K22" s="286"/>
+      <c r="L22" s="286"/>
+      <c r="M22" s="286"/>
+      <c r="N22" s="286"/>
+      <c r="O22" s="286"/>
+      <c r="P22" s="286"/>
+      <c r="Q22" s="286"/>
+      <c r="R22" s="286"/>
+      <c r="S22" s="286"/>
+      <c r="T22" s="286"/>
+      <c r="U22" s="286"/>
+      <c r="V22" s="286"/>
+      <c r="W22" s="286"/>
+      <c r="X22" s="286"/>
+      <c r="Y22" s="286"/>
+      <c r="Z22" s="286"/>
+      <c r="AA22" s="286"/>
+      <c r="AB22" s="286"/>
+      <c r="AC22" s="286"/>
+      <c r="AD22" s="286"/>
+      <c r="AE22" s="286"/>
+      <c r="AF22" s="286"/>
+      <c r="AG22" s="286"/>
+      <c r="AH22" s="287"/>
+      <c r="AI22" s="299"/>
+      <c r="AJ22" s="300"/>
+      <c r="AK22" s="300"/>
+      <c r="AL22" s="301"/>
+    </row>
+    <row r="23" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B23" s="285"/>
+      <c r="C23" s="286"/>
+      <c r="D23" s="286"/>
+      <c r="E23" s="286"/>
+      <c r="F23" s="286"/>
+      <c r="G23" s="286"/>
+      <c r="H23" s="286"/>
+      <c r="I23" s="286"/>
+      <c r="J23" s="286"/>
+      <c r="K23" s="286"/>
+      <c r="L23" s="286"/>
+      <c r="M23" s="286"/>
+      <c r="N23" s="286"/>
+      <c r="O23" s="286"/>
+      <c r="P23" s="286"/>
+      <c r="Q23" s="286"/>
+      <c r="R23" s="286"/>
+      <c r="S23" s="286"/>
+      <c r="T23" s="286"/>
+      <c r="U23" s="286"/>
+      <c r="V23" s="286"/>
+      <c r="W23" s="286"/>
+      <c r="X23" s="286"/>
+      <c r="Y23" s="286"/>
+      <c r="Z23" s="286"/>
+      <c r="AA23" s="286"/>
+      <c r="AB23" s="286"/>
+      <c r="AC23" s="286"/>
+      <c r="AD23" s="286"/>
+      <c r="AE23" s="286"/>
+      <c r="AF23" s="286"/>
+      <c r="AG23" s="286"/>
+      <c r="AH23" s="287"/>
+      <c r="AI23" s="302"/>
+      <c r="AJ23" s="303"/>
+      <c r="AK23" s="303"/>
+      <c r="AL23" s="304"/>
+    </row>
+    <row r="24" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.95">
+      <c r="B24" s="285"/>
+      <c r="C24" s="286"/>
+      <c r="D24" s="286"/>
+      <c r="E24" s="286"/>
+      <c r="F24" s="286"/>
+      <c r="G24" s="286"/>
+      <c r="H24" s="286"/>
+      <c r="I24" s="286"/>
+      <c r="J24" s="286"/>
+      <c r="K24" s="286"/>
+      <c r="L24" s="286"/>
+      <c r="M24" s="286"/>
+      <c r="N24" s="286"/>
+      <c r="O24" s="286"/>
+      <c r="P24" s="286"/>
+      <c r="Q24" s="286"/>
+      <c r="R24" s="286"/>
+      <c r="S24" s="286"/>
+      <c r="T24" s="286"/>
+      <c r="U24" s="286"/>
+      <c r="V24" s="286"/>
+      <c r="W24" s="286"/>
+      <c r="X24" s="286"/>
+      <c r="Y24" s="286"/>
+      <c r="Z24" s="286"/>
+      <c r="AA24" s="286"/>
+      <c r="AB24" s="286"/>
+      <c r="AC24" s="286"/>
+      <c r="AD24" s="286"/>
+      <c r="AE24" s="286"/>
+      <c r="AF24" s="286"/>
+      <c r="AG24" s="286"/>
+      <c r="AH24" s="287"/>
+      <c r="AI24" s="291" t="s">
         <v>90</v>
       </c>
-      <c r="AJ24" s="304"/>
-      <c r="AK24" s="304"/>
-      <c r="AL24" s="304"/>
-    </row>
-    <row r="25" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B25" s="298"/>
-      <c r="C25" s="299"/>
-      <c r="D25" s="299"/>
-      <c r="E25" s="299"/>
-      <c r="F25" s="299"/>
-      <c r="G25" s="299"/>
-      <c r="H25" s="299"/>
-      <c r="I25" s="299"/>
-      <c r="J25" s="299"/>
-      <c r="K25" s="299"/>
-      <c r="L25" s="299"/>
-      <c r="M25" s="299"/>
-      <c r="N25" s="299"/>
-      <c r="O25" s="299"/>
-      <c r="P25" s="299"/>
-      <c r="Q25" s="299"/>
-      <c r="R25" s="299"/>
-      <c r="S25" s="299"/>
-      <c r="T25" s="299"/>
-      <c r="U25" s="299"/>
-      <c r="V25" s="299"/>
-      <c r="W25" s="299"/>
-      <c r="X25" s="299"/>
-      <c r="Y25" s="299"/>
-      <c r="Z25" s="299"/>
-      <c r="AA25" s="299"/>
-      <c r="AB25" s="299"/>
-      <c r="AC25" s="299"/>
-      <c r="AD25" s="299"/>
-      <c r="AE25" s="299"/>
-      <c r="AF25" s="299"/>
-      <c r="AG25" s="299"/>
-      <c r="AH25" s="300"/>
-      <c r="AI25" s="308"/>
-      <c r="AJ25" s="309"/>
-      <c r="AK25" s="309"/>
-      <c r="AL25" s="310"/>
-    </row>
-    <row r="26" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B26" s="298"/>
-      <c r="C26" s="299"/>
-      <c r="D26" s="299"/>
-      <c r="E26" s="299"/>
-      <c r="F26" s="299"/>
-      <c r="G26" s="299"/>
-      <c r="H26" s="299"/>
-      <c r="I26" s="299"/>
-      <c r="J26" s="299"/>
-      <c r="K26" s="299"/>
-      <c r="L26" s="299"/>
-      <c r="M26" s="299"/>
-      <c r="N26" s="299"/>
-      <c r="O26" s="299"/>
-      <c r="P26" s="299"/>
-      <c r="Q26" s="299"/>
-      <c r="R26" s="299"/>
-      <c r="S26" s="299"/>
-      <c r="T26" s="299"/>
-      <c r="U26" s="299"/>
-      <c r="V26" s="299"/>
-      <c r="W26" s="299"/>
-      <c r="X26" s="299"/>
-      <c r="Y26" s="299"/>
-      <c r="Z26" s="299"/>
-      <c r="AA26" s="299"/>
-      <c r="AB26" s="299"/>
-      <c r="AC26" s="299"/>
-      <c r="AD26" s="299"/>
-      <c r="AE26" s="299"/>
-      <c r="AF26" s="299"/>
-      <c r="AG26" s="299"/>
-      <c r="AH26" s="300"/>
-      <c r="AI26" s="311"/>
-      <c r="AJ26" s="312"/>
-      <c r="AK26" s="312"/>
-      <c r="AL26" s="313"/>
-    </row>
-    <row r="27" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B27" s="298"/>
-      <c r="C27" s="299"/>
-      <c r="D27" s="299"/>
-      <c r="E27" s="299"/>
-      <c r="F27" s="299"/>
-      <c r="G27" s="299"/>
-      <c r="H27" s="299"/>
-      <c r="I27" s="299"/>
-      <c r="J27" s="299"/>
-      <c r="K27" s="299"/>
-      <c r="L27" s="299"/>
-      <c r="M27" s="299"/>
-      <c r="N27" s="299"/>
-      <c r="O27" s="299"/>
-      <c r="P27" s="299"/>
-      <c r="Q27" s="299"/>
-      <c r="R27" s="299"/>
-      <c r="S27" s="299"/>
-      <c r="T27" s="299"/>
-      <c r="U27" s="299"/>
-      <c r="V27" s="299"/>
-      <c r="W27" s="299"/>
-      <c r="X27" s="299"/>
-      <c r="Y27" s="299"/>
-      <c r="Z27" s="299"/>
-      <c r="AA27" s="299"/>
-      <c r="AB27" s="299"/>
-      <c r="AC27" s="299"/>
-      <c r="AD27" s="299"/>
-      <c r="AE27" s="299"/>
-      <c r="AF27" s="299"/>
-      <c r="AG27" s="299"/>
-      <c r="AH27" s="300"/>
-      <c r="AI27" s="314"/>
-      <c r="AJ27" s="315"/>
-      <c r="AK27" s="315"/>
-      <c r="AL27" s="316"/>
-    </row>
-    <row r="28" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B28" s="298"/>
-      <c r="C28" s="299"/>
-      <c r="D28" s="299"/>
-      <c r="E28" s="299"/>
-      <c r="F28" s="299"/>
-      <c r="G28" s="299"/>
-      <c r="H28" s="299"/>
-      <c r="I28" s="299"/>
-      <c r="J28" s="299"/>
-      <c r="K28" s="299"/>
-      <c r="L28" s="299"/>
-      <c r="M28" s="299"/>
-      <c r="N28" s="299"/>
-      <c r="O28" s="299"/>
-      <c r="P28" s="299"/>
-      <c r="Q28" s="299"/>
-      <c r="R28" s="299"/>
-      <c r="S28" s="299"/>
-      <c r="T28" s="299"/>
-      <c r="U28" s="299"/>
-      <c r="V28" s="299"/>
-      <c r="W28" s="299"/>
-      <c r="X28" s="299"/>
-      <c r="Y28" s="299"/>
-      <c r="Z28" s="299"/>
-      <c r="AA28" s="299"/>
-      <c r="AB28" s="299"/>
-      <c r="AC28" s="299"/>
-      <c r="AD28" s="299"/>
-      <c r="AE28" s="299"/>
-      <c r="AF28" s="299"/>
-      <c r="AG28" s="299"/>
-      <c r="AH28" s="300"/>
-      <c r="AI28" s="304" t="s">
+      <c r="AJ24" s="291"/>
+      <c r="AK24" s="291"/>
+      <c r="AL24" s="291"/>
+    </row>
+    <row r="25" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B25" s="285"/>
+      <c r="C25" s="286"/>
+      <c r="D25" s="286"/>
+      <c r="E25" s="286"/>
+      <c r="F25" s="286"/>
+      <c r="G25" s="286"/>
+      <c r="H25" s="286"/>
+      <c r="I25" s="286"/>
+      <c r="J25" s="286"/>
+      <c r="K25" s="286"/>
+      <c r="L25" s="286"/>
+      <c r="M25" s="286"/>
+      <c r="N25" s="286"/>
+      <c r="O25" s="286"/>
+      <c r="P25" s="286"/>
+      <c r="Q25" s="286"/>
+      <c r="R25" s="286"/>
+      <c r="S25" s="286"/>
+      <c r="T25" s="286"/>
+      <c r="U25" s="286"/>
+      <c r="V25" s="286"/>
+      <c r="W25" s="286"/>
+      <c r="X25" s="286"/>
+      <c r="Y25" s="286"/>
+      <c r="Z25" s="286"/>
+      <c r="AA25" s="286"/>
+      <c r="AB25" s="286"/>
+      <c r="AC25" s="286"/>
+      <c r="AD25" s="286"/>
+      <c r="AE25" s="286"/>
+      <c r="AF25" s="286"/>
+      <c r="AG25" s="286"/>
+      <c r="AH25" s="287"/>
+      <c r="AI25" s="296"/>
+      <c r="AJ25" s="297"/>
+      <c r="AK25" s="297"/>
+      <c r="AL25" s="298"/>
+    </row>
+    <row r="26" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B26" s="285"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="286"/>
+      <c r="E26" s="286"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
+      <c r="H26" s="286"/>
+      <c r="I26" s="286"/>
+      <c r="J26" s="286"/>
+      <c r="K26" s="286"/>
+      <c r="L26" s="286"/>
+      <c r="M26" s="286"/>
+      <c r="N26" s="286"/>
+      <c r="O26" s="286"/>
+      <c r="P26" s="286"/>
+      <c r="Q26" s="286"/>
+      <c r="R26" s="286"/>
+      <c r="S26" s="286"/>
+      <c r="T26" s="286"/>
+      <c r="U26" s="286"/>
+      <c r="V26" s="286"/>
+      <c r="W26" s="286"/>
+      <c r="X26" s="286"/>
+      <c r="Y26" s="286"/>
+      <c r="Z26" s="286"/>
+      <c r="AA26" s="286"/>
+      <c r="AB26" s="286"/>
+      <c r="AC26" s="286"/>
+      <c r="AD26" s="286"/>
+      <c r="AE26" s="286"/>
+      <c r="AF26" s="286"/>
+      <c r="AG26" s="286"/>
+      <c r="AH26" s="287"/>
+      <c r="AI26" s="299"/>
+      <c r="AJ26" s="300"/>
+      <c r="AK26" s="300"/>
+      <c r="AL26" s="301"/>
+    </row>
+    <row r="27" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B27" s="285"/>
+      <c r="C27" s="286"/>
+      <c r="D27" s="286"/>
+      <c r="E27" s="286"/>
+      <c r="F27" s="286"/>
+      <c r="G27" s="286"/>
+      <c r="H27" s="286"/>
+      <c r="I27" s="286"/>
+      <c r="J27" s="286"/>
+      <c r="K27" s="286"/>
+      <c r="L27" s="286"/>
+      <c r="M27" s="286"/>
+      <c r="N27" s="286"/>
+      <c r="O27" s="286"/>
+      <c r="P27" s="286"/>
+      <c r="Q27" s="286"/>
+      <c r="R27" s="286"/>
+      <c r="S27" s="286"/>
+      <c r="T27" s="286"/>
+      <c r="U27" s="286"/>
+      <c r="V27" s="286"/>
+      <c r="W27" s="286"/>
+      <c r="X27" s="286"/>
+      <c r="Y27" s="286"/>
+      <c r="Z27" s="286"/>
+      <c r="AA27" s="286"/>
+      <c r="AB27" s="286"/>
+      <c r="AC27" s="286"/>
+      <c r="AD27" s="286"/>
+      <c r="AE27" s="286"/>
+      <c r="AF27" s="286"/>
+      <c r="AG27" s="286"/>
+      <c r="AH27" s="287"/>
+      <c r="AI27" s="302"/>
+      <c r="AJ27" s="303"/>
+      <c r="AK27" s="303"/>
+      <c r="AL27" s="304"/>
+    </row>
+    <row r="28" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.95">
+      <c r="B28" s="285"/>
+      <c r="C28" s="286"/>
+      <c r="D28" s="286"/>
+      <c r="E28" s="286"/>
+      <c r="F28" s="286"/>
+      <c r="G28" s="286"/>
+      <c r="H28" s="286"/>
+      <c r="I28" s="286"/>
+      <c r="J28" s="286"/>
+      <c r="K28" s="286"/>
+      <c r="L28" s="286"/>
+      <c r="M28" s="286"/>
+      <c r="N28" s="286"/>
+      <c r="O28" s="286"/>
+      <c r="P28" s="286"/>
+      <c r="Q28" s="286"/>
+      <c r="R28" s="286"/>
+      <c r="S28" s="286"/>
+      <c r="T28" s="286"/>
+      <c r="U28" s="286"/>
+      <c r="V28" s="286"/>
+      <c r="W28" s="286"/>
+      <c r="X28" s="286"/>
+      <c r="Y28" s="286"/>
+      <c r="Z28" s="286"/>
+      <c r="AA28" s="286"/>
+      <c r="AB28" s="286"/>
+      <c r="AC28" s="286"/>
+      <c r="AD28" s="286"/>
+      <c r="AE28" s="286"/>
+      <c r="AF28" s="286"/>
+      <c r="AG28" s="286"/>
+      <c r="AH28" s="287"/>
+      <c r="AI28" s="291" t="s">
         <v>91</v>
       </c>
-      <c r="AJ28" s="304"/>
-      <c r="AK28" s="304"/>
-      <c r="AL28" s="304"/>
-    </row>
-    <row r="29" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B29" s="298"/>
-      <c r="C29" s="299"/>
-      <c r="D29" s="299"/>
-      <c r="E29" s="299"/>
-      <c r="F29" s="299"/>
-      <c r="G29" s="299"/>
-      <c r="H29" s="299"/>
-      <c r="I29" s="299"/>
-      <c r="J29" s="299"/>
-      <c r="K29" s="299"/>
-      <c r="L29" s="299"/>
-      <c r="M29" s="299"/>
-      <c r="N29" s="299"/>
-      <c r="O29" s="299"/>
-      <c r="P29" s="299"/>
-      <c r="Q29" s="299"/>
-      <c r="R29" s="299"/>
-      <c r="S29" s="299"/>
-      <c r="T29" s="299"/>
-      <c r="U29" s="299"/>
-      <c r="V29" s="299"/>
-      <c r="W29" s="299"/>
-      <c r="X29" s="299"/>
-      <c r="Y29" s="299"/>
-      <c r="Z29" s="299"/>
-      <c r="AA29" s="299"/>
-      <c r="AB29" s="299"/>
-      <c r="AC29" s="299"/>
-      <c r="AD29" s="299"/>
-      <c r="AE29" s="299"/>
-      <c r="AF29" s="299"/>
-      <c r="AG29" s="299"/>
-      <c r="AH29" s="300"/>
-      <c r="AI29" s="308"/>
-      <c r="AJ29" s="309"/>
-      <c r="AK29" s="309"/>
-      <c r="AL29" s="310"/>
-    </row>
-    <row r="30" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B30" s="298"/>
-      <c r="C30" s="299"/>
-      <c r="D30" s="299"/>
-      <c r="E30" s="299"/>
-      <c r="F30" s="299"/>
-      <c r="G30" s="299"/>
-      <c r="H30" s="299"/>
-      <c r="I30" s="299"/>
-      <c r="J30" s="299"/>
-      <c r="K30" s="299"/>
-      <c r="L30" s="299"/>
-      <c r="M30" s="299"/>
-      <c r="N30" s="299"/>
-      <c r="O30" s="299"/>
-      <c r="P30" s="299"/>
-      <c r="Q30" s="299"/>
-      <c r="R30" s="299"/>
-      <c r="S30" s="299"/>
-      <c r="T30" s="299"/>
-      <c r="U30" s="299"/>
-      <c r="V30" s="299"/>
-      <c r="W30" s="299"/>
-      <c r="X30" s="299"/>
-      <c r="Y30" s="299"/>
-      <c r="Z30" s="299"/>
-      <c r="AA30" s="299"/>
-      <c r="AB30" s="299"/>
-      <c r="AC30" s="299"/>
-      <c r="AD30" s="299"/>
-      <c r="AE30" s="299"/>
-      <c r="AF30" s="299"/>
-      <c r="AG30" s="299"/>
-      <c r="AH30" s="300"/>
-      <c r="AI30" s="311"/>
-      <c r="AJ30" s="312"/>
-      <c r="AK30" s="312"/>
-      <c r="AL30" s="313"/>
-    </row>
-    <row r="31" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="298"/>
-      <c r="C31" s="299"/>
-      <c r="D31" s="299"/>
-      <c r="E31" s="299"/>
-      <c r="F31" s="299"/>
-      <c r="G31" s="299"/>
-      <c r="H31" s="299"/>
-      <c r="I31" s="299"/>
-      <c r="J31" s="299"/>
-      <c r="K31" s="299"/>
-      <c r="L31" s="299"/>
-      <c r="M31" s="299"/>
-      <c r="N31" s="299"/>
-      <c r="O31" s="299"/>
-      <c r="P31" s="299"/>
-      <c r="Q31" s="299"/>
-      <c r="R31" s="299"/>
-      <c r="S31" s="299"/>
-      <c r="T31" s="299"/>
-      <c r="U31" s="299"/>
-      <c r="V31" s="299"/>
-      <c r="W31" s="299"/>
-      <c r="X31" s="299"/>
-      <c r="Y31" s="299"/>
-      <c r="Z31" s="299"/>
-      <c r="AA31" s="299"/>
-      <c r="AB31" s="299"/>
-      <c r="AC31" s="299"/>
-      <c r="AD31" s="299"/>
-      <c r="AE31" s="299"/>
-      <c r="AF31" s="299"/>
-      <c r="AG31" s="299"/>
-      <c r="AH31" s="300"/>
-      <c r="AI31" s="314"/>
-      <c r="AJ31" s="315"/>
-      <c r="AK31" s="315"/>
-      <c r="AL31" s="316"/>
-    </row>
-    <row r="32" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B32" s="298"/>
-      <c r="C32" s="299"/>
-      <c r="D32" s="299"/>
-      <c r="E32" s="299"/>
-      <c r="F32" s="299"/>
-      <c r="G32" s="299"/>
-      <c r="H32" s="299"/>
-      <c r="I32" s="299"/>
-      <c r="J32" s="299"/>
-      <c r="K32" s="299"/>
-      <c r="L32" s="299"/>
-      <c r="M32" s="299"/>
-      <c r="N32" s="299"/>
-      <c r="O32" s="299"/>
-      <c r="P32" s="299"/>
-      <c r="Q32" s="299"/>
-      <c r="R32" s="299"/>
-      <c r="S32" s="299"/>
-      <c r="T32" s="299"/>
-      <c r="U32" s="299"/>
-      <c r="V32" s="299"/>
-      <c r="W32" s="299"/>
-      <c r="X32" s="299"/>
-      <c r="Y32" s="299"/>
-      <c r="Z32" s="299"/>
-      <c r="AA32" s="299"/>
-      <c r="AB32" s="299"/>
-      <c r="AC32" s="299"/>
-      <c r="AD32" s="299"/>
-      <c r="AE32" s="299"/>
-      <c r="AF32" s="299"/>
-      <c r="AG32" s="299"/>
-      <c r="AH32" s="300"/>
-      <c r="AI32" s="306" t="s">
+      <c r="AJ28" s="291"/>
+      <c r="AK28" s="291"/>
+      <c r="AL28" s="291"/>
+    </row>
+    <row r="29" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B29" s="285"/>
+      <c r="C29" s="286"/>
+      <c r="D29" s="286"/>
+      <c r="E29" s="286"/>
+      <c r="F29" s="286"/>
+      <c r="G29" s="286"/>
+      <c r="H29" s="286"/>
+      <c r="I29" s="286"/>
+      <c r="J29" s="286"/>
+      <c r="K29" s="286"/>
+      <c r="L29" s="286"/>
+      <c r="M29" s="286"/>
+      <c r="N29" s="286"/>
+      <c r="O29" s="286"/>
+      <c r="P29" s="286"/>
+      <c r="Q29" s="286"/>
+      <c r="R29" s="286"/>
+      <c r="S29" s="286"/>
+      <c r="T29" s="286"/>
+      <c r="U29" s="286"/>
+      <c r="V29" s="286"/>
+      <c r="W29" s="286"/>
+      <c r="X29" s="286"/>
+      <c r="Y29" s="286"/>
+      <c r="Z29" s="286"/>
+      <c r="AA29" s="286"/>
+      <c r="AB29" s="286"/>
+      <c r="AC29" s="286"/>
+      <c r="AD29" s="286"/>
+      <c r="AE29" s="286"/>
+      <c r="AF29" s="286"/>
+      <c r="AG29" s="286"/>
+      <c r="AH29" s="287"/>
+      <c r="AI29" s="296"/>
+      <c r="AJ29" s="297"/>
+      <c r="AK29" s="297"/>
+      <c r="AL29" s="298"/>
+    </row>
+    <row r="30" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B30" s="285"/>
+      <c r="C30" s="286"/>
+      <c r="D30" s="286"/>
+      <c r="E30" s="286"/>
+      <c r="F30" s="286"/>
+      <c r="G30" s="286"/>
+      <c r="H30" s="286"/>
+      <c r="I30" s="286"/>
+      <c r="J30" s="286"/>
+      <c r="K30" s="286"/>
+      <c r="L30" s="286"/>
+      <c r="M30" s="286"/>
+      <c r="N30" s="286"/>
+      <c r="O30" s="286"/>
+      <c r="P30" s="286"/>
+      <c r="Q30" s="286"/>
+      <c r="R30" s="286"/>
+      <c r="S30" s="286"/>
+      <c r="T30" s="286"/>
+      <c r="U30" s="286"/>
+      <c r="V30" s="286"/>
+      <c r="W30" s="286"/>
+      <c r="X30" s="286"/>
+      <c r="Y30" s="286"/>
+      <c r="Z30" s="286"/>
+      <c r="AA30" s="286"/>
+      <c r="AB30" s="286"/>
+      <c r="AC30" s="286"/>
+      <c r="AD30" s="286"/>
+      <c r="AE30" s="286"/>
+      <c r="AF30" s="286"/>
+      <c r="AG30" s="286"/>
+      <c r="AH30" s="287"/>
+      <c r="AI30" s="299"/>
+      <c r="AJ30" s="300"/>
+      <c r="AK30" s="300"/>
+      <c r="AL30" s="301"/>
+    </row>
+    <row r="31" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B31" s="285"/>
+      <c r="C31" s="286"/>
+      <c r="D31" s="286"/>
+      <c r="E31" s="286"/>
+      <c r="F31" s="286"/>
+      <c r="G31" s="286"/>
+      <c r="H31" s="286"/>
+      <c r="I31" s="286"/>
+      <c r="J31" s="286"/>
+      <c r="K31" s="286"/>
+      <c r="L31" s="286"/>
+      <c r="M31" s="286"/>
+      <c r="N31" s="286"/>
+      <c r="O31" s="286"/>
+      <c r="P31" s="286"/>
+      <c r="Q31" s="286"/>
+      <c r="R31" s="286"/>
+      <c r="S31" s="286"/>
+      <c r="T31" s="286"/>
+      <c r="U31" s="286"/>
+      <c r="V31" s="286"/>
+      <c r="W31" s="286"/>
+      <c r="X31" s="286"/>
+      <c r="Y31" s="286"/>
+      <c r="Z31" s="286"/>
+      <c r="AA31" s="286"/>
+      <c r="AB31" s="286"/>
+      <c r="AC31" s="286"/>
+      <c r="AD31" s="286"/>
+      <c r="AE31" s="286"/>
+      <c r="AF31" s="286"/>
+      <c r="AG31" s="286"/>
+      <c r="AH31" s="287"/>
+      <c r="AI31" s="302"/>
+      <c r="AJ31" s="303"/>
+      <c r="AK31" s="303"/>
+      <c r="AL31" s="304"/>
+    </row>
+    <row r="32" spans="2:40" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B32" s="285"/>
+      <c r="C32" s="286"/>
+      <c r="D32" s="286"/>
+      <c r="E32" s="286"/>
+      <c r="F32" s="286"/>
+      <c r="G32" s="286"/>
+      <c r="H32" s="286"/>
+      <c r="I32" s="286"/>
+      <c r="J32" s="286"/>
+      <c r="K32" s="286"/>
+      <c r="L32" s="286"/>
+      <c r="M32" s="286"/>
+      <c r="N32" s="286"/>
+      <c r="O32" s="286"/>
+      <c r="P32" s="286"/>
+      <c r="Q32" s="286"/>
+      <c r="R32" s="286"/>
+      <c r="S32" s="286"/>
+      <c r="T32" s="286"/>
+      <c r="U32" s="286"/>
+      <c r="V32" s="286"/>
+      <c r="W32" s="286"/>
+      <c r="X32" s="286"/>
+      <c r="Y32" s="286"/>
+      <c r="Z32" s="286"/>
+      <c r="AA32" s="286"/>
+      <c r="AB32" s="286"/>
+      <c r="AC32" s="286"/>
+      <c r="AD32" s="286"/>
+      <c r="AE32" s="286"/>
+      <c r="AF32" s="286"/>
+      <c r="AG32" s="286"/>
+      <c r="AH32" s="287"/>
+      <c r="AI32" s="293" t="s">
         <v>25</v>
       </c>
-      <c r="AJ32" s="306"/>
-      <c r="AK32" s="306"/>
-      <c r="AL32" s="306"/>
+      <c r="AJ32" s="293"/>
+      <c r="AK32" s="293"/>
+      <c r="AL32" s="293"/>
       <c r="AM32" s="166"/>
       <c r="AN32" s="166"/>
     </row>
-    <row r="33" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B33" s="298"/>
-      <c r="C33" s="299"/>
-      <c r="D33" s="299"/>
-      <c r="E33" s="299"/>
-      <c r="F33" s="299"/>
-      <c r="G33" s="299"/>
-      <c r="H33" s="299"/>
-      <c r="I33" s="299"/>
-      <c r="J33" s="299"/>
-      <c r="K33" s="299"/>
-      <c r="L33" s="299"/>
-      <c r="M33" s="299"/>
-      <c r="N33" s="299"/>
-      <c r="O33" s="299"/>
-      <c r="P33" s="299"/>
-      <c r="Q33" s="299"/>
-      <c r="R33" s="299"/>
-      <c r="S33" s="299"/>
-      <c r="T33" s="299"/>
-      <c r="U33" s="299"/>
-      <c r="V33" s="299"/>
-      <c r="W33" s="299"/>
-      <c r="X33" s="299"/>
-      <c r="Y33" s="299"/>
-      <c r="Z33" s="299"/>
-      <c r="AA33" s="299"/>
-      <c r="AB33" s="299"/>
-      <c r="AC33" s="299"/>
-      <c r="AD33" s="299"/>
-      <c r="AE33" s="299"/>
-      <c r="AF33" s="299"/>
-      <c r="AG33" s="299"/>
-      <c r="AH33" s="300"/>
-      <c r="AI33" s="286"/>
-      <c r="AJ33" s="287"/>
-      <c r="AK33" s="287"/>
-      <c r="AL33" s="288"/>
+    <row r="33" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B33" s="285"/>
+      <c r="C33" s="286"/>
+      <c r="D33" s="286"/>
+      <c r="E33" s="286"/>
+      <c r="F33" s="286"/>
+      <c r="G33" s="286"/>
+      <c r="H33" s="286"/>
+      <c r="I33" s="286"/>
+      <c r="J33" s="286"/>
+      <c r="K33" s="286"/>
+      <c r="L33" s="286"/>
+      <c r="M33" s="286"/>
+      <c r="N33" s="286"/>
+      <c r="O33" s="286"/>
+      <c r="P33" s="286"/>
+      <c r="Q33" s="286"/>
+      <c r="R33" s="286"/>
+      <c r="S33" s="286"/>
+      <c r="T33" s="286"/>
+      <c r="U33" s="286"/>
+      <c r="V33" s="286"/>
+      <c r="W33" s="286"/>
+      <c r="X33" s="286"/>
+      <c r="Y33" s="286"/>
+      <c r="Z33" s="286"/>
+      <c r="AA33" s="286"/>
+      <c r="AB33" s="286"/>
+      <c r="AC33" s="286"/>
+      <c r="AD33" s="286"/>
+      <c r="AE33" s="286"/>
+      <c r="AF33" s="286"/>
+      <c r="AG33" s="286"/>
+      <c r="AH33" s="287"/>
+      <c r="AI33" s="273"/>
+      <c r="AJ33" s="274"/>
+      <c r="AK33" s="274"/>
+      <c r="AL33" s="275"/>
       <c r="AM33" s="166"/>
       <c r="AN33" s="166"/>
     </row>
-    <row r="34" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B34" s="298"/>
-      <c r="C34" s="299"/>
-      <c r="D34" s="299"/>
-      <c r="E34" s="299"/>
-      <c r="F34" s="299"/>
-      <c r="G34" s="299"/>
-      <c r="H34" s="299"/>
-      <c r="I34" s="299"/>
-      <c r="J34" s="299"/>
-      <c r="K34" s="299"/>
-      <c r="L34" s="299"/>
-      <c r="M34" s="299"/>
-      <c r="N34" s="299"/>
-      <c r="O34" s="299"/>
-      <c r="P34" s="299"/>
-      <c r="Q34" s="299"/>
-      <c r="R34" s="299"/>
-      <c r="S34" s="299"/>
-      <c r="T34" s="299"/>
-      <c r="U34" s="299"/>
-      <c r="V34" s="299"/>
-      <c r="W34" s="299"/>
-      <c r="X34" s="299"/>
-      <c r="Y34" s="299"/>
-      <c r="Z34" s="299"/>
-      <c r="AA34" s="299"/>
-      <c r="AB34" s="299"/>
-      <c r="AC34" s="299"/>
-      <c r="AD34" s="299"/>
-      <c r="AE34" s="299"/>
-      <c r="AF34" s="299"/>
-      <c r="AG34" s="299"/>
-      <c r="AH34" s="300"/>
-      <c r="AI34" s="289"/>
-      <c r="AJ34" s="290"/>
-      <c r="AK34" s="290"/>
-      <c r="AL34" s="291"/>
+    <row r="34" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B34" s="285"/>
+      <c r="C34" s="286"/>
+      <c r="D34" s="286"/>
+      <c r="E34" s="286"/>
+      <c r="F34" s="286"/>
+      <c r="G34" s="286"/>
+      <c r="H34" s="286"/>
+      <c r="I34" s="286"/>
+      <c r="J34" s="286"/>
+      <c r="K34" s="286"/>
+      <c r="L34" s="286"/>
+      <c r="M34" s="286"/>
+      <c r="N34" s="286"/>
+      <c r="O34" s="286"/>
+      <c r="P34" s="286"/>
+      <c r="Q34" s="286"/>
+      <c r="R34" s="286"/>
+      <c r="S34" s="286"/>
+      <c r="T34" s="286"/>
+      <c r="U34" s="286"/>
+      <c r="V34" s="286"/>
+      <c r="W34" s="286"/>
+      <c r="X34" s="286"/>
+      <c r="Y34" s="286"/>
+      <c r="Z34" s="286"/>
+      <c r="AA34" s="286"/>
+      <c r="AB34" s="286"/>
+      <c r="AC34" s="286"/>
+      <c r="AD34" s="286"/>
+      <c r="AE34" s="286"/>
+      <c r="AF34" s="286"/>
+      <c r="AG34" s="286"/>
+      <c r="AH34" s="287"/>
+      <c r="AI34" s="276"/>
+      <c r="AJ34" s="277"/>
+      <c r="AK34" s="277"/>
+      <c r="AL34" s="278"/>
       <c r="AM34" s="166"/>
       <c r="AN34" s="166"/>
     </row>
-    <row r="35" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B35" s="301"/>
-      <c r="C35" s="302"/>
-      <c r="D35" s="302"/>
-      <c r="E35" s="302"/>
-      <c r="F35" s="302"/>
-      <c r="G35" s="302"/>
-      <c r="H35" s="302"/>
-      <c r="I35" s="302"/>
-      <c r="J35" s="302"/>
-      <c r="K35" s="302"/>
-      <c r="L35" s="302"/>
-      <c r="M35" s="302"/>
-      <c r="N35" s="302"/>
-      <c r="O35" s="302"/>
-      <c r="P35" s="302"/>
-      <c r="Q35" s="302"/>
-      <c r="R35" s="302"/>
-      <c r="S35" s="302"/>
-      <c r="T35" s="302"/>
-      <c r="U35" s="302"/>
-      <c r="V35" s="302"/>
-      <c r="W35" s="302"/>
-      <c r="X35" s="302"/>
-      <c r="Y35" s="302"/>
-      <c r="Z35" s="302"/>
-      <c r="AA35" s="302"/>
-      <c r="AB35" s="302"/>
-      <c r="AC35" s="302"/>
-      <c r="AD35" s="302"/>
-      <c r="AE35" s="302"/>
-      <c r="AF35" s="302"/>
-      <c r="AG35" s="302"/>
-      <c r="AH35" s="303"/>
-      <c r="AI35" s="292"/>
-      <c r="AJ35" s="293"/>
-      <c r="AK35" s="293"/>
-      <c r="AL35" s="294"/>
+    <row r="35" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B35" s="288"/>
+      <c r="C35" s="289"/>
+      <c r="D35" s="289"/>
+      <c r="E35" s="289"/>
+      <c r="F35" s="289"/>
+      <c r="G35" s="289"/>
+      <c r="H35" s="289"/>
+      <c r="I35" s="289"/>
+      <c r="J35" s="289"/>
+      <c r="K35" s="289"/>
+      <c r="L35" s="289"/>
+      <c r="M35" s="289"/>
+      <c r="N35" s="289"/>
+      <c r="O35" s="289"/>
+      <c r="P35" s="289"/>
+      <c r="Q35" s="289"/>
+      <c r="R35" s="289"/>
+      <c r="S35" s="289"/>
+      <c r="T35" s="289"/>
+      <c r="U35" s="289"/>
+      <c r="V35" s="289"/>
+      <c r="W35" s="289"/>
+      <c r="X35" s="289"/>
+      <c r="Y35" s="289"/>
+      <c r="Z35" s="289"/>
+      <c r="AA35" s="289"/>
+      <c r="AB35" s="289"/>
+      <c r="AC35" s="289"/>
+      <c r="AD35" s="289"/>
+      <c r="AE35" s="289"/>
+      <c r="AF35" s="289"/>
+      <c r="AG35" s="289"/>
+      <c r="AH35" s="290"/>
+      <c r="AI35" s="279"/>
+      <c r="AJ35" s="280"/>
+      <c r="AK35" s="280"/>
+      <c r="AL35" s="281"/>
       <c r="AM35" s="166"/>
       <c r="AN35" s="166"/>
     </row>
-    <row r="36" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AL36" s="166"/>
       <c r="AM36" s="166"/>
       <c r="AN36" s="166"/>
     </row>
-    <row r="37" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AL37" s="166"/>
       <c r="AM37" s="166"/>
       <c r="AN37" s="166"/>
     </row>
-    <row r="38" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:43" ht="24.9" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AL38" s="166"/>
       <c r="AM38" s="166"/>
       <c r="AN38" s="166"/>
     </row>
-    <row r="39" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AL39" s="166"/>
       <c r="AM39" s="166"/>
       <c r="AN39" s="166"/>
     </row>
-    <row r="40" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AL40" s="166"/>
       <c r="AM40" s="166"/>
       <c r="AN40" s="166"/>
     </row>
-    <row r="42" spans="2:43" s="177" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="43" spans="2:43" s="177" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.5"/>
-    <row r="44" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:43" s="177" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="43" spans="2:43" s="177" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="44" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AF44" s="177"/>
       <c r="AG44" s="177"/>
       <c r="AH44" s="177"/>
@@ -12861,7 +12827,7 @@
       <c r="AP44" s="177"/>
       <c r="AQ44" s="177"/>
     </row>
-    <row r="45" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AF45" s="177"/>
       <c r="AG45" s="177"/>
       <c r="AH45" s="177"/>
@@ -12875,7 +12841,7 @@
       <c r="AP45" s="177"/>
       <c r="AQ45" s="177"/>
     </row>
-    <row r="46" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AF46" s="177"/>
       <c r="AG46" s="177"/>
       <c r="AH46" s="177"/>
@@ -12889,7 +12855,7 @@
       <c r="AP46" s="177"/>
       <c r="AQ46" s="177"/>
     </row>
-    <row r="47" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:43" ht="24" customHeight="1" x14ac:dyDescent="0.85">
       <c r="AF47" s="177"/>
       <c r="AG47" s="177"/>
       <c r="AH47" s="177"/>
@@ -12905,14 +12871,22 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B1:V1"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="AD3:AL3"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AL4"/>
+    <mergeCell ref="K3:AC3"/>
+    <mergeCell ref="K4:AC4"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="V5:W6"/>
+    <mergeCell ref="AA5:AB6"/>
+    <mergeCell ref="AD5:AF6"/>
+    <mergeCell ref="AG5:AI6"/>
+    <mergeCell ref="AJ5:AL6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:R6"/>
     <mergeCell ref="AI33:AL35"/>
     <mergeCell ref="B7:AH35"/>
     <mergeCell ref="AI7:AL7"/>
@@ -12929,22 +12903,14 @@
     <mergeCell ref="AI28:AL28"/>
     <mergeCell ref="AI29:AL31"/>
     <mergeCell ref="AI32:AL32"/>
-    <mergeCell ref="AD5:AF6"/>
-    <mergeCell ref="AG5:AI6"/>
-    <mergeCell ref="AJ5:AL6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:R6"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:R5"/>
-    <mergeCell ref="V5:W6"/>
-    <mergeCell ref="AA5:AB6"/>
-    <mergeCell ref="AD3:AL3"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AL4"/>
-    <mergeCell ref="K3:AC3"/>
-    <mergeCell ref="K4:AC4"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="E5:J5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
@@ -12957,178 +12923,178 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:CV58"/>
-  <sheetFormatPr defaultColWidth="4.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="4.4609375" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="56" width="4.6640625" style="114" customWidth="1"/>
-    <col min="57" max="16384" width="4.44140625" style="114"/>
+    <col min="1" max="56" width="4.69140625" style="114" customWidth="1"/>
+    <col min="57" max="16384" width="4.4609375" style="114"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="202" t="s">
+    <row r="1" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="202"/>
-      <c r="O1" s="202"/>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
+      <c r="K1" s="242"/>
+      <c r="L1" s="242"/>
+      <c r="M1" s="242"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="242"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
       <c r="V1" s="145"/>
-      <c r="W1" s="329" t="s">
+      <c r="W1" s="337" t="s">
         <v>1</v>
       </c>
-      <c r="X1" s="329"/>
-      <c r="Y1" s="329"/>
-      <c r="Z1" s="329"/>
-      <c r="AA1" s="329"/>
-      <c r="AB1" s="329"/>
-      <c r="AC1" s="329"/>
-      <c r="AD1" s="329"/>
-      <c r="AE1" s="329"/>
-      <c r="AF1" s="329"/>
-      <c r="AG1" s="329"/>
-      <c r="AH1" s="329"/>
-      <c r="AI1" s="329"/>
-      <c r="AJ1" s="330" t="s">
+      <c r="X1" s="337"/>
+      <c r="Y1" s="337"/>
+      <c r="Z1" s="337"/>
+      <c r="AA1" s="337"/>
+      <c r="AB1" s="337"/>
+      <c r="AC1" s="337"/>
+      <c r="AD1" s="337"/>
+      <c r="AE1" s="337"/>
+      <c r="AF1" s="337"/>
+      <c r="AG1" s="337"/>
+      <c r="AH1" s="337"/>
+      <c r="AI1" s="337"/>
+      <c r="AJ1" s="338" t="s">
         <v>2</v>
       </c>
-      <c r="AK1" s="330"/>
-      <c r="AL1" s="330"/>
-      <c r="AM1" s="330"/>
-      <c r="AN1" s="330"/>
-      <c r="AO1" s="330"/>
-      <c r="AP1" s="330"/>
-      <c r="AQ1" s="330"/>
-      <c r="AR1" s="330"/>
-      <c r="AS1" s="324" t="s">
+      <c r="AK1" s="338"/>
+      <c r="AL1" s="338"/>
+      <c r="AM1" s="338"/>
+      <c r="AN1" s="338"/>
+      <c r="AO1" s="338"/>
+      <c r="AP1" s="338"/>
+      <c r="AQ1" s="338"/>
+      <c r="AR1" s="338"/>
+      <c r="AS1" s="332" t="s">
         <v>21</v>
       </c>
-      <c r="AT1" s="324"/>
-      <c r="AU1" s="324"/>
-      <c r="AV1" s="324"/>
-      <c r="AW1" s="324" t="s">
+      <c r="AT1" s="332"/>
+      <c r="AU1" s="332"/>
+      <c r="AV1" s="332"/>
+      <c r="AW1" s="332" t="s">
         <v>22</v>
       </c>
-      <c r="AX1" s="324"/>
-      <c r="AY1" s="324"/>
-      <c r="AZ1" s="324"/>
-      <c r="BA1" s="324" t="s">
+      <c r="AX1" s="332"/>
+      <c r="AY1" s="332"/>
+      <c r="AZ1" s="332"/>
+      <c r="BA1" s="332" t="s">
         <v>23</v>
       </c>
-      <c r="BB1" s="324"/>
-      <c r="BC1" s="324"/>
-      <c r="BD1" s="324"/>
-    </row>
-    <row r="2" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="317" t="s">
+      <c r="BB1" s="332"/>
+      <c r="BC1" s="332"/>
+      <c r="BD1" s="332"/>
+    </row>
+    <row r="2" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="267" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="317"/>
-      <c r="C2" s="317"/>
-      <c r="D2" s="317"/>
-      <c r="E2" s="317"/>
-      <c r="F2" s="317"/>
-      <c r="G2" s="317"/>
-      <c r="H2" s="317"/>
-      <c r="I2" s="317"/>
-      <c r="J2" s="317"/>
-      <c r="K2" s="317"/>
-      <c r="L2" s="317"/>
-      <c r="M2" s="317"/>
-      <c r="N2" s="317"/>
-      <c r="O2" s="317"/>
-      <c r="P2" s="317"/>
-      <c r="Q2" s="317"/>
-      <c r="R2" s="317"/>
-      <c r="S2" s="317"/>
-      <c r="T2" s="317"/>
-      <c r="U2" s="317"/>
-      <c r="W2" s="323" t="s">
+      <c r="B2" s="267"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="267"/>
+      <c r="J2" s="267"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="267"/>
+      <c r="N2" s="267"/>
+      <c r="O2" s="267"/>
+      <c r="P2" s="267"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="267"/>
+      <c r="S2" s="267"/>
+      <c r="T2" s="267"/>
+      <c r="U2" s="267"/>
+      <c r="W2" s="331" t="s">
         <v>0</v>
       </c>
-      <c r="X2" s="323"/>
-      <c r="Y2" s="323"/>
-      <c r="Z2" s="323"/>
-      <c r="AA2" s="323"/>
-      <c r="AB2" s="323"/>
-      <c r="AC2" s="323"/>
-      <c r="AD2" s="323"/>
-      <c r="AE2" s="323"/>
-      <c r="AF2" s="323"/>
-      <c r="AG2" s="323"/>
-      <c r="AH2" s="323"/>
-      <c r="AI2" s="323"/>
-      <c r="AJ2" s="330" t="s">
+      <c r="X2" s="331"/>
+      <c r="Y2" s="331"/>
+      <c r="Z2" s="331"/>
+      <c r="AA2" s="331"/>
+      <c r="AB2" s="331"/>
+      <c r="AC2" s="331"/>
+      <c r="AD2" s="331"/>
+      <c r="AE2" s="331"/>
+      <c r="AF2" s="331"/>
+      <c r="AG2" s="331"/>
+      <c r="AH2" s="331"/>
+      <c r="AI2" s="331"/>
+      <c r="AJ2" s="338" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="330"/>
-      <c r="AL2" s="330"/>
-      <c r="AM2" s="330"/>
-      <c r="AN2" s="330"/>
-      <c r="AO2" s="330"/>
-      <c r="AP2" s="330"/>
-      <c r="AQ2" s="330"/>
-      <c r="AR2" s="330"/>
-      <c r="AS2" s="327"/>
-      <c r="AT2" s="327"/>
-      <c r="AU2" s="327"/>
-      <c r="AV2" s="327"/>
-      <c r="AW2" s="325"/>
-      <c r="AX2" s="325"/>
-      <c r="AY2" s="325"/>
-      <c r="AZ2" s="325"/>
-      <c r="BA2" s="325"/>
-      <c r="BB2" s="325"/>
-      <c r="BC2" s="325"/>
-      <c r="BD2" s="325"/>
-    </row>
-    <row r="3" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="AK2" s="338"/>
+      <c r="AL2" s="338"/>
+      <c r="AM2" s="338"/>
+      <c r="AN2" s="338"/>
+      <c r="AO2" s="338"/>
+      <c r="AP2" s="338"/>
+      <c r="AQ2" s="338"/>
+      <c r="AR2" s="338"/>
+      <c r="AS2" s="335"/>
+      <c r="AT2" s="335"/>
+      <c r="AU2" s="335"/>
+      <c r="AV2" s="335"/>
+      <c r="AW2" s="333"/>
+      <c r="AX2" s="333"/>
+      <c r="AY2" s="333"/>
+      <c r="AZ2" s="333"/>
+      <c r="BA2" s="333"/>
+      <c r="BB2" s="333"/>
+      <c r="BC2" s="333"/>
+      <c r="BD2" s="333"/>
+    </row>
+    <row r="3" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A3" s="115"/>
-      <c r="W3" s="323" t="s">
+      <c r="W3" s="331" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="323"/>
-      <c r="Y3" s="323"/>
-      <c r="Z3" s="323"/>
-      <c r="AA3" s="323"/>
-      <c r="AB3" s="323"/>
-      <c r="AC3" s="323"/>
-      <c r="AD3" s="323"/>
-      <c r="AE3" s="323"/>
-      <c r="AF3" s="323"/>
-      <c r="AG3" s="323"/>
-      <c r="AH3" s="323"/>
-      <c r="AI3" s="323"/>
-      <c r="AS3" s="328"/>
-      <c r="AT3" s="328"/>
-      <c r="AU3" s="328"/>
-      <c r="AV3" s="328"/>
-      <c r="AW3" s="326"/>
-      <c r="AX3" s="326"/>
-      <c r="AY3" s="326"/>
-      <c r="AZ3" s="326"/>
-      <c r="BA3" s="326"/>
-      <c r="BB3" s="326"/>
-      <c r="BC3" s="326"/>
-      <c r="BD3" s="326"/>
+      <c r="X3" s="331"/>
+      <c r="Y3" s="331"/>
+      <c r="Z3" s="331"/>
+      <c r="AA3" s="331"/>
+      <c r="AB3" s="331"/>
+      <c r="AC3" s="331"/>
+      <c r="AD3" s="331"/>
+      <c r="AE3" s="331"/>
+      <c r="AF3" s="331"/>
+      <c r="AG3" s="331"/>
+      <c r="AH3" s="331"/>
+      <c r="AI3" s="331"/>
+      <c r="AS3" s="336"/>
+      <c r="AT3" s="336"/>
+      <c r="AU3" s="336"/>
+      <c r="AV3" s="336"/>
+      <c r="AW3" s="334"/>
+      <c r="AX3" s="334"/>
+      <c r="AY3" s="334"/>
+      <c r="AZ3" s="334"/>
+      <c r="BA3" s="334"/>
+      <c r="BB3" s="334"/>
+      <c r="BC3" s="334"/>
+      <c r="BD3" s="334"/>
       <c r="CU3" s="116"/>
       <c r="CV3" s="116"/>
     </row>
-    <row r="4" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="117"/>
       <c r="B4" s="117"/>
       <c r="C4" s="117"/>
@@ -13218,7 +13184,7 @@
       <c r="CI4" s="117"/>
       <c r="CJ4" s="117"/>
     </row>
-    <row r="5" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="117"/>
       <c r="B5" s="117"/>
       <c r="C5" s="117"/>
@@ -13308,7 +13274,7 @@
       <c r="CI5" s="117"/>
       <c r="CJ5" s="117"/>
     </row>
-    <row r="6" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="117"/>
       <c r="B6" s="117"/>
       <c r="C6" s="117"/>
@@ -13398,7 +13364,7 @@
       <c r="CI6" s="117"/>
       <c r="CJ6" s="117"/>
     </row>
-    <row r="7" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="117"/>
       <c r="B7" s="117"/>
       <c r="C7" s="117"/>
@@ -13488,7 +13454,7 @@
       <c r="CI7" s="117"/>
       <c r="CJ7" s="117"/>
     </row>
-    <row r="8" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="123"/>
       <c r="E8" s="123"/>
       <c r="F8" s="123"/>
@@ -13552,7 +13518,7 @@
       <c r="BO8" s="124"/>
       <c r="BP8" s="124"/>
     </row>
-    <row r="9" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:100" s="121" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="123"/>
       <c r="E9" s="123"/>
       <c r="F9" s="123"/>
@@ -13616,7 +13582,7 @@
       <c r="BO9" s="124"/>
       <c r="BP9" s="124"/>
     </row>
-    <row r="10" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="125"/>
       <c r="B10" s="125"/>
       <c r="C10" s="126"/>
@@ -13676,207 +13642,207 @@
       <c r="BE10" s="126"/>
       <c r="BF10" s="126"/>
     </row>
-    <row r="11" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="338"/>
-      <c r="B11" s="338"/>
-      <c r="C11" s="338"/>
-      <c r="AC11" s="338"/>
-      <c r="AD11" s="338"/>
-      <c r="AE11" s="338"/>
-    </row>
-    <row r="12" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="324"/>
+      <c r="B11" s="324"/>
+      <c r="C11" s="324"/>
+      <c r="AC11" s="324"/>
+      <c r="AD11" s="324"/>
+      <c r="AE11" s="324"/>
+    </row>
+    <row r="12" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="127"/>
       <c r="AC12" s="127"/>
     </row>
-    <row r="13" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="332" t="s">
+    <row r="13" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:100" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="325" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="333"/>
-      <c r="C21" s="333"/>
-      <c r="D21" s="333"/>
-      <c r="E21" s="333"/>
-      <c r="F21" s="333"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="332" t="s">
+      <c r="B21" s="326"/>
+      <c r="C21" s="326"/>
+      <c r="D21" s="326"/>
+      <c r="E21" s="326"/>
+      <c r="F21" s="326"/>
+      <c r="G21" s="327"/>
+      <c r="H21" s="325" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="333"/>
-      <c r="J21" s="333"/>
-      <c r="K21" s="333"/>
-      <c r="L21" s="333"/>
-      <c r="M21" s="333"/>
-      <c r="N21" s="334"/>
-      <c r="O21" s="332" t="s">
+      <c r="I21" s="326"/>
+      <c r="J21" s="326"/>
+      <c r="K21" s="326"/>
+      <c r="L21" s="326"/>
+      <c r="M21" s="326"/>
+      <c r="N21" s="327"/>
+      <c r="O21" s="325" t="s">
         <v>52</v>
       </c>
-      <c r="P21" s="333"/>
-      <c r="Q21" s="333"/>
-      <c r="R21" s="333"/>
-      <c r="S21" s="333"/>
-      <c r="T21" s="333"/>
-      <c r="U21" s="334"/>
-      <c r="V21" s="332" t="s">
+      <c r="P21" s="326"/>
+      <c r="Q21" s="326"/>
+      <c r="R21" s="326"/>
+      <c r="S21" s="326"/>
+      <c r="T21" s="326"/>
+      <c r="U21" s="327"/>
+      <c r="V21" s="325" t="s">
         <v>57</v>
       </c>
-      <c r="W21" s="333"/>
-      <c r="X21" s="333"/>
-      <c r="Y21" s="333"/>
-      <c r="Z21" s="333"/>
-      <c r="AA21" s="333"/>
-      <c r="AB21" s="334"/>
-      <c r="AC21" s="332" t="s">
+      <c r="W21" s="326"/>
+      <c r="X21" s="326"/>
+      <c r="Y21" s="326"/>
+      <c r="Z21" s="326"/>
+      <c r="AA21" s="326"/>
+      <c r="AB21" s="327"/>
+      <c r="AC21" s="325" t="s">
         <v>53</v>
       </c>
-      <c r="AD21" s="333"/>
-      <c r="AE21" s="333"/>
-      <c r="AF21" s="333"/>
-      <c r="AG21" s="333"/>
-      <c r="AH21" s="333"/>
-      <c r="AI21" s="334"/>
-      <c r="AJ21" s="332" t="s">
+      <c r="AD21" s="326"/>
+      <c r="AE21" s="326"/>
+      <c r="AF21" s="326"/>
+      <c r="AG21" s="326"/>
+      <c r="AH21" s="326"/>
+      <c r="AI21" s="327"/>
+      <c r="AJ21" s="325" t="s">
         <v>58</v>
       </c>
-      <c r="AK21" s="333"/>
-      <c r="AL21" s="333"/>
-      <c r="AM21" s="333"/>
-      <c r="AN21" s="333"/>
-      <c r="AO21" s="333"/>
-      <c r="AP21" s="334"/>
-      <c r="AQ21" s="332" t="s">
+      <c r="AK21" s="326"/>
+      <c r="AL21" s="326"/>
+      <c r="AM21" s="326"/>
+      <c r="AN21" s="326"/>
+      <c r="AO21" s="326"/>
+      <c r="AP21" s="327"/>
+      <c r="AQ21" s="325" t="s">
         <v>59</v>
       </c>
-      <c r="AR21" s="333"/>
-      <c r="AS21" s="333"/>
-      <c r="AT21" s="333"/>
-      <c r="AU21" s="333"/>
-      <c r="AV21" s="333"/>
-      <c r="AW21" s="334"/>
-      <c r="AX21" s="332" t="s">
+      <c r="AR21" s="326"/>
+      <c r="AS21" s="326"/>
+      <c r="AT21" s="326"/>
+      <c r="AU21" s="326"/>
+      <c r="AV21" s="326"/>
+      <c r="AW21" s="327"/>
+      <c r="AX21" s="325" t="s">
         <v>60</v>
       </c>
-      <c r="AY21" s="333"/>
-      <c r="AZ21" s="333"/>
-      <c r="BA21" s="333"/>
-      <c r="BB21" s="333"/>
-      <c r="BC21" s="333"/>
-      <c r="BD21" s="334"/>
-    </row>
-    <row r="22" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AY21" s="326"/>
+      <c r="AZ21" s="326"/>
+      <c r="BA21" s="326"/>
+      <c r="BB21" s="326"/>
+      <c r="BC21" s="326"/>
+      <c r="BD21" s="327"/>
+    </row>
+    <row r="22" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="335" t="s">
+      <c r="B22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="336"/>
-      <c r="D22" s="336"/>
-      <c r="E22" s="336"/>
-      <c r="F22" s="336"/>
+      <c r="C22" s="329"/>
+      <c r="D22" s="329"/>
+      <c r="E22" s="329"/>
+      <c r="F22" s="329"/>
       <c r="G22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="H22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="I22" s="335" t="s">
+      <c r="I22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="336"/>
-      <c r="K22" s="336"/>
-      <c r="L22" s="336"/>
-      <c r="M22" s="336"/>
+      <c r="J22" s="329"/>
+      <c r="K22" s="329"/>
+      <c r="L22" s="329"/>
+      <c r="M22" s="329"/>
       <c r="N22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="O22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="P22" s="335" t="s">
+      <c r="P22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="Q22" s="336"/>
-      <c r="R22" s="336"/>
-      <c r="S22" s="336"/>
-      <c r="T22" s="336"/>
+      <c r="Q22" s="329"/>
+      <c r="R22" s="329"/>
+      <c r="S22" s="329"/>
+      <c r="T22" s="329"/>
       <c r="U22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="V22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="W22" s="335" t="s">
+      <c r="W22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="X22" s="336"/>
-      <c r="Y22" s="336"/>
-      <c r="Z22" s="336"/>
-      <c r="AA22" s="337"/>
+      <c r="X22" s="329"/>
+      <c r="Y22" s="329"/>
+      <c r="Z22" s="329"/>
+      <c r="AA22" s="330"/>
       <c r="AB22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="AC22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AD22" s="335" t="s">
+      <c r="AD22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="AE22" s="336"/>
-      <c r="AF22" s="336"/>
-      <c r="AG22" s="336"/>
-      <c r="AH22" s="336"/>
+      <c r="AE22" s="329"/>
+      <c r="AF22" s="329"/>
+      <c r="AG22" s="329"/>
+      <c r="AH22" s="329"/>
       <c r="AI22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="AJ22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AK22" s="335" t="s">
+      <c r="AK22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="AL22" s="336"/>
-      <c r="AM22" s="336"/>
-      <c r="AN22" s="336"/>
-      <c r="AO22" s="336"/>
+      <c r="AL22" s="329"/>
+      <c r="AM22" s="329"/>
+      <c r="AN22" s="329"/>
+      <c r="AO22" s="329"/>
       <c r="AP22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="AQ22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AR22" s="335" t="s">
+      <c r="AR22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="AS22" s="336"/>
-      <c r="AT22" s="336"/>
-      <c r="AU22" s="336"/>
-      <c r="AV22" s="336"/>
+      <c r="AS22" s="329"/>
+      <c r="AT22" s="329"/>
+      <c r="AU22" s="329"/>
+      <c r="AV22" s="329"/>
       <c r="AW22" s="128" t="s">
         <v>55</v>
       </c>
       <c r="AX22" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="AY22" s="335" t="s">
+      <c r="AY22" s="328" t="s">
         <v>54</v>
       </c>
-      <c r="AZ22" s="336"/>
-      <c r="BA22" s="336"/>
-      <c r="BB22" s="336"/>
-      <c r="BC22" s="337"/>
+      <c r="AZ22" s="329"/>
+      <c r="BA22" s="329"/>
+      <c r="BB22" s="329"/>
+      <c r="BC22" s="330"/>
       <c r="BD22" s="128" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="129">
         <v>1</v>
       </c>
@@ -13950,7 +13916,7 @@
       <c r="BC23" s="134"/>
       <c r="BD23" s="135"/>
     </row>
-    <row r="24" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="129">
         <v>2</v>
       </c>
@@ -14024,7 +13990,7 @@
       <c r="BC24" s="134"/>
       <c r="BD24" s="135"/>
     </row>
-    <row r="25" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="129">
         <v>3</v>
       </c>
@@ -14098,7 +14064,7 @@
       <c r="BC25" s="134"/>
       <c r="BD25" s="135"/>
     </row>
-    <row r="26" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="129">
         <v>4</v>
       </c>
@@ -14172,7 +14138,7 @@
       <c r="BC26" s="134"/>
       <c r="BD26" s="135"/>
     </row>
-    <row r="27" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="129">
         <v>5</v>
       </c>
@@ -14246,7 +14212,7 @@
       <c r="BC27" s="134"/>
       <c r="BD27" s="136"/>
     </row>
-    <row r="28" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="129">
         <v>6</v>
       </c>
@@ -14320,7 +14286,7 @@
       <c r="BC28" s="134"/>
       <c r="BD28" s="135"/>
     </row>
-    <row r="29" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="129">
         <v>7</v>
       </c>
@@ -14394,7 +14360,7 @@
       <c r="BC29" s="134"/>
       <c r="BD29" s="135"/>
     </row>
-    <row r="30" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="129">
         <v>8</v>
       </c>
@@ -14468,7 +14434,7 @@
       <c r="BC30" s="134"/>
       <c r="BD30" s="138"/>
     </row>
-    <row r="31" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="129">
         <v>9</v>
       </c>
@@ -14542,7 +14508,7 @@
       <c r="BC31" s="134"/>
       <c r="BD31" s="138"/>
     </row>
-    <row r="32" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:56" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="129">
         <v>10</v>
       </c>
@@ -14616,7 +14582,7 @@
       <c r="BC32" s="134"/>
       <c r="BD32" s="132"/>
     </row>
-    <row r="33" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="129">
         <v>11</v>
       </c>
@@ -14690,7 +14656,7 @@
       <c r="BC33" s="134"/>
       <c r="BD33" s="132"/>
     </row>
-    <row r="34" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="129">
         <v>12</v>
       </c>
@@ -14764,7 +14730,7 @@
       <c r="BC34" s="134"/>
       <c r="BD34" s="132"/>
     </row>
-    <row r="35" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="129">
         <v>13</v>
       </c>
@@ -14838,7 +14804,7 @@
       <c r="BC35" s="134"/>
       <c r="BD35" s="132"/>
     </row>
-    <row r="36" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="129">
         <v>14</v>
       </c>
@@ -14912,7 +14878,7 @@
       <c r="BC36" s="134"/>
       <c r="BD36" s="132"/>
     </row>
-    <row r="37" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="129">
         <v>15</v>
       </c>
@@ -14986,7 +14952,7 @@
       <c r="BC37" s="134"/>
       <c r="BD37" s="132"/>
     </row>
-    <row r="38" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="129">
         <v>16</v>
       </c>
@@ -15060,7 +15026,7 @@
       <c r="BC38" s="134"/>
       <c r="BD38" s="135"/>
     </row>
-    <row r="39" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="129">
         <v>17</v>
       </c>
@@ -15134,7 +15100,7 @@
       <c r="BC39" s="134"/>
       <c r="BD39" s="135"/>
     </row>
-    <row r="40" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="129">
         <v>18</v>
       </c>
@@ -15208,7 +15174,7 @@
       <c r="BC40" s="134"/>
       <c r="BD40" s="135"/>
     </row>
-    <row r="41" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="129">
         <v>19</v>
       </c>
@@ -15282,7 +15248,7 @@
       <c r="BC41" s="134"/>
       <c r="BD41" s="135"/>
     </row>
-    <row r="42" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="129">
         <v>20</v>
       </c>
@@ -15356,106 +15322,106 @@
       <c r="BC42" s="134"/>
       <c r="BD42" s="136"/>
     </row>
-    <row r="43" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="331" t="s">
+    <row r="43" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="331"/>
-      <c r="C43" s="331"/>
-      <c r="D43" s="331"/>
-      <c r="E43" s="331"/>
-      <c r="F43" s="331"/>
+      <c r="B43" s="323"/>
+      <c r="C43" s="323"/>
+      <c r="D43" s="323"/>
+      <c r="E43" s="323"/>
+      <c r="F43" s="323"/>
       <c r="G43" s="132">
         <f>SUM(G23:G42)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="331" t="s">
+      <c r="H43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="331"/>
-      <c r="J43" s="331"/>
-      <c r="K43" s="331"/>
-      <c r="L43" s="331"/>
-      <c r="M43" s="331"/>
+      <c r="I43" s="323"/>
+      <c r="J43" s="323"/>
+      <c r="K43" s="323"/>
+      <c r="L43" s="323"/>
+      <c r="M43" s="323"/>
       <c r="N43" s="132">
         <f>SUM(N23:N42)</f>
         <v>0</v>
       </c>
-      <c r="O43" s="331" t="s">
+      <c r="O43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="P43" s="331"/>
-      <c r="Q43" s="331"/>
-      <c r="R43" s="331"/>
-      <c r="S43" s="331"/>
-      <c r="T43" s="331"/>
+      <c r="P43" s="323"/>
+      <c r="Q43" s="323"/>
+      <c r="R43" s="323"/>
+      <c r="S43" s="323"/>
+      <c r="T43" s="323"/>
       <c r="U43" s="132">
         <f>SUM(U23:U42)</f>
         <v>0</v>
       </c>
-      <c r="V43" s="331" t="s">
+      <c r="V43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="W43" s="331"/>
-      <c r="X43" s="331"/>
-      <c r="Y43" s="331"/>
-      <c r="Z43" s="331"/>
-      <c r="AA43" s="331"/>
+      <c r="W43" s="323"/>
+      <c r="X43" s="323"/>
+      <c r="Y43" s="323"/>
+      <c r="Z43" s="323"/>
+      <c r="AA43" s="323"/>
       <c r="AB43" s="132">
         <f>SUM(AB23:AB42)</f>
         <v>0</v>
       </c>
-      <c r="AC43" s="331" t="s">
+      <c r="AC43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="AD43" s="331"/>
-      <c r="AE43" s="331"/>
-      <c r="AF43" s="331"/>
-      <c r="AG43" s="331"/>
-      <c r="AH43" s="331"/>
+      <c r="AD43" s="323"/>
+      <c r="AE43" s="323"/>
+      <c r="AF43" s="323"/>
+      <c r="AG43" s="323"/>
+      <c r="AH43" s="323"/>
       <c r="AI43" s="132">
         <f>SUM(AI23:AI42)</f>
         <v>0</v>
       </c>
-      <c r="AJ43" s="331" t="s">
+      <c r="AJ43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="AK43" s="331"/>
-      <c r="AL43" s="331"/>
-      <c r="AM43" s="331"/>
-      <c r="AN43" s="331"/>
-      <c r="AO43" s="331"/>
+      <c r="AK43" s="323"/>
+      <c r="AL43" s="323"/>
+      <c r="AM43" s="323"/>
+      <c r="AN43" s="323"/>
+      <c r="AO43" s="323"/>
       <c r="AP43" s="132">
         <f>SUM(AP23:AP42)</f>
         <v>0</v>
       </c>
-      <c r="AQ43" s="331" t="s">
+      <c r="AQ43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="AR43" s="331"/>
-      <c r="AS43" s="331"/>
-      <c r="AT43" s="331"/>
-      <c r="AU43" s="331"/>
-      <c r="AV43" s="331"/>
+      <c r="AR43" s="323"/>
+      <c r="AS43" s="323"/>
+      <c r="AT43" s="323"/>
+      <c r="AU43" s="323"/>
+      <c r="AV43" s="323"/>
       <c r="AW43" s="132">
         <f>SUM(AW23:AW42)</f>
         <v>0</v>
       </c>
-      <c r="AX43" s="331" t="s">
+      <c r="AX43" s="323" t="s">
         <v>20</v>
       </c>
-      <c r="AY43" s="331"/>
-      <c r="AZ43" s="331"/>
-      <c r="BA43" s="331"/>
-      <c r="BB43" s="331"/>
-      <c r="BC43" s="331"/>
+      <c r="AY43" s="323"/>
+      <c r="AZ43" s="323"/>
+      <c r="BA43" s="323"/>
+      <c r="BB43" s="323"/>
+      <c r="BC43" s="323"/>
       <c r="BD43" s="132">
         <f>SUM(BD23:BD42)</f>
         <v>0</v>
       </c>
       <c r="BK43" s="116"/>
     </row>
-    <row r="44" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:63" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="143"/>
       <c r="B44" s="143"/>
       <c r="C44" s="143"/>
@@ -15515,34 +15481,33 @@
       <c r="BC44" s="143"/>
       <c r="BD44" s="143"/>
     </row>
-    <row r="45" spans="1:63" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:63" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:63" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:63" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:63" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="O43:T43"/>
-    <mergeCell ref="V43:AA43"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="V21:AB21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="I22:M22"/>
-    <mergeCell ref="P22:T22"/>
-    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W3:AI3"/>
+    <mergeCell ref="BA1:BD1"/>
+    <mergeCell ref="AW1:AZ1"/>
+    <mergeCell ref="AS1:AV1"/>
+    <mergeCell ref="BA2:BD3"/>
+    <mergeCell ref="AW2:AZ3"/>
+    <mergeCell ref="AS2:AV3"/>
+    <mergeCell ref="W1:AI1"/>
+    <mergeCell ref="W2:AI2"/>
+    <mergeCell ref="AJ1:AR1"/>
+    <mergeCell ref="AJ2:AR2"/>
     <mergeCell ref="AJ43:AO43"/>
     <mergeCell ref="AQ43:AV43"/>
     <mergeCell ref="AX43:BC43"/>
@@ -15559,17 +15524,18 @@
     <mergeCell ref="AC21:AI21"/>
     <mergeCell ref="AC43:AH43"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="W3:AI3"/>
-    <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="AW1:AZ1"/>
-    <mergeCell ref="AS1:AV1"/>
-    <mergeCell ref="BA2:BD3"/>
-    <mergeCell ref="AW2:AZ3"/>
-    <mergeCell ref="AS2:AV3"/>
-    <mergeCell ref="W1:AI1"/>
-    <mergeCell ref="W2:AI2"/>
-    <mergeCell ref="AJ1:AR1"/>
-    <mergeCell ref="AJ2:AR2"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="O43:T43"/>
+    <mergeCell ref="V43:AA43"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="V21:AB21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="P22:T22"/>
+    <mergeCell ref="W22:AA22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.15748031496062992" bottom="0.19685039370078741" header="0" footer="0"/>
@@ -15585,446 +15551,446 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="21.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.07421875" defaultRowHeight="21" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="21" width="10.6640625" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="21" width="10.69140625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9.07421875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A1" s="1"/>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="L1" s="201" t="s">
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
+      <c r="L1" s="241" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
+      <c r="M1" s="241"/>
+      <c r="N1" s="241"/>
+      <c r="O1" s="241"/>
       <c r="P1" s="149"/>
-      <c r="R1" s="200" t="s">
+      <c r="R1" s="240" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-    </row>
-    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="203" t="s">
+      <c r="S1" s="240"/>
+      <c r="T1" s="240"/>
+      <c r="U1" s="240"/>
+    </row>
+    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="243" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-    </row>
-    <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="346" t="s">
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+    </row>
+    <row r="3" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="358" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
-      <c r="G3" s="346"/>
-      <c r="H3" s="346"/>
-      <c r="I3" s="346"/>
-      <c r="J3" s="346"/>
-      <c r="L3" s="201" t="s">
+      <c r="B3" s="358"/>
+      <c r="C3" s="358"/>
+      <c r="D3" s="358"/>
+      <c r="E3" s="358"/>
+      <c r="F3" s="358"/>
+      <c r="G3" s="358"/>
+      <c r="H3" s="358"/>
+      <c r="I3" s="358"/>
+      <c r="J3" s="358"/>
+      <c r="L3" s="241" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="201"/>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="201"/>
-      <c r="R3" s="200" t="s">
+      <c r="M3" s="241"/>
+      <c r="N3" s="241"/>
+      <c r="O3" s="241"/>
+      <c r="P3" s="241"/>
+      <c r="R3" s="240" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="200"/>
-      <c r="T3" s="200"/>
-      <c r="U3" s="200"/>
-    </row>
-    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="346"/>
-      <c r="B4" s="346"/>
-      <c r="C4" s="346"/>
-      <c r="D4" s="346"/>
-      <c r="E4" s="346"/>
-      <c r="F4" s="346"/>
-      <c r="G4" s="346"/>
-      <c r="H4" s="346"/>
-      <c r="I4" s="346"/>
-      <c r="J4" s="346"/>
-    </row>
-    <row r="5" spans="1:21" ht="9.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="S3" s="240"/>
+      <c r="T3" s="240"/>
+      <c r="U3" s="240"/>
+    </row>
+    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="358"/>
+      <c r="B4" s="358"/>
+      <c r="C4" s="358"/>
+      <c r="D4" s="358"/>
+      <c r="E4" s="358"/>
+      <c r="F4" s="358"/>
+      <c r="G4" s="358"/>
+      <c r="H4" s="358"/>
+      <c r="I4" s="358"/>
+      <c r="J4" s="358"/>
+    </row>
+    <row r="5" spans="1:21" ht="9.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="3"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:21" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="340" t="s">
+    <row r="6" spans="1:21" s="14" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A6" s="352" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="341"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="341"/>
-      <c r="E6" s="341"/>
-      <c r="F6" s="341"/>
-      <c r="G6" s="341"/>
-      <c r="H6" s="341"/>
-      <c r="I6" s="341"/>
-      <c r="J6" s="342"/>
-      <c r="K6" s="339"/>
-      <c r="L6" s="343" t="s">
+      <c r="B6" s="353"/>
+      <c r="C6" s="353"/>
+      <c r="D6" s="353"/>
+      <c r="E6" s="353"/>
+      <c r="F6" s="353"/>
+      <c r="G6" s="353"/>
+      <c r="H6" s="353"/>
+      <c r="I6" s="353"/>
+      <c r="J6" s="354"/>
+      <c r="K6" s="351"/>
+      <c r="L6" s="355" t="s">
         <v>67</v>
       </c>
-      <c r="M6" s="344"/>
-      <c r="N6" s="344"/>
-      <c r="O6" s="344"/>
-      <c r="P6" s="344"/>
-      <c r="Q6" s="344"/>
-      <c r="R6" s="344"/>
-      <c r="S6" s="344"/>
-      <c r="T6" s="344"/>
-      <c r="U6" s="345"/>
-    </row>
-    <row r="7" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="347"/>
-      <c r="B7" s="348"/>
-      <c r="C7" s="348"/>
-      <c r="D7" s="348"/>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
-      <c r="G7" s="348"/>
-      <c r="H7" s="348"/>
-      <c r="I7" s="348"/>
-      <c r="J7" s="349"/>
-      <c r="K7" s="339"/>
-      <c r="L7" s="352"/>
-      <c r="M7" s="353"/>
-      <c r="N7" s="353"/>
-      <c r="O7" s="353"/>
-      <c r="P7" s="353"/>
-      <c r="Q7" s="353"/>
-      <c r="R7" s="353"/>
-      <c r="S7" s="353"/>
-      <c r="T7" s="353"/>
-      <c r="U7" s="354"/>
-    </row>
-    <row r="8" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="350"/>
-      <c r="B8" s="339"/>
-      <c r="C8" s="339"/>
-      <c r="D8" s="339"/>
-      <c r="E8" s="339"/>
-      <c r="F8" s="339"/>
-      <c r="G8" s="339"/>
-      <c r="H8" s="339"/>
-      <c r="I8" s="339"/>
-      <c r="J8" s="351"/>
-      <c r="K8" s="339"/>
-      <c r="L8" s="355"/>
-      <c r="M8" s="356"/>
-      <c r="N8" s="356"/>
-      <c r="O8" s="356"/>
-      <c r="P8" s="356"/>
-      <c r="Q8" s="356"/>
-      <c r="R8" s="356"/>
-      <c r="S8" s="356"/>
-      <c r="T8" s="356"/>
-      <c r="U8" s="357"/>
-    </row>
-    <row r="9" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="350"/>
-      <c r="B9" s="339"/>
-      <c r="C9" s="339"/>
-      <c r="D9" s="339"/>
-      <c r="E9" s="339"/>
-      <c r="F9" s="339"/>
-      <c r="G9" s="339"/>
-      <c r="H9" s="339"/>
-      <c r="I9" s="339"/>
-      <c r="J9" s="351"/>
-      <c r="K9" s="339"/>
-      <c r="L9" s="355"/>
-      <c r="M9" s="356"/>
-      <c r="N9" s="356"/>
-      <c r="O9" s="356"/>
-      <c r="P9" s="356"/>
-      <c r="Q9" s="356"/>
-      <c r="R9" s="356"/>
-      <c r="S9" s="356"/>
-      <c r="T9" s="356"/>
-      <c r="U9" s="357"/>
-    </row>
-    <row r="10" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="350"/>
-      <c r="B10" s="339"/>
-      <c r="C10" s="339"/>
-      <c r="D10" s="339"/>
-      <c r="E10" s="339"/>
-      <c r="F10" s="339"/>
-      <c r="G10" s="339"/>
-      <c r="H10" s="339"/>
-      <c r="I10" s="339"/>
-      <c r="J10" s="351"/>
-      <c r="K10" s="339"/>
-      <c r="L10" s="355"/>
-      <c r="M10" s="356"/>
-      <c r="N10" s="356"/>
-      <c r="O10" s="356"/>
-      <c r="P10" s="356"/>
-      <c r="Q10" s="356"/>
-      <c r="R10" s="356"/>
-      <c r="S10" s="356"/>
-      <c r="T10" s="356"/>
-      <c r="U10" s="357"/>
-    </row>
-    <row r="11" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="350"/>
-      <c r="B11" s="339"/>
-      <c r="C11" s="339"/>
-      <c r="D11" s="339"/>
-      <c r="E11" s="339"/>
-      <c r="F11" s="339"/>
-      <c r="G11" s="339"/>
-      <c r="H11" s="339"/>
-      <c r="I11" s="339"/>
-      <c r="J11" s="351"/>
-      <c r="K11" s="339"/>
-      <c r="L11" s="355"/>
-      <c r="M11" s="356"/>
-      <c r="N11" s="356"/>
-      <c r="O11" s="356"/>
-      <c r="P11" s="356"/>
-      <c r="Q11" s="356"/>
-      <c r="R11" s="356"/>
-      <c r="S11" s="356"/>
-      <c r="T11" s="356"/>
-      <c r="U11" s="357"/>
-    </row>
-    <row r="12" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="350"/>
-      <c r="B12" s="339"/>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
-      <c r="G12" s="339"/>
-      <c r="H12" s="339"/>
-      <c r="I12" s="339"/>
-      <c r="J12" s="351"/>
-      <c r="K12" s="339"/>
-      <c r="L12" s="355"/>
-      <c r="M12" s="356"/>
-      <c r="N12" s="356"/>
-      <c r="O12" s="356"/>
-      <c r="P12" s="356"/>
-      <c r="Q12" s="356"/>
-      <c r="R12" s="356"/>
-      <c r="S12" s="356"/>
-      <c r="T12" s="356"/>
-      <c r="U12" s="357"/>
-    </row>
-    <row r="13" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="350"/>
-      <c r="B13" s="339"/>
-      <c r="C13" s="339"/>
-      <c r="D13" s="339"/>
-      <c r="E13" s="339"/>
-      <c r="F13" s="339"/>
-      <c r="G13" s="339"/>
-      <c r="H13" s="339"/>
-      <c r="I13" s="339"/>
-      <c r="J13" s="351"/>
-      <c r="K13" s="339"/>
-      <c r="L13" s="355"/>
-      <c r="M13" s="356"/>
-      <c r="N13" s="356"/>
-      <c r="O13" s="356"/>
-      <c r="P13" s="356"/>
-      <c r="Q13" s="356"/>
-      <c r="R13" s="356"/>
-      <c r="S13" s="356"/>
-      <c r="T13" s="356"/>
-      <c r="U13" s="357"/>
-    </row>
-    <row r="14" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="350"/>
-      <c r="B14" s="339"/>
-      <c r="C14" s="339"/>
-      <c r="D14" s="339"/>
-      <c r="E14" s="339"/>
-      <c r="F14" s="339"/>
-      <c r="G14" s="339"/>
-      <c r="H14" s="339"/>
-      <c r="I14" s="339"/>
-      <c r="J14" s="351"/>
-      <c r="K14" s="339"/>
-      <c r="L14" s="355"/>
-      <c r="M14" s="356"/>
-      <c r="N14" s="356"/>
-      <c r="O14" s="356"/>
-      <c r="P14" s="356"/>
-      <c r="Q14" s="356"/>
-      <c r="R14" s="356"/>
-      <c r="S14" s="356"/>
-      <c r="T14" s="356"/>
-      <c r="U14" s="357"/>
-    </row>
-    <row r="15" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="350"/>
-      <c r="B15" s="339"/>
-      <c r="C15" s="339"/>
-      <c r="D15" s="339"/>
-      <c r="E15" s="339"/>
-      <c r="F15" s="339"/>
-      <c r="G15" s="339"/>
-      <c r="H15" s="339"/>
-      <c r="I15" s="339"/>
-      <c r="J15" s="351"/>
-      <c r="K15" s="339"/>
-      <c r="L15" s="355"/>
-      <c r="M15" s="356"/>
-      <c r="N15" s="356"/>
-      <c r="O15" s="356"/>
-      <c r="P15" s="356"/>
-      <c r="Q15" s="356"/>
-      <c r="R15" s="356"/>
-      <c r="S15" s="356"/>
-      <c r="T15" s="356"/>
-      <c r="U15" s="357"/>
-    </row>
-    <row r="16" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="350"/>
-      <c r="B16" s="339"/>
-      <c r="C16" s="339"/>
-      <c r="D16" s="339"/>
-      <c r="E16" s="339"/>
-      <c r="F16" s="339"/>
-      <c r="G16" s="339"/>
-      <c r="H16" s="339"/>
-      <c r="I16" s="339"/>
-      <c r="J16" s="351"/>
-      <c r="K16" s="339"/>
-      <c r="L16" s="355"/>
-      <c r="M16" s="356"/>
-      <c r="N16" s="356"/>
-      <c r="O16" s="356"/>
-      <c r="P16" s="356"/>
-      <c r="Q16" s="356"/>
-      <c r="R16" s="356"/>
-      <c r="S16" s="356"/>
-      <c r="T16" s="356"/>
-      <c r="U16" s="357"/>
-    </row>
-    <row r="17" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="350"/>
-      <c r="B17" s="339"/>
-      <c r="C17" s="339"/>
-      <c r="D17" s="339"/>
-      <c r="E17" s="339"/>
-      <c r="F17" s="339"/>
-      <c r="G17" s="339"/>
-      <c r="H17" s="339"/>
-      <c r="I17" s="339"/>
-      <c r="J17" s="351"/>
-      <c r="K17" s="339"/>
-      <c r="L17" s="355"/>
-      <c r="M17" s="356"/>
-      <c r="N17" s="356"/>
-      <c r="O17" s="356"/>
-      <c r="P17" s="356"/>
-      <c r="Q17" s="356"/>
-      <c r="R17" s="356"/>
-      <c r="S17" s="356"/>
-      <c r="T17" s="356"/>
-      <c r="U17" s="357"/>
-    </row>
-    <row r="18" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="350"/>
-      <c r="B18" s="339"/>
-      <c r="C18" s="339"/>
-      <c r="D18" s="339"/>
-      <c r="E18" s="339"/>
-      <c r="F18" s="339"/>
-      <c r="G18" s="339"/>
-      <c r="H18" s="339"/>
-      <c r="I18" s="339"/>
-      <c r="J18" s="351"/>
-      <c r="K18" s="339"/>
-      <c r="L18" s="355"/>
-      <c r="M18" s="356"/>
-      <c r="N18" s="356"/>
-      <c r="O18" s="356"/>
-      <c r="P18" s="356"/>
-      <c r="Q18" s="356"/>
-      <c r="R18" s="356"/>
-      <c r="S18" s="356"/>
-      <c r="T18" s="356"/>
-      <c r="U18" s="357"/>
-    </row>
-    <row r="19" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="350"/>
-      <c r="B19" s="339"/>
-      <c r="C19" s="339"/>
-      <c r="D19" s="339"/>
-      <c r="E19" s="339"/>
-      <c r="F19" s="339"/>
-      <c r="G19" s="339"/>
-      <c r="H19" s="339"/>
-      <c r="I19" s="339"/>
-      <c r="J19" s="351"/>
-      <c r="K19" s="339"/>
-      <c r="L19" s="355"/>
-      <c r="M19" s="356"/>
-      <c r="N19" s="356"/>
-      <c r="O19" s="356"/>
-      <c r="P19" s="356"/>
-      <c r="Q19" s="356"/>
-      <c r="R19" s="356"/>
-      <c r="S19" s="356"/>
-      <c r="T19" s="356"/>
-      <c r="U19" s="357"/>
-    </row>
-    <row r="20" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="350"/>
-      <c r="B20" s="339"/>
-      <c r="C20" s="339"/>
-      <c r="D20" s="339"/>
-      <c r="E20" s="339"/>
-      <c r="F20" s="339"/>
-      <c r="G20" s="339"/>
-      <c r="H20" s="339"/>
-      <c r="I20" s="339"/>
-      <c r="J20" s="351"/>
-      <c r="K20" s="339"/>
-      <c r="L20" s="355"/>
-      <c r="M20" s="356"/>
-      <c r="N20" s="356"/>
-      <c r="O20" s="356"/>
-      <c r="P20" s="356"/>
-      <c r="Q20" s="356"/>
-      <c r="R20" s="356"/>
-      <c r="S20" s="356"/>
-      <c r="T20" s="356"/>
-      <c r="U20" s="357"/>
-    </row>
-    <row r="21" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="M6" s="356"/>
+      <c r="N6" s="356"/>
+      <c r="O6" s="356"/>
+      <c r="P6" s="356"/>
+      <c r="Q6" s="356"/>
+      <c r="R6" s="356"/>
+      <c r="S6" s="356"/>
+      <c r="T6" s="356"/>
+      <c r="U6" s="357"/>
+    </row>
+    <row r="7" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="359"/>
+      <c r="B7" s="360"/>
+      <c r="C7" s="360"/>
+      <c r="D7" s="360"/>
+      <c r="E7" s="360"/>
+      <c r="F7" s="360"/>
+      <c r="G7" s="360"/>
+      <c r="H7" s="360"/>
+      <c r="I7" s="360"/>
+      <c r="J7" s="361"/>
+      <c r="K7" s="351"/>
+      <c r="L7" s="364"/>
+      <c r="M7" s="365"/>
+      <c r="N7" s="365"/>
+      <c r="O7" s="365"/>
+      <c r="P7" s="365"/>
+      <c r="Q7" s="365"/>
+      <c r="R7" s="365"/>
+      <c r="S7" s="365"/>
+      <c r="T7" s="365"/>
+      <c r="U7" s="366"/>
+    </row>
+    <row r="8" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="362"/>
+      <c r="B8" s="351"/>
+      <c r="C8" s="351"/>
+      <c r="D8" s="351"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
+      <c r="G8" s="351"/>
+      <c r="H8" s="351"/>
+      <c r="I8" s="351"/>
+      <c r="J8" s="363"/>
+      <c r="K8" s="351"/>
+      <c r="L8" s="367"/>
+      <c r="M8" s="368"/>
+      <c r="N8" s="368"/>
+      <c r="O8" s="368"/>
+      <c r="P8" s="368"/>
+      <c r="Q8" s="368"/>
+      <c r="R8" s="368"/>
+      <c r="S8" s="368"/>
+      <c r="T8" s="368"/>
+      <c r="U8" s="369"/>
+    </row>
+    <row r="9" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="362"/>
+      <c r="B9" s="351"/>
+      <c r="C9" s="351"/>
+      <c r="D9" s="351"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
+      <c r="G9" s="351"/>
+      <c r="H9" s="351"/>
+      <c r="I9" s="351"/>
+      <c r="J9" s="363"/>
+      <c r="K9" s="351"/>
+      <c r="L9" s="367"/>
+      <c r="M9" s="368"/>
+      <c r="N9" s="368"/>
+      <c r="O9" s="368"/>
+      <c r="P9" s="368"/>
+      <c r="Q9" s="368"/>
+      <c r="R9" s="368"/>
+      <c r="S9" s="368"/>
+      <c r="T9" s="368"/>
+      <c r="U9" s="369"/>
+    </row>
+    <row r="10" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="362"/>
+      <c r="B10" s="351"/>
+      <c r="C10" s="351"/>
+      <c r="D10" s="351"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
+      <c r="G10" s="351"/>
+      <c r="H10" s="351"/>
+      <c r="I10" s="351"/>
+      <c r="J10" s="363"/>
+      <c r="K10" s="351"/>
+      <c r="L10" s="367"/>
+      <c r="M10" s="368"/>
+      <c r="N10" s="368"/>
+      <c r="O10" s="368"/>
+      <c r="P10" s="368"/>
+      <c r="Q10" s="368"/>
+      <c r="R10" s="368"/>
+      <c r="S10" s="368"/>
+      <c r="T10" s="368"/>
+      <c r="U10" s="369"/>
+    </row>
+    <row r="11" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="362"/>
+      <c r="B11" s="351"/>
+      <c r="C11" s="351"/>
+      <c r="D11" s="351"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
+      <c r="G11" s="351"/>
+      <c r="H11" s="351"/>
+      <c r="I11" s="351"/>
+      <c r="J11" s="363"/>
+      <c r="K11" s="351"/>
+      <c r="L11" s="367"/>
+      <c r="M11" s="368"/>
+      <c r="N11" s="368"/>
+      <c r="O11" s="368"/>
+      <c r="P11" s="368"/>
+      <c r="Q11" s="368"/>
+      <c r="R11" s="368"/>
+      <c r="S11" s="368"/>
+      <c r="T11" s="368"/>
+      <c r="U11" s="369"/>
+    </row>
+    <row r="12" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="362"/>
+      <c r="B12" s="351"/>
+      <c r="C12" s="351"/>
+      <c r="D12" s="351"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
+      <c r="G12" s="351"/>
+      <c r="H12" s="351"/>
+      <c r="I12" s="351"/>
+      <c r="J12" s="363"/>
+      <c r="K12" s="351"/>
+      <c r="L12" s="367"/>
+      <c r="M12" s="368"/>
+      <c r="N12" s="368"/>
+      <c r="O12" s="368"/>
+      <c r="P12" s="368"/>
+      <c r="Q12" s="368"/>
+      <c r="R12" s="368"/>
+      <c r="S12" s="368"/>
+      <c r="T12" s="368"/>
+      <c r="U12" s="369"/>
+    </row>
+    <row r="13" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="362"/>
+      <c r="B13" s="351"/>
+      <c r="C13" s="351"/>
+      <c r="D13" s="351"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
+      <c r="G13" s="351"/>
+      <c r="H13" s="351"/>
+      <c r="I13" s="351"/>
+      <c r="J13" s="363"/>
+      <c r="K13" s="351"/>
+      <c r="L13" s="367"/>
+      <c r="M13" s="368"/>
+      <c r="N13" s="368"/>
+      <c r="O13" s="368"/>
+      <c r="P13" s="368"/>
+      <c r="Q13" s="368"/>
+      <c r="R13" s="368"/>
+      <c r="S13" s="368"/>
+      <c r="T13" s="368"/>
+      <c r="U13" s="369"/>
+    </row>
+    <row r="14" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="362"/>
+      <c r="B14" s="351"/>
+      <c r="C14" s="351"/>
+      <c r="D14" s="351"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
+      <c r="G14" s="351"/>
+      <c r="H14" s="351"/>
+      <c r="I14" s="351"/>
+      <c r="J14" s="363"/>
+      <c r="K14" s="351"/>
+      <c r="L14" s="367"/>
+      <c r="M14" s="368"/>
+      <c r="N14" s="368"/>
+      <c r="O14" s="368"/>
+      <c r="P14" s="368"/>
+      <c r="Q14" s="368"/>
+      <c r="R14" s="368"/>
+      <c r="S14" s="368"/>
+      <c r="T14" s="368"/>
+      <c r="U14" s="369"/>
+    </row>
+    <row r="15" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="362"/>
+      <c r="B15" s="351"/>
+      <c r="C15" s="351"/>
+      <c r="D15" s="351"/>
+      <c r="E15" s="351"/>
+      <c r="F15" s="351"/>
+      <c r="G15" s="351"/>
+      <c r="H15" s="351"/>
+      <c r="I15" s="351"/>
+      <c r="J15" s="363"/>
+      <c r="K15" s="351"/>
+      <c r="L15" s="367"/>
+      <c r="M15" s="368"/>
+      <c r="N15" s="368"/>
+      <c r="O15" s="368"/>
+      <c r="P15" s="368"/>
+      <c r="Q15" s="368"/>
+      <c r="R15" s="368"/>
+      <c r="S15" s="368"/>
+      <c r="T15" s="368"/>
+      <c r="U15" s="369"/>
+    </row>
+    <row r="16" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="362"/>
+      <c r="B16" s="351"/>
+      <c r="C16" s="351"/>
+      <c r="D16" s="351"/>
+      <c r="E16" s="351"/>
+      <c r="F16" s="351"/>
+      <c r="G16" s="351"/>
+      <c r="H16" s="351"/>
+      <c r="I16" s="351"/>
+      <c r="J16" s="363"/>
+      <c r="K16" s="351"/>
+      <c r="L16" s="367"/>
+      <c r="M16" s="368"/>
+      <c r="N16" s="368"/>
+      <c r="O16" s="368"/>
+      <c r="P16" s="368"/>
+      <c r="Q16" s="368"/>
+      <c r="R16" s="368"/>
+      <c r="S16" s="368"/>
+      <c r="T16" s="368"/>
+      <c r="U16" s="369"/>
+    </row>
+    <row r="17" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="362"/>
+      <c r="B17" s="351"/>
+      <c r="C17" s="351"/>
+      <c r="D17" s="351"/>
+      <c r="E17" s="351"/>
+      <c r="F17" s="351"/>
+      <c r="G17" s="351"/>
+      <c r="H17" s="351"/>
+      <c r="I17" s="351"/>
+      <c r="J17" s="363"/>
+      <c r="K17" s="351"/>
+      <c r="L17" s="367"/>
+      <c r="M17" s="368"/>
+      <c r="N17" s="368"/>
+      <c r="O17" s="368"/>
+      <c r="P17" s="368"/>
+      <c r="Q17" s="368"/>
+      <c r="R17" s="368"/>
+      <c r="S17" s="368"/>
+      <c r="T17" s="368"/>
+      <c r="U17" s="369"/>
+    </row>
+    <row r="18" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="362"/>
+      <c r="B18" s="351"/>
+      <c r="C18" s="351"/>
+      <c r="D18" s="351"/>
+      <c r="E18" s="351"/>
+      <c r="F18" s="351"/>
+      <c r="G18" s="351"/>
+      <c r="H18" s="351"/>
+      <c r="I18" s="351"/>
+      <c r="J18" s="363"/>
+      <c r="K18" s="351"/>
+      <c r="L18" s="367"/>
+      <c r="M18" s="368"/>
+      <c r="N18" s="368"/>
+      <c r="O18" s="368"/>
+      <c r="P18" s="368"/>
+      <c r="Q18" s="368"/>
+      <c r="R18" s="368"/>
+      <c r="S18" s="368"/>
+      <c r="T18" s="368"/>
+      <c r="U18" s="369"/>
+    </row>
+    <row r="19" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="362"/>
+      <c r="B19" s="351"/>
+      <c r="C19" s="351"/>
+      <c r="D19" s="351"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
+      <c r="G19" s="351"/>
+      <c r="H19" s="351"/>
+      <c r="I19" s="351"/>
+      <c r="J19" s="363"/>
+      <c r="K19" s="351"/>
+      <c r="L19" s="367"/>
+      <c r="M19" s="368"/>
+      <c r="N19" s="368"/>
+      <c r="O19" s="368"/>
+      <c r="P19" s="368"/>
+      <c r="Q19" s="368"/>
+      <c r="R19" s="368"/>
+      <c r="S19" s="368"/>
+      <c r="T19" s="368"/>
+      <c r="U19" s="369"/>
+    </row>
+    <row r="20" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="362"/>
+      <c r="B20" s="351"/>
+      <c r="C20" s="351"/>
+      <c r="D20" s="351"/>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
+      <c r="G20" s="351"/>
+      <c r="H20" s="351"/>
+      <c r="I20" s="351"/>
+      <c r="J20" s="363"/>
+      <c r="K20" s="351"/>
+      <c r="L20" s="367"/>
+      <c r="M20" s="368"/>
+      <c r="N20" s="368"/>
+      <c r="O20" s="368"/>
+      <c r="P20" s="368"/>
+      <c r="Q20" s="368"/>
+      <c r="R20" s="368"/>
+      <c r="S20" s="368"/>
+      <c r="T20" s="368"/>
+      <c r="U20" s="369"/>
+    </row>
+    <row r="21" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="1.05">
       <c r="A21" s="155" t="s">
         <v>68</v>
       </c>
@@ -16037,7 +16003,7 @@
       <c r="H21" s="152"/>
       <c r="I21" s="152"/>
       <c r="J21" s="153"/>
-      <c r="K21" s="339"/>
+      <c r="K21" s="351"/>
       <c r="L21" s="155" t="s">
         <v>69</v>
       </c>
@@ -16051,7 +16017,7 @@
       <c r="T21" s="152"/>
       <c r="U21" s="153"/>
     </row>
-    <row r="22" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
       <c r="A22" s="150"/>
       <c r="B22" s="151"/>
       <c r="C22" s="151"/>
@@ -16062,7 +16028,7 @@
       <c r="H22" s="151"/>
       <c r="I22" s="151"/>
       <c r="J22" s="154"/>
-      <c r="K22" s="339"/>
+      <c r="K22" s="351"/>
       <c r="L22" s="150"/>
       <c r="M22" s="151"/>
       <c r="N22" s="151"/>
@@ -16074,7 +16040,7 @@
       <c r="T22" s="151"/>
       <c r="U22" s="154"/>
     </row>
-    <row r="23" spans="1:21" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" s="25" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="39"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39"/>
@@ -16092,15 +16058,15 @@
       <c r="P23" s="48"/>
       <c r="Q23" s="39"/>
     </row>
-    <row r="24" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A24" s="367" t="s">
+    <row r="24" spans="1:21" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A24" s="348" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="368"/>
-      <c r="C24" s="368"/>
-      <c r="D24" s="368"/>
-      <c r="E24" s="368"/>
-      <c r="F24" s="369"/>
+      <c r="B24" s="349"/>
+      <c r="C24" s="349"/>
+      <c r="D24" s="349"/>
+      <c r="E24" s="349"/>
+      <c r="F24" s="350"/>
       <c r="G24" s="158">
         <v>1</v>
       </c>
@@ -16116,131 +16082,131 @@
       <c r="K24" s="158">
         <v>5</v>
       </c>
-      <c r="L24" s="365" t="s">
+      <c r="L24" s="346" t="s">
         <v>71</v>
       </c>
-      <c r="M24" s="365"/>
+      <c r="M24" s="346"/>
       <c r="N24" s="159" t="s">
         <v>72</v>
       </c>
       <c r="O24" s="157"/>
-      <c r="P24" s="358" t="s">
+      <c r="P24" s="339" t="s">
         <v>70</v>
       </c>
-      <c r="Q24" s="359"/>
-      <c r="R24" s="359"/>
-      <c r="S24" s="359"/>
-      <c r="T24" s="359"/>
-      <c r="U24" s="360"/>
-    </row>
-    <row r="25" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="364"/>
-      <c r="B25" s="364"/>
-      <c r="C25" s="364"/>
-      <c r="D25" s="364"/>
-      <c r="E25" s="364"/>
-      <c r="F25" s="364"/>
+      <c r="Q24" s="340"/>
+      <c r="R24" s="340"/>
+      <c r="S24" s="340"/>
+      <c r="T24" s="340"/>
+      <c r="U24" s="341"/>
+    </row>
+    <row r="25" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A25" s="345"/>
+      <c r="B25" s="345"/>
+      <c r="C25" s="345"/>
+      <c r="D25" s="345"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
       <c r="G25" s="160"/>
       <c r="H25" s="160"/>
       <c r="I25" s="160"/>
       <c r="J25" s="160"/>
       <c r="K25" s="160"/>
-      <c r="L25" s="366"/>
-      <c r="M25" s="366"/>
+      <c r="L25" s="347"/>
+      <c r="M25" s="347"/>
       <c r="N25" s="160"/>
-      <c r="P25" s="361"/>
-      <c r="Q25" s="362"/>
-      <c r="R25" s="362"/>
-      <c r="S25" s="362"/>
-      <c r="T25" s="362"/>
-      <c r="U25" s="363"/>
-    </row>
-    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="364"/>
-      <c r="B26" s="364"/>
-      <c r="C26" s="364"/>
-      <c r="D26" s="364"/>
-      <c r="E26" s="364"/>
-      <c r="F26" s="364"/>
+      <c r="P25" s="342"/>
+      <c r="Q25" s="343"/>
+      <c r="R25" s="343"/>
+      <c r="S25" s="343"/>
+      <c r="T25" s="343"/>
+      <c r="U25" s="344"/>
+    </row>
+    <row r="26" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A26" s="345"/>
+      <c r="B26" s="345"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
       <c r="G26" s="160"/>
       <c r="H26" s="160"/>
       <c r="I26" s="160"/>
       <c r="J26" s="160"/>
       <c r="K26" s="160"/>
-      <c r="L26" s="366"/>
-      <c r="M26" s="366"/>
+      <c r="L26" s="347"/>
+      <c r="M26" s="347"/>
       <c r="N26" s="160"/>
       <c r="P26" s="161"/>
       <c r="U26" s="162"/>
     </row>
-    <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="364"/>
-      <c r="B27" s="364"/>
-      <c r="C27" s="364"/>
-      <c r="D27" s="364"/>
-      <c r="E27" s="364"/>
-      <c r="F27" s="364"/>
+    <row r="27" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A27" s="345"/>
+      <c r="B27" s="345"/>
+      <c r="C27" s="345"/>
+      <c r="D27" s="345"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
       <c r="G27" s="160"/>
       <c r="H27" s="160"/>
       <c r="I27" s="160"/>
       <c r="J27" s="160"/>
       <c r="K27" s="160"/>
-      <c r="L27" s="366"/>
-      <c r="M27" s="366"/>
+      <c r="L27" s="347"/>
+      <c r="M27" s="347"/>
       <c r="N27" s="160"/>
       <c r="P27" s="161"/>
       <c r="U27" s="162"/>
     </row>
-    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="364"/>
-      <c r="B28" s="364"/>
-      <c r="C28" s="364"/>
-      <c r="D28" s="364"/>
-      <c r="E28" s="364"/>
-      <c r="F28" s="364"/>
+    <row r="28" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A28" s="345"/>
+      <c r="B28" s="345"/>
+      <c r="C28" s="345"/>
+      <c r="D28" s="345"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
       <c r="G28" s="160"/>
       <c r="H28" s="160"/>
       <c r="I28" s="160"/>
       <c r="J28" s="160"/>
       <c r="K28" s="160"/>
-      <c r="L28" s="366"/>
-      <c r="M28" s="366"/>
+      <c r="L28" s="347"/>
+      <c r="M28" s="347"/>
       <c r="N28" s="160"/>
       <c r="P28" s="161"/>
       <c r="U28" s="162"/>
     </row>
-    <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="364"/>
-      <c r="B29" s="364"/>
-      <c r="C29" s="364"/>
-      <c r="D29" s="364"/>
-      <c r="E29" s="364"/>
-      <c r="F29" s="364"/>
+    <row r="29" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="A29" s="345"/>
+      <c r="B29" s="345"/>
+      <c r="C29" s="345"/>
+      <c r="D29" s="345"/>
+      <c r="E29" s="345"/>
+      <c r="F29" s="345"/>
       <c r="G29" s="160"/>
       <c r="H29" s="160"/>
       <c r="I29" s="160"/>
       <c r="J29" s="160"/>
       <c r="K29" s="160"/>
-      <c r="L29" s="366"/>
-      <c r="M29" s="366"/>
+      <c r="L29" s="347"/>
+      <c r="M29" s="347"/>
       <c r="N29" s="160"/>
       <c r="P29" s="161"/>
       <c r="U29" s="162"/>
     </row>
-    <row r="30" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="364"/>
-      <c r="B30" s="364"/>
-      <c r="C30" s="364"/>
-      <c r="D30" s="364"/>
-      <c r="E30" s="364"/>
-      <c r="F30" s="364"/>
+    <row r="30" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A30" s="345"/>
+      <c r="B30" s="345"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
       <c r="G30" s="160"/>
       <c r="H30" s="160"/>
       <c r="I30" s="160"/>
       <c r="J30" s="160"/>
       <c r="K30" s="160"/>
-      <c r="L30" s="366"/>
-      <c r="M30" s="366"/>
+      <c r="L30" s="347"/>
+      <c r="M30" s="347"/>
       <c r="N30" s="160"/>
       <c r="P30" s="163"/>
       <c r="Q30" s="5"/>
@@ -16251,6 +16217,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="K6:K22"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="L6:U6"/>
+    <mergeCell ref="A3:J4"/>
+    <mergeCell ref="A7:J20"/>
+    <mergeCell ref="L7:U20"/>
     <mergeCell ref="P24:U25"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="L24:M24"/>
@@ -16266,18 +16244,6 @@
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="K6:K22"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="L6:U6"/>
-    <mergeCell ref="A3:J4"/>
-    <mergeCell ref="A7:J20"/>
-    <mergeCell ref="L7:U20"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.19685039370078741" top="0.3" bottom="0" header="0" footer="0.38"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
